--- a/src/assets/downloads/LZK-Rechner_LNF_V1.0_Beispiel.xlsx
+++ b/src/assets/downloads/LZK-Rechner_LNF_V1.0_Beispiel.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20414"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20415"/>
   <workbookPr updateLinks="never"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Julia Pelzeter\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Julia Pelzeter\Downloads\Online-Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C5DAC21-6B16-4725-B1BF-715610F1738E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9AFBD6D-EC2F-4E54-A5D3-9191262F3CBA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" tabRatio="887" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1166,9 +1166,6 @@
     </r>
   </si>
   <si>
-    <t>Ladeverhalten Elektroauto</t>
-  </si>
-  <si>
     <t>Ergänzende Angaben für Elektrofahrzeuge:</t>
   </si>
   <si>
@@ -3525,6 +3522,9 @@
   </si>
   <si>
     <t>=Input_Beschaffung!$C$14</t>
+  </si>
+  <si>
+    <t>Ladeverhalten Elektrofahrzeug</t>
   </si>
 </sst>
 </file>
@@ -5839,49 +5839,49 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" xfId="4" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" xfId="4" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" xfId="4" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="20" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" xfId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" xfId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" xfId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="20" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
@@ -6027,6 +6027,33 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -6046,31 +6073,7 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6083,9 +6086,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -12771,8 +12771,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="10145819" y="2392680"/>
-          <a:ext cx="1630074" cy="969010"/>
+          <a:off x="10143914" y="2432685"/>
+          <a:ext cx="1631979" cy="972820"/>
           <a:chOff x="8390255" y="2565400"/>
           <a:chExt cx="1643409" cy="965200"/>
         </a:xfrm>
@@ -14366,7 +14366,7 @@
   <sheetData>
     <row r="2" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B2" s="16" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C2" s="16"/>
       <c r="D2" s="16"/>
@@ -14376,7 +14376,7 @@
       <c r="H2" s="16"/>
       <c r="I2" s="16"/>
       <c r="J2" s="268" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.25">
@@ -14398,17 +14398,17 @@
       <c r="J4" s="115"/>
     </row>
     <row r="5" spans="2:10" ht="163.19999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="394" t="s">
-        <v>531</v>
-      </c>
-      <c r="C5" s="394"/>
-      <c r="D5" s="394"/>
-      <c r="E5" s="394"/>
-      <c r="F5" s="394"/>
-      <c r="G5" s="394"/>
-      <c r="H5" s="394"/>
-      <c r="I5" s="394"/>
-      <c r="J5" s="394"/>
+      <c r="B5" s="391" t="s">
+        <v>530</v>
+      </c>
+      <c r="C5" s="391"/>
+      <c r="D5" s="391"/>
+      <c r="E5" s="391"/>
+      <c r="F5" s="391"/>
+      <c r="G5" s="391"/>
+      <c r="H5" s="391"/>
+      <c r="I5" s="391"/>
+      <c r="J5" s="391"/>
     </row>
     <row r="6" spans="2:10" ht="11.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="245"/>
@@ -14446,13 +14446,13 @@
     <row r="9" spans="2:10" ht="52.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D9" s="245"/>
       <c r="E9" s="245"/>
-      <c r="F9" s="395" t="s">
-        <v>412</v>
-      </c>
-      <c r="G9" s="395"/>
-      <c r="H9" s="395"/>
-      <c r="I9" s="395"/>
-      <c r="J9" s="395"/>
+      <c r="F9" s="392" t="s">
+        <v>411</v>
+      </c>
+      <c r="G9" s="392"/>
+      <c r="H9" s="392"/>
+      <c r="I9" s="392"/>
+      <c r="J9" s="392"/>
     </row>
     <row r="10" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D10" s="245"/>
@@ -14466,31 +14466,31 @@
     <row r="11" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D11" s="245"/>
       <c r="E11" s="245"/>
-      <c r="F11" s="396" t="s">
-        <v>427</v>
-      </c>
-      <c r="G11" s="397"/>
-      <c r="H11" s="397"/>
-      <c r="I11" s="397"/>
-      <c r="J11" s="397"/>
+      <c r="F11" s="393" t="s">
+        <v>426</v>
+      </c>
+      <c r="G11" s="394"/>
+      <c r="H11" s="394"/>
+      <c r="I11" s="394"/>
+      <c r="J11" s="394"/>
     </row>
     <row r="12" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D12" s="245"/>
       <c r="E12" s="245"/>
-      <c r="F12" s="397"/>
-      <c r="G12" s="397"/>
-      <c r="H12" s="397"/>
-      <c r="I12" s="397"/>
-      <c r="J12" s="397"/>
+      <c r="F12" s="394"/>
+      <c r="G12" s="394"/>
+      <c r="H12" s="394"/>
+      <c r="I12" s="394"/>
+      <c r="J12" s="394"/>
     </row>
     <row r="13" spans="2:10" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D13" s="245"/>
       <c r="E13" s="245"/>
-      <c r="F13" s="397"/>
-      <c r="G13" s="397"/>
-      <c r="H13" s="397"/>
-      <c r="I13" s="397"/>
-      <c r="J13" s="397"/>
+      <c r="F13" s="394"/>
+      <c r="G13" s="394"/>
+      <c r="H13" s="394"/>
+      <c r="I13" s="394"/>
+      <c r="J13" s="394"/>
     </row>
     <row r="14" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D14" s="245"/>
@@ -14504,22 +14504,22 @@
     <row r="15" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D15" s="245"/>
       <c r="E15" s="245"/>
-      <c r="F15" s="398" t="s">
+      <c r="F15" s="395" t="s">
         <v>1</v>
       </c>
-      <c r="G15" s="399"/>
-      <c r="H15" s="399"/>
-      <c r="I15" s="399"/>
-      <c r="J15" s="399"/>
+      <c r="G15" s="396"/>
+      <c r="H15" s="396"/>
+      <c r="I15" s="396"/>
+      <c r="J15" s="396"/>
     </row>
     <row r="16" spans="2:10" ht="73.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D16" s="245"/>
       <c r="E16" s="245"/>
-      <c r="F16" s="399"/>
-      <c r="G16" s="399"/>
-      <c r="H16" s="399"/>
-      <c r="I16" s="399"/>
-      <c r="J16" s="399"/>
+      <c r="F16" s="396"/>
+      <c r="G16" s="396"/>
+      <c r="H16" s="396"/>
+      <c r="I16" s="396"/>
+      <c r="J16" s="396"/>
     </row>
     <row r="17" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D17" s="245"/>
@@ -14533,13 +14533,13 @@
     <row r="18" spans="2:10" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D18" s="245"/>
       <c r="E18" s="245"/>
-      <c r="F18" s="400" t="s">
+      <c r="F18" s="397" t="s">
         <v>2</v>
       </c>
-      <c r="G18" s="401"/>
-      <c r="H18" s="401"/>
-      <c r="I18" s="401"/>
-      <c r="J18" s="401"/>
+      <c r="G18" s="398"/>
+      <c r="H18" s="398"/>
+      <c r="I18" s="398"/>
+      <c r="J18" s="398"/>
     </row>
     <row r="19" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D19" s="245"/>
@@ -14553,31 +14553,31 @@
     <row r="20" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D20" s="245"/>
       <c r="E20" s="245"/>
-      <c r="F20" s="402" t="s">
+      <c r="F20" s="399" t="s">
         <v>3</v>
       </c>
-      <c r="G20" s="402"/>
-      <c r="H20" s="402"/>
-      <c r="I20" s="402"/>
-      <c r="J20" s="402"/>
+      <c r="G20" s="399"/>
+      <c r="H20" s="399"/>
+      <c r="I20" s="399"/>
+      <c r="J20" s="399"/>
     </row>
     <row r="21" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D21" s="245"/>
       <c r="E21" s="245"/>
-      <c r="F21" s="402"/>
-      <c r="G21" s="402"/>
-      <c r="H21" s="402"/>
-      <c r="I21" s="402"/>
-      <c r="J21" s="402"/>
+      <c r="F21" s="399"/>
+      <c r="G21" s="399"/>
+      <c r="H21" s="399"/>
+      <c r="I21" s="399"/>
+      <c r="J21" s="399"/>
     </row>
     <row r="22" spans="2:10" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D22" s="245"/>
       <c r="E22" s="245"/>
-      <c r="F22" s="402"/>
-      <c r="G22" s="402"/>
-      <c r="H22" s="402"/>
-      <c r="I22" s="402"/>
-      <c r="J22" s="402"/>
+      <c r="F22" s="399"/>
+      <c r="G22" s="399"/>
+      <c r="H22" s="399"/>
+      <c r="I22" s="399"/>
+      <c r="J22" s="399"/>
     </row>
     <row r="23" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D23" s="245"/>
@@ -14591,22 +14591,22 @@
     <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D24" s="245"/>
       <c r="E24" s="245"/>
-      <c r="F24" s="403" t="s">
+      <c r="F24" s="400" t="s">
         <v>4</v>
       </c>
-      <c r="G24" s="403"/>
-      <c r="H24" s="403"/>
-      <c r="I24" s="403"/>
-      <c r="J24" s="403"/>
+      <c r="G24" s="400"/>
+      <c r="H24" s="400"/>
+      <c r="I24" s="400"/>
+      <c r="J24" s="400"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D25" s="245"/>
       <c r="E25" s="245"/>
-      <c r="F25" s="403"/>
-      <c r="G25" s="403"/>
-      <c r="H25" s="403"/>
-      <c r="I25" s="403"/>
-      <c r="J25" s="403"/>
+      <c r="F25" s="400"/>
+      <c r="G25" s="400"/>
+      <c r="H25" s="400"/>
+      <c r="I25" s="400"/>
+      <c r="J25" s="400"/>
     </row>
     <row r="26" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="245"/>
@@ -14620,49 +14620,49 @@
     <row r="27" spans="2:10" ht="7.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D27" s="245"/>
       <c r="E27" s="245"/>
-      <c r="F27" s="393"/>
-      <c r="G27" s="393"/>
-      <c r="H27" s="393"/>
-      <c r="I27" s="393"/>
-      <c r="J27" s="393"/>
+      <c r="F27" s="390"/>
+      <c r="G27" s="390"/>
+      <c r="H27" s="390"/>
+      <c r="I27" s="390"/>
+      <c r="J27" s="390"/>
     </row>
     <row r="28" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D28" s="245"/>
       <c r="E28" s="245"/>
-      <c r="F28" s="404" t="s">
-        <v>428</v>
-      </c>
-      <c r="G28" s="404"/>
-      <c r="H28" s="404"/>
-      <c r="I28" s="404"/>
-      <c r="J28" s="404"/>
+      <c r="F28" s="401" t="s">
+        <v>427</v>
+      </c>
+      <c r="G28" s="401"/>
+      <c r="H28" s="401"/>
+      <c r="I28" s="401"/>
+      <c r="J28" s="401"/>
     </row>
     <row r="29" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D29" s="245"/>
       <c r="E29" s="245"/>
-      <c r="F29" s="404"/>
-      <c r="G29" s="404"/>
-      <c r="H29" s="404"/>
-      <c r="I29" s="404"/>
-      <c r="J29" s="404"/>
+      <c r="F29" s="401"/>
+      <c r="G29" s="401"/>
+      <c r="H29" s="401"/>
+      <c r="I29" s="401"/>
+      <c r="J29" s="401"/>
     </row>
     <row r="30" spans="2:10" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D30" s="245"/>
       <c r="E30" s="245"/>
-      <c r="F30" s="404"/>
-      <c r="G30" s="404"/>
-      <c r="H30" s="404"/>
-      <c r="I30" s="404"/>
-      <c r="J30" s="404"/>
+      <c r="F30" s="401"/>
+      <c r="G30" s="401"/>
+      <c r="H30" s="401"/>
+      <c r="I30" s="401"/>
+      <c r="J30" s="401"/>
     </row>
     <row r="31" spans="2:10" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D31" s="245"/>
       <c r="E31" s="245"/>
-      <c r="F31" s="392"/>
-      <c r="G31" s="392"/>
-      <c r="H31" s="392"/>
-      <c r="I31" s="392"/>
-      <c r="J31" s="392"/>
+      <c r="F31" s="402"/>
+      <c r="G31" s="402"/>
+      <c r="H31" s="402"/>
+      <c r="I31" s="402"/>
+      <c r="J31" s="402"/>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="250" t="s">
@@ -14711,15 +14711,15 @@
     <row r="36" spans="2:11" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="116"/>
       <c r="C36" s="113"/>
-      <c r="D36" s="392" t="s">
+      <c r="D36" s="402" t="s">
         <v>7</v>
       </c>
-      <c r="E36" s="392"/>
-      <c r="F36" s="392"/>
-      <c r="G36" s="392"/>
-      <c r="H36" s="392"/>
-      <c r="I36" s="392"/>
-      <c r="J36" s="392"/>
+      <c r="E36" s="402"/>
+      <c r="F36" s="402"/>
+      <c r="G36" s="402"/>
+      <c r="H36" s="402"/>
+      <c r="I36" s="402"/>
+      <c r="J36" s="402"/>
     </row>
     <row r="37" spans="2:11" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="117"/>
@@ -14735,24 +14735,24 @@
     <row r="38" spans="2:11" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="241"/>
       <c r="C38" s="113"/>
-      <c r="D38" s="393" t="s">
+      <c r="D38" s="390" t="s">
         <v>8</v>
       </c>
-      <c r="E38" s="393"/>
-      <c r="F38" s="393"/>
-      <c r="G38" s="393"/>
-      <c r="H38" s="393"/>
-      <c r="I38" s="393"/>
-      <c r="J38" s="393"/>
+      <c r="E38" s="390"/>
+      <c r="F38" s="390"/>
+      <c r="G38" s="390"/>
+      <c r="H38" s="390"/>
+      <c r="I38" s="390"/>
+      <c r="J38" s="390"/>
     </row>
     <row r="39" spans="2:11" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D39" s="393"/>
-      <c r="E39" s="393"/>
-      <c r="F39" s="393"/>
-      <c r="G39" s="393"/>
-      <c r="H39" s="393"/>
-      <c r="I39" s="393"/>
-      <c r="J39" s="393"/>
+      <c r="D39" s="390"/>
+      <c r="E39" s="390"/>
+      <c r="F39" s="390"/>
+      <c r="G39" s="390"/>
+      <c r="H39" s="390"/>
+      <c r="I39" s="390"/>
+      <c r="J39" s="390"/>
     </row>
     <row r="40" spans="2:11" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="117"/>
@@ -14770,15 +14770,15 @@
         <v>9</v>
       </c>
       <c r="C41" s="113"/>
-      <c r="D41" s="390" t="s">
+      <c r="D41" s="403" t="s">
         <v>10</v>
       </c>
-      <c r="E41" s="390"/>
-      <c r="F41" s="390"/>
-      <c r="G41" s="390"/>
-      <c r="H41" s="390"/>
-      <c r="I41" s="390"/>
-      <c r="J41" s="390"/>
+      <c r="E41" s="403"/>
+      <c r="F41" s="403"/>
+      <c r="G41" s="403"/>
+      <c r="H41" s="403"/>
+      <c r="I41" s="403"/>
+      <c r="J41" s="403"/>
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" s="113"/>
@@ -14792,30 +14792,30 @@
       <c r="J42" s="245"/>
     </row>
     <row r="43" spans="2:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="391" t="s">
+      <c r="B43" s="404" t="s">
         <v>11</v>
       </c>
       <c r="C43" s="103"/>
-      <c r="D43" s="392" t="s">
+      <c r="D43" s="402" t="s">
         <v>12</v>
       </c>
-      <c r="E43" s="392"/>
-      <c r="F43" s="392"/>
-      <c r="G43" s="392"/>
-      <c r="H43" s="392"/>
-      <c r="I43" s="392"/>
-      <c r="J43" s="392"/>
+      <c r="E43" s="402"/>
+      <c r="F43" s="402"/>
+      <c r="G43" s="402"/>
+      <c r="H43" s="402"/>
+      <c r="I43" s="402"/>
+      <c r="J43" s="402"/>
     </row>
     <row r="44" spans="2:11" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="B44" s="391"/>
+      <c r="B44" s="404"/>
       <c r="C44" s="103"/>
-      <c r="D44" s="392"/>
-      <c r="E44" s="392"/>
-      <c r="F44" s="392"/>
-      <c r="G44" s="392"/>
-      <c r="H44" s="392"/>
-      <c r="I44" s="392"/>
-      <c r="J44" s="392"/>
+      <c r="D44" s="402"/>
+      <c r="E44" s="402"/>
+      <c r="F44" s="402"/>
+      <c r="G44" s="402"/>
+      <c r="H44" s="402"/>
+      <c r="I44" s="402"/>
+      <c r="J44" s="402"/>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="D45" s="112"/>
@@ -14827,17 +14827,17 @@
       <c r="J45" s="114"/>
     </row>
     <row r="46" spans="2:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="392" t="s">
-        <v>403</v>
-      </c>
-      <c r="C46" s="392"/>
-      <c r="D46" s="392"/>
-      <c r="E46" s="392"/>
-      <c r="F46" s="392"/>
-      <c r="G46" s="392"/>
-      <c r="H46" s="392"/>
-      <c r="I46" s="392"/>
-      <c r="J46" s="392"/>
+      <c r="B46" s="402" t="s">
+        <v>402</v>
+      </c>
+      <c r="C46" s="402"/>
+      <c r="D46" s="402"/>
+      <c r="E46" s="402"/>
+      <c r="F46" s="402"/>
+      <c r="G46" s="402"/>
+      <c r="H46" s="402"/>
+      <c r="I46" s="402"/>
+      <c r="J46" s="402"/>
       <c r="K46" s="107"/>
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.25">
@@ -14872,17 +14872,17 @@
       <c r="J49" s="112"/>
     </row>
     <row r="50" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="392" t="s">
+      <c r="B50" s="402" t="s">
         <v>14</v>
       </c>
-      <c r="C50" s="392"/>
-      <c r="D50" s="392"/>
-      <c r="E50" s="392"/>
-      <c r="F50" s="392"/>
-      <c r="G50" s="392"/>
-      <c r="H50" s="392"/>
-      <c r="I50" s="392"/>
-      <c r="J50" s="392"/>
+      <c r="C50" s="402"/>
+      <c r="D50" s="402"/>
+      <c r="E50" s="402"/>
+      <c r="F50" s="402"/>
+      <c r="G50" s="402"/>
+      <c r="H50" s="402"/>
+      <c r="I50" s="402"/>
+      <c r="J50" s="402"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D51" s="114"/>
@@ -14945,6 +14945,11 @@
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="17">
+    <mergeCell ref="D41:J41"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="D43:J44"/>
+    <mergeCell ref="B46:J46"/>
+    <mergeCell ref="B50:J50"/>
     <mergeCell ref="D38:J39"/>
     <mergeCell ref="B5:J5"/>
     <mergeCell ref="F9:J9"/>
@@ -14957,11 +14962,6 @@
     <mergeCell ref="F28:J30"/>
     <mergeCell ref="F31:J31"/>
     <mergeCell ref="D36:J36"/>
-    <mergeCell ref="D41:J41"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="D43:J44"/>
-    <mergeCell ref="B46:J46"/>
-    <mergeCell ref="B50:J50"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F9:J9" location="Input_Beschaffung!A1" display="Geben Sie die übergeordneten Informationen zu Ihrem Beschaffungsfall ein. Hier können Informationen wie die erwartete jährliche Fahrleistung, die Art der Beschaffung (Kauf/Leasing) und weitere Informationen eingegeben werden." xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -15003,7 +15003,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>20</v>
@@ -15016,7 +15016,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B4" s="154" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -15032,7 +15032,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C6" s="54">
         <v>4</v>
@@ -15045,7 +15045,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C7" s="102" t="str">
         <f>IF(Anbieter4=0,"",Anbieter4)</f>
@@ -15067,7 +15067,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C9" s="102"/>
       <c r="E9" s="125"/>
@@ -15075,7 +15075,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C10" s="102" t="str">
         <f>IF(Hersteller4=0,"",Hersteller4)</f>
@@ -15087,7 +15087,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C11" s="102" t="str">
         <f>IF(Modell4=0,"",Modell4)</f>
@@ -15099,7 +15099,7 @@
     </row>
     <row r="12" spans="1:6" ht="43.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="56" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C12" s="102" t="str">
         <f>IF(Zusatzinfo4=0,"",Zusatzinfo4)</f>
@@ -15111,7 +15111,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B13" s="57" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="102" t="str">
         <f>IF(Antriebsart4=0,"",Antriebsart4)</f>
@@ -15122,7 +15122,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C14" s="102" t="str">
         <f>IF(Energie4=0,"",Energie4)</f>
@@ -15138,7 +15138,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B16" s="154" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -15154,7 +15154,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B18" s="72" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C18" s="288">
         <f>0.0057*(ReichwPHEV4/23)^3-0.0838*(ReichwPHEV4/23)^2+0.4261*(ReichwPHEV4/23)+ 0.1633</f>
@@ -15166,35 +15166,35 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C19" s="289">
         <f>Verbrauch4/(1-0.9*C18)</f>
         <v>0</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E19" s="125"/>
       <c r="F19" s="125"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B20" s="72" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C20" s="290">
         <f>VerbEl_WLTP4/C18</f>
         <v>152.48009797917942</v>
       </c>
       <c r="D20" s="184" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E20" s="125"/>
       <c r="F20" s="125"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B21" s="186" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C21" s="291">
         <f>0.0021*(ReichwPHEV4/23)^3-0.0358*(ReichwPHEV4/23)^2+0.2607*(ReichwPHEV4/23)- 0.0267</f>
@@ -15209,14 +15209,14 @@
         <v>11</v>
       </c>
       <c r="B22" s="470" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C22" s="292">
         <f>C19*(1-0.9*C21)</f>
         <v>0</v>
       </c>
       <c r="D22" s="185" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E22" s="125"/>
       <c r="F22" s="125"/>
@@ -15229,7 +15229,7 @@
         <v>-4.0712186160440904</v>
       </c>
       <c r="D23" s="183" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E23" s="125"/>
       <c r="F23" s="125"/>
@@ -15241,7 +15241,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B25" s="154" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
@@ -15254,7 +15254,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B27" s="60" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C27" s="61"/>
       <c r="D27" s="60"/>
@@ -15263,42 +15263,42 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C28" s="279">
         <f>IF(Antriebsart4="Vollelektrisch (BEV)",0,IFERROR(VLOOKUP(Energie4,EnKostList,8,FALSE),0)*IF(Antriebsart4="Plug-In-Hybrid (PHEV)",VerbPHEV4,Verbrauch4)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E28" s="125"/>
       <c r="F28" s="125"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C29" s="279">
         <f>IF(Antriebsart4="Verbrenner",0,VLOOKUP("Strom",EnKostList,8,FALSE)*IF(Antriebsart4="Plug-In-Hybrid (PHEV)",VerbElPHEV4,VerbEl_WLTP4)/100*Fahrleistung)</f>
         <v>3124.95</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E29" s="125"/>
       <c r="F29" s="125"/>
     </row>
     <row r="30" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="64" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C30" s="280">
         <f>SUM(C28:C29)</f>
         <v>3124.95</v>
       </c>
       <c r="D30" s="64" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E30" s="125"/>
       <c r="F30" s="125"/>
@@ -15311,7 +15311,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B32" s="60" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C32" s="145" t="str">
         <f>CONCATENATE("Energieträger: ",Energie4)</f>
@@ -15323,70 +15323,70 @@
     </row>
     <row r="33" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B33" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C33" s="279">
         <f>IF(Antriebsart4="Plug-In-Hybrid (PHEV)",VerbPHEV4*VLOOKUP(Energie4,CO2List,2,FALSE)/100,CO2_4)*Fahrleistung/1000000</f>
         <v>0</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E33" s="125"/>
       <c r="F33" s="125"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C34" s="279">
         <f>C33*Kost_THG</f>
         <v>0</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E34" s="125"/>
       <c r="F34" s="125"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B35" s="7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C35" s="287">
         <f>IF(Energie4="Strom",0,NOX_4*Fahrleistung*Kost_NOX/1000)</f>
         <v>0</v>
       </c>
       <c r="D35" s="65" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E35" s="125"/>
       <c r="F35" s="125"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B36" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C36" s="287">
         <f>IF(Energie4="Strom",0,Partikel4*Fahrleistung*Kost_Partikel/1000)</f>
         <v>0</v>
       </c>
       <c r="D36" s="65" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E36" s="125"/>
       <c r="F36" s="125"/>
     </row>
     <row r="37" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="64" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C37" s="280">
         <f>SUM(C34:C36)</f>
         <v>0</v>
       </c>
       <c r="D37" s="64" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E37" s="125"/>
       <c r="F37" s="125"/>
@@ -15399,7 +15399,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B39" s="60" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C39" s="145" t="str">
         <f>CONCATENATE("Energieträger: ",Energie4,IF(Antriebsart4="Plug-In-Hybrid (PHEV)","+Strom",""))</f>
@@ -15411,28 +15411,28 @@
     </row>
     <row r="40" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B40" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C40" s="279">
         <f>IFERROR(IF(Antriebsart4="Vollelektrisch (BEV)",VLOOKUP("Strom",CO2List,3,FALSE)*VerbEl_WLTP4/100*Fahrleistung/1000000,IF(Antriebsart4="Verbrenner",VLOOKUP(Energie4,CO2List,3,FALSE)*Verbrauch4/100*Fahrleistung/1000000,VLOOKUP(Energie4,CO2List,3,FALSE)*VerbPHEV4/100*Fahrleistung/1000000+VLOOKUP("Strom",CO2List,3,FALSE)*VerbElPHEV4/100*Fahrleistung/1000000)),0)</f>
         <v>1.8114749999999993</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E40" s="125"/>
       <c r="F40" s="125"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B41" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C41" s="279">
         <f>C40*Kost_THG</f>
         <v>1557.8684999999994</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E41" s="125"/>
       <c r="F41" s="125"/>
@@ -15443,7 +15443,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B43" s="154" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
@@ -15460,55 +15460,55 @@
     <row r="45" spans="1:6" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="107"/>
       <c r="B45" s="90" t="s">
+        <v>158</v>
+      </c>
+      <c r="C45" s="134" t="s">
         <v>159</v>
-      </c>
-      <c r="C45" s="134" t="s">
-        <v>160</v>
       </c>
       <c r="D45" s="62"/>
       <c r="E45" s="125"/>
       <c r="F45" s="125"/>
     </row>
     <row r="46" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A46" s="391" t="s">
+      <c r="A46" s="404" t="s">
         <v>11</v>
       </c>
       <c r="B46" s="468" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C46" s="281">
         <f>IF(OR(Antriebsart4="Vollelektrisch (BEV)",Antriebsart4="Plug-In-Hybrid (PHEV)"),Batterie4*Batterie_THG/1000,0)</f>
         <v>4.2</v>
       </c>
       <c r="D46" s="131" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E46" s="127"/>
       <c r="F46" s="125"/>
     </row>
     <row r="47" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="391"/>
+      <c r="A47" s="404"/>
       <c r="B47" s="469"/>
       <c r="C47" s="281">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
         <v>19.09090909090909</v>
       </c>
       <c r="D47" s="130" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E47" s="127"/>
       <c r="F47" s="125"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B48" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C48" s="279">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Kost_THG, C46/Haltedauer*Kost_THG)</f>
         <v>410.45454545454544</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E48" s="125"/>
       <c r="F48" s="125"/>
@@ -15532,20 +15532,20 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="54" spans="1:6" s="70" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="68" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C54" s="282">
         <f>IF(FinArt="Kauf",IF(KaufpreisRech="Kaufpreis",Gesamtpreis4,0),Gesamtpreis4*Haltedauer*12+IF(FinArt="Leasing",LeasSondZahl4,0))</f>
         <v>0</v>
       </c>
       <c r="D54" s="68" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E54" s="69"/>
       <c r="F54" s="58"/>
@@ -15555,72 +15555,72 @@
         <v>11</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C55" s="283">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis4-Gesamtpreis4*(-0.2*LN(Haltedauer)+0.667),0)</f>
         <v>33044.160956034983</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E55" s="125"/>
       <c r="F55" s="73"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B56" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C56" s="283">
         <f>C30*Haltedauer</f>
         <v>21874.649999999998</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F56" s="73"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C57" s="283">
         <f>C37*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F57" s="58"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C58" s="283">
         <f>C41*Haltedauer</f>
         <v>10905.079499999996</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F58" s="58"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B59" s="333" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C59" s="334">
         <f>C48*Haltedauer</f>
         <v>2873.181818181818</v>
       </c>
       <c r="D59" s="80" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="391" t="s">
+      <c r="A60" s="404" t="s">
         <v>11</v>
       </c>
       <c r="B60" s="327" t="str">
@@ -15638,7 +15638,7 @@
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="391"/>
+      <c r="A61" s="404"/>
       <c r="B61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
@@ -15654,7 +15654,7 @@
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="391"/>
+      <c r="A62" s="404"/>
       <c r="B62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
@@ -15671,14 +15671,14 @@
     </row>
     <row r="63" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B63" s="64" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C63" s="284">
         <f>SUM(C54:C62)</f>
         <v>68697.0722742168</v>
       </c>
       <c r="D63" s="64" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E63" s="14"/>
       <c r="F63" s="58"/>
@@ -15693,26 +15693,26 @@
     </row>
     <row r="65" spans="2:5" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B65" s="68" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C65" s="285">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Haltedauer, C46)</f>
         <v>3.3409090909090908</v>
       </c>
       <c r="D65" s="68" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="66" spans="2:5" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B66" s="72" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C66" s="286">
         <f>C33*Haltedauer+C40*Haltedauer</f>
         <v>12.680324999999995</v>
       </c>
       <c r="D66" s="72" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E66" s="71"/>
     </row>
@@ -15763,7 +15763,7 @@
     </row>
     <row r="2" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>20</v>
@@ -15776,7 +15776,7 @@
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="154" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -15792,7 +15792,7 @@
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C6" s="54">
         <v>5</v>
@@ -15805,7 +15805,7 @@
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C7" s="102" t="str">
         <f>IF(Anbieter5=0,"",Anbieter5)</f>
@@ -15827,7 +15827,7 @@
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C9" s="102"/>
       <c r="E9" s="125"/>
@@ -15835,7 +15835,7 @@
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C10" s="102" t="str">
         <f>IF(Hersteller5=0,"",Hersteller5)</f>
@@ -15847,7 +15847,7 @@
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C11" s="102" t="str">
         <f>IF(Modell5=0,"",Modell5)</f>
@@ -15859,7 +15859,7 @@
     </row>
     <row r="12" spans="2:6" ht="43.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="56" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C12" s="102" t="str">
         <f>IF(Zusatzinfo5=0,"",Zusatzinfo5)</f>
@@ -15871,7 +15871,7 @@
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B13" s="57" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="102" t="str">
         <f>IF(Antriebsart5=0,"",Antriebsart5)</f>
@@ -15882,7 +15882,7 @@
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C14" s="102" t="str">
         <f>IF(Energie5=0,"",Energie5)</f>
@@ -15900,7 +15900,7 @@
     </row>
     <row r="16" spans="2:6" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="154" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -15917,7 +15917,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B18" s="72" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C18" s="288">
         <f>0.0057*(ReichwPHEV5/23)^3-0.0838*(ReichwPHEV5/23)^2+0.4261*(ReichwPHEV5/23)+ 0.1633</f>
@@ -15929,35 +15929,35 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C19" s="289">
         <f>Verbrauch5/(1-0.9*C18)</f>
         <v>0</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E19" s="125"/>
       <c r="F19" s="125"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B20" s="72" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C20" s="290">
         <f>VerbEl_WLTP5/C18</f>
         <v>113.90079608083283</v>
       </c>
       <c r="D20" s="184" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E20" s="125"/>
       <c r="F20" s="125"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B21" s="186" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C21" s="291">
         <f>0.0021*(ReichwPHEV5/23)^3-0.0358*(ReichwPHEV5/23)^2+0.2607*(ReichwPHEV5/23)- 0.0267</f>
@@ -15972,14 +15972,14 @@
         <v>11</v>
       </c>
       <c r="B22" s="470" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C22" s="292">
         <f>C19*(1-0.9*C21)</f>
         <v>0</v>
       </c>
       <c r="D22" s="185" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E22" s="125"/>
       <c r="F22" s="125"/>
@@ -15992,7 +15992,7 @@
         <v>-3.0411512553582369</v>
       </c>
       <c r="D23" s="183" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E23" s="125"/>
       <c r="F23" s="125"/>
@@ -16004,7 +16004,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B25" s="154" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
@@ -16017,7 +16017,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B27" s="60" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C27" s="61"/>
       <c r="D27" s="60"/>
@@ -16026,42 +16026,42 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C28" s="279">
         <f>IF(Antriebsart5="Vollelektrisch (BEV)",0,IFERROR(VLOOKUP(Energie5,EnKostList,8,FALSE),0)*IF(Antriebsart5="Plug-In-Hybrid (PHEV)",VerbPHEV5,Verbrauch5)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E28" s="125"/>
       <c r="F28" s="125"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C29" s="279">
         <f>IF(Antriebsart5="Verbrenner",0,VLOOKUP("Strom",EnKostList,8,FALSE)*IF(Antriebsart5="Plug-In-Hybrid (PHEV)",VerbElPHEV5,VerbEl_WLTP5)/100*Fahrleistung)</f>
         <v>2334.3000000000002</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E29" s="125"/>
       <c r="F29" s="125"/>
     </row>
     <row r="30" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="64" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C30" s="280">
         <f>SUM(C28:C29)</f>
         <v>2334.3000000000002</v>
       </c>
       <c r="D30" s="64" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E30" s="125"/>
       <c r="F30" s="125"/>
@@ -16074,7 +16074,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B32" s="60" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C32" s="145" t="str">
         <f>CONCATENATE("Energieträger: ",Energie5)</f>
@@ -16087,70 +16087,70 @@
     <row r="33" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A33" s="126"/>
       <c r="B33" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C33" s="279">
         <f>IF(Antriebsart5="Plug-In-Hybrid (PHEV)",VerbPHEV5*VLOOKUP(Energie5,CO2List,2,FALSE)/100,CO2_5)*Fahrleistung/1000000</f>
         <v>0</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E33" s="125"/>
       <c r="F33" s="125"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C34" s="279">
         <f>C33*Kost_THG</f>
         <v>0</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E34" s="125"/>
       <c r="F34" s="125"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B35" s="7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C35" s="287">
         <f>IF(Energie5="Strom",0,NOX_5*Fahrleistung*Kost_NOX/1000)</f>
         <v>0</v>
       </c>
       <c r="D35" s="65" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E35" s="125"/>
       <c r="F35" s="125"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B36" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C36" s="287">
         <f>IF(Energie5="Strom",0,Partikel5*Fahrleistung*Kost_Partikel/1000)</f>
         <v>0</v>
       </c>
       <c r="D36" s="65" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E36" s="125"/>
       <c r="F36" s="125"/>
     </row>
     <row r="37" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="64" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C37" s="280">
         <f>SUM(C34:C36)</f>
         <v>0</v>
       </c>
       <c r="D37" s="64" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E37" s="125"/>
       <c r="F37" s="125"/>
@@ -16163,7 +16163,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B39" s="60" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C39" s="145" t="str">
         <f>CONCATENATE("Energieträger: ",Energie5,IF(Antriebsart5="Plug-In-Hybrid (PHEV)","+Strom",""))</f>
@@ -16175,28 +16175,28 @@
     </row>
     <row r="40" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B40" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C40" s="279">
         <f>IFERROR(IF(Antriebsart5="Vollelektrisch (BEV)",VLOOKUP("Strom",CO2List,3,FALSE)*VerbEl_WLTP5/100*Fahrleistung/1000000,IF(Antriebsart5="Verbrenner",VLOOKUP(Energie5,CO2List,3,FALSE)*Verbrauch5/100*Fahrleistung/1000000,VLOOKUP(Energie5,CO2List,3,FALSE)*VerbPHEV5/100*Fahrleistung/1000000+VLOOKUP("Strom",CO2List,3,FALSE)*VerbElPHEV5/100*Fahrleistung/1000000)),0)</f>
         <v>1.3531500000000001</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E40" s="125"/>
       <c r="F40" s="125"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B41" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C41" s="279">
         <f>C40*Kost_THG</f>
         <v>1163.7090000000001</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E41" s="125"/>
       <c r="F41" s="125"/>
@@ -16207,7 +16207,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B43" s="154" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
@@ -16224,55 +16224,55 @@
     <row r="45" spans="1:6" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="107"/>
       <c r="B45" s="90" t="s">
+        <v>158</v>
+      </c>
+      <c r="C45" s="134" t="s">
         <v>159</v>
-      </c>
-      <c r="C45" s="134" t="s">
-        <v>160</v>
       </c>
       <c r="D45" s="62"/>
       <c r="E45" s="125"/>
       <c r="F45" s="125"/>
     </row>
     <row r="46" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A46" s="391" t="s">
+      <c r="A46" s="404" t="s">
         <v>11</v>
       </c>
       <c r="B46" s="468" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C46" s="281">
         <f>IF(OR(Antriebsart5="Vollelektrisch (BEV)",Antriebsart5="Plug-In-Hybrid (PHEV)"),Batterie5*Batterie_THG/1000,0)</f>
         <v>6.3</v>
       </c>
       <c r="D46" s="131" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E46" s="127"/>
       <c r="F46" s="125"/>
     </row>
     <row r="47" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="391"/>
+      <c r="A47" s="404"/>
       <c r="B47" s="469"/>
       <c r="C47" s="281">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
         <v>28.636363636363637</v>
       </c>
       <c r="D47" s="130" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E47" s="127"/>
       <c r="F47" s="125"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B48" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C48" s="279">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Kost_THG, C46/Haltedauer*Kost_THG)</f>
         <v>615.68181818181824</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E48" s="125"/>
       <c r="F48" s="125"/>
@@ -16296,20 +16296,20 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="54" spans="1:6" s="70" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="68" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C54" s="282">
         <f>IF(FinArt="Kauf",IF(KaufpreisRech="Kaufpreis",Gesamtpreis5,0),Gesamtpreis5*Haltedauer*12+IF(FinArt="Leasing",LeasSondZahl5,0))</f>
         <v>0</v>
       </c>
       <c r="D54" s="68" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E54" s="69"/>
       <c r="F54" s="58"/>
@@ -16319,72 +16319,72 @@
         <v>11</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C55" s="283">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis5-Gesamtpreis5*(-0.2*LN(Haltedauer)+0.667),0)</f>
         <v>26805.952582527021</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E55" s="125"/>
       <c r="F55" s="73"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B56" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C56" s="283">
         <f>C30*Haltedauer</f>
         <v>16340.100000000002</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F56" s="73"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C57" s="283">
         <f>C37*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F57" s="58"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C58" s="283">
         <f>C41*Haltedauer</f>
         <v>8145.9630000000006</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F58" s="58"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B59" s="329" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C59" s="330">
         <f>C48*Haltedauer</f>
         <v>4309.7727272727279</v>
       </c>
       <c r="D59" s="329" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="391" t="s">
+      <c r="A60" s="404" t="s">
         <v>11</v>
       </c>
       <c r="B60" s="327" t="str">
@@ -16402,7 +16402,7 @@
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="391"/>
+      <c r="A61" s="404"/>
       <c r="B61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
@@ -16418,7 +16418,7 @@
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="391"/>
+      <c r="A62" s="404"/>
       <c r="B62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
@@ -16435,14 +16435,14 @@
     </row>
     <row r="63" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B63" s="64" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C63" s="284">
         <f>SUM(C54:C62)</f>
         <v>55601.788309799755</v>
       </c>
       <c r="D63" s="64" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E63" s="14"/>
       <c r="F63" s="58"/>
@@ -16457,26 +16457,26 @@
     </row>
     <row r="65" spans="2:5" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B65" s="68" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C65" s="285">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Haltedauer, C46)</f>
         <v>5.0113636363636367</v>
       </c>
       <c r="D65" s="68" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="66" spans="2:5" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B66" s="72" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C66" s="286">
         <f>C33*Haltedauer+C40*Haltedauer</f>
         <v>9.4720500000000012</v>
       </c>
       <c r="D66" s="72" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E66" s="71"/>
     </row>
@@ -16522,7 +16522,7 @@
   <sheetData>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H2" s="106" t="s">
         <v>20</v>
@@ -16530,7 +16530,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B4" s="154" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
@@ -16539,18 +16539,18 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C6" s="63" t="s">
+        <v>169</v>
+      </c>
+      <c r="D6" s="63" t="s">
         <v>170</v>
       </c>
-      <c r="D6" s="63" t="s">
-        <v>171</v>
-      </c>
       <c r="E6" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C7" s="302">
         <v>74.027000000000001</v>
@@ -16559,12 +16559,12 @@
         <v>23.4</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C8" s="302">
         <v>72.787000000000006</v>
@@ -16573,12 +16573,12 @@
         <v>23.2</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C9" s="302">
         <v>56.220999999999997</v>
@@ -16587,12 +16587,12 @@
         <v>20.3</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="92" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C10" s="10"/>
       <c r="D10" s="10"/>
@@ -16602,7 +16602,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B12" s="154" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C12" s="93"/>
       <c r="D12" s="5"/>
@@ -16620,14 +16620,14 @@
     </row>
     <row r="14" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="110" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C14" s="472" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D14" s="472"/>
       <c r="E14" s="473" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F14" s="473"/>
       <c r="G14" s="304"/>
@@ -16635,40 +16635,40 @@
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="66"/>
       <c r="B15" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C15" s="58">
         <v>1</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E15" s="136">
         <f>42.722*0.832</f>
         <v>35.544704000000003</v>
       </c>
       <c r="F15" s="111" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G15" s="111"/>
       <c r="H15" s="136"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C16" s="58">
         <v>1</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E16" s="136">
         <f>43.543*0.742</f>
         <v>32.308906</v>
       </c>
       <c r="F16" s="111" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G16" s="111"/>
       <c r="H16" s="136"/>
@@ -16676,54 +16676,54 @@
     <row r="17" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A17" s="66"/>
       <c r="B17" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C17" s="58">
         <v>1</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E17" s="303">
         <v>46.5</v>
       </c>
       <c r="F17" s="111" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G17" s="111"/>
     </row>
     <row r="18" spans="1:37" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="92" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D18" s="106"/>
       <c r="E18" s="10"/>
     </row>
     <row r="20" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B20" s="154" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
       <c r="H20" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="21" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B21" s="66"/>
       <c r="I21" s="58" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J21" s="135" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="K21" s="135"/>
       <c r="L21" s="135"/>
       <c r="M21" s="135"/>
       <c r="O21" s="137" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="P21" s="137"/>
       <c r="Q21" s="137"/>
@@ -16733,13 +16733,13 @@
     <row r="22" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B22" s="66"/>
       <c r="C22" s="63" t="s">
+        <v>169</v>
+      </c>
+      <c r="D22" s="63" t="s">
         <v>170</v>
       </c>
-      <c r="D22" s="63" t="s">
-        <v>171</v>
-      </c>
       <c r="E22" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23" spans="1:37" ht="16.2" x14ac:dyDescent="0.35">
@@ -16747,7 +16747,7 @@
         <v>11</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C23" s="58">
         <v>0</v>
@@ -16757,12 +16757,12 @@
         <v>290.99999999999994</v>
       </c>
       <c r="E23" s="74" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F23" s="11"/>
       <c r="G23" s="11"/>
       <c r="I23" s="58" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J23" s="2">
         <v>2023</v>
@@ -16851,7 +16851,7 @@
     </row>
     <row r="24" spans="1:37" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B24" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C24" s="96">
         <f>C7*E15</f>
@@ -16862,10 +16862,10 @@
         <v>831.74607360000005</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I24" s="58" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="J24" s="300">
         <v>445</v>
@@ -16954,7 +16954,7 @@
     </row>
     <row r="25" spans="1:37" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B25" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C25" s="96">
         <f>C8*E16</f>
@@ -16965,12 +16965,12 @@
         <v>749.56661919999999</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="26" spans="1:37" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B26" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C26" s="96">
         <f>C9*E17</f>
@@ -16981,7 +16981,7 @@
         <v>943.95</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="K26" s="136"/>
     </row>
@@ -17036,7 +17036,7 @@
   <sheetData>
     <row r="2" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q2" s="106" t="s">
         <v>20</v>
@@ -17044,17 +17044,17 @@
     </row>
     <row r="39" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="234" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="40" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="234" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="41" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="234" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="42" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17065,12 +17065,12 @@
     </row>
     <row r="44" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="45" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="267" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="I45" s="106"/>
     </row>
@@ -17080,39 +17080,39 @@
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B48" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="50" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B50" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B51" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="53" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B53" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.25">
@@ -17120,1231 +17120,1231 @@
         <v>30</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="55" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B55" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B56" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="57" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B59" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="60" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B60" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>631</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>632</v>
       </c>
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B61" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="62" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B62" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>208</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B63" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D63" s="1" t="s">
         <v>210</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="64" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B64" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D64" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="65" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B65" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="D65" s="1" t="s">
         <v>214</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="66" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B66" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D66" s="1" t="s">
         <v>216</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="67" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B67" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D67" s="1" t="s">
         <v>218</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="68" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B68" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D68" s="1" t="s">
         <v>220</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="69" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B69" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D69" s="1" t="s">
         <v>222</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="70" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B70" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="D70" s="1" t="s">
         <v>224</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="71" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B71" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D71" s="1" t="s">
         <v>226</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="72" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B72" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="73" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B73" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="74" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B74" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="75" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B75" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="76" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B76" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="77" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B77" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="78" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B78" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="79" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B79" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="80" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B80" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="81" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B81" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="82" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B82" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D82" s="1" t="s">
         <v>248</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="83" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B83" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D83" s="1" t="s">
         <v>250</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="84" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B84" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="D84" s="1" t="s">
         <v>252</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="85" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B85" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="D85" s="1" t="s">
         <v>254</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="86" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B86" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="D86" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="87" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B87" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="88" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B88" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="89" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B89" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="90" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B90" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="91" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B91" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="92" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B92" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="93" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B93" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="94" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B94" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="95" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B95" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="96" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B96" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="97" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B97" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="D97" s="1" t="s">
         <v>268</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="98" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B98" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>270</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="99" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B99" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D99" s="1" t="s">
         <v>272</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="100" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B100" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="D100" s="1" t="s">
         <v>274</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="101" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B101" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="D101" s="1" t="s">
         <v>276</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="102" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B102" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="103" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B103" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="104" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B104" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="105" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B105" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="106" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B106" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="107" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B107" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="D107" s="1" t="s">
         <v>288</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="108" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B108" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="D108" s="1" t="s">
         <v>290</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="109" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B109" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>292</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="110" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B110" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="D110" s="1" t="s">
         <v>294</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="111" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B111" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="D111" s="1" t="s">
         <v>296</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="112" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B112" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="113" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B113" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="114" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B114" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="115" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B115" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="116" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B116" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="117" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B117" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="118" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B118" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="119" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B119" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="120" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B120" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="121" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B121" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="122" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B122" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="123" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B123" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="124" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B124" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="125" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B125" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="126" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B126" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="127" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B127" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="128" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B128" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="129" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B129" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="130" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B130" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="131" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B131" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="132" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B132" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="133" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B133" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="134" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B134" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="135" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B135" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="136" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B136" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="137" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B137" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="138" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B138" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="139" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B139" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="140" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B140" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="141" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B141" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="142" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B142" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="143" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B143" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="144" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B144" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="145" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B145" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="146" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B146" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="147" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B147" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="148" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B148" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="149" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B149" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="150" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B150" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="151" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B151" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="152" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B152" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="153" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B153" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="154" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B154" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="155" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B155" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="D155" s="1" t="s">
         <v>348</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="156" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B156" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="D156" s="1" t="s">
         <v>350</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="157" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B157" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="D157" s="1" t="s">
         <v>352</v>
-      </c>
-      <c r="D157" s="1" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="158" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B158" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="D158" s="1" t="s">
         <v>354</v>
-      </c>
-      <c r="D158" s="1" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="159" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B159" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="D159" s="1" t="s">
         <v>356</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="160" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B160" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="161" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B161" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="162" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B162" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="163" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B163" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="164" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B164" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="165" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B165" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="166" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B166" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="167" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B167" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="168" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B168" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="D168" s="1" t="s">
         <v>605</v>
-      </c>
-      <c r="D168" s="1" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="169" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B169" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="D169" s="1" t="s">
         <v>607</v>
-      </c>
-      <c r="D169" s="1" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="170" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B170" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="171" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B171" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="D171" s="1" t="s">
         <v>610</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="172" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B172" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="173" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B173" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="174" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B174" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="D174" s="1" t="s">
         <v>613</v>
-      </c>
-      <c r="D174" s="1" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="175" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B175" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="176" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B176" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="D176" s="1" t="s">
         <v>616</v>
-      </c>
-      <c r="D176" s="1" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="177" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B177" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="178" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B178" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="179" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B179" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="D179" s="1" t="s">
         <v>620</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="180" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B180" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="D180" s="1" t="s">
         <v>622</v>
-      </c>
-      <c r="D180" s="1" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="181" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B181" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="182" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B182" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="183" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B183" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="184" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B184" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="185" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B185" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="186" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B186" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="187" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B187" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="188" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B188" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="189" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B189" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="190" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B190" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="191" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B191" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="192" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B192" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="193" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B193" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="194" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B194" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="195" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B195" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="196" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B196" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="197" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B197" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="198" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B198" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="199" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B199" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="200" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B200" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="201" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B201" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="202" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B202" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D202" s="1" t="s">
         <v>380</v>
-      </c>
-      <c r="D202" s="1" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="203" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B203" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="204" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B204" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="205" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B205" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="D205" s="1" t="s">
         <v>624</v>
-      </c>
-      <c r="D205" s="1" t="s">
-        <v>625</v>
       </c>
     </row>
     <row r="206" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B206" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="D206" s="1" t="s">
         <v>626</v>
-      </c>
-      <c r="D206" s="1" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="207" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B207" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="D207" s="1" t="s">
         <v>628</v>
-      </c>
-      <c r="D207" s="1" t="s">
-        <v>629</v>
       </c>
     </row>
   </sheetData>
@@ -18374,7 +18374,7 @@
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
@@ -18386,37 +18386,37 @@
         <v>29</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>188</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -18425,7 +18425,7 @@
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
@@ -18435,7 +18435,7 @@
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
@@ -18444,22 +18444,22 @@
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
@@ -18468,38 +18468,38 @@
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>192</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
@@ -18508,39 +18508,39 @@
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B29" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C29" s="3"/>
       <c r="D29" s="5"/>
@@ -18549,17 +18549,17 @@
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B30" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B33" s="3" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C33" s="3"/>
       <c r="D33" s="5"/>
@@ -18568,32 +18568,32 @@
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B35" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B36" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B37" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B38" s="1" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B40" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C40" s="3"/>
       <c r="D40" s="5"/>
@@ -18602,22 +18602,22 @@
     </row>
     <row r="41" spans="2:6" ht="27.6" x14ac:dyDescent="0.25">
       <c r="B41" s="385" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="42" spans="2:6" ht="27.6" x14ac:dyDescent="0.25">
       <c r="B42" s="385" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="43" spans="2:6" ht="27.6" x14ac:dyDescent="0.25">
       <c r="B43" s="385" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B45" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C45" s="5"/>
       <c r="D45" s="5"/>
@@ -18626,12 +18626,12 @@
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B46" s="12" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B47" s="12" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
   </sheetData>
@@ -18657,7 +18657,7 @@
   <sheetData>
     <row r="2" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C2" s="132"/>
       <c r="E2" s="106" t="s">
@@ -18666,159 +18666,159 @@
     </row>
     <row r="4" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B4" s="275" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C4" s="275" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="5" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C5" s="276" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="6" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B6" s="275" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C6" s="275" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="7" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C7" s="276" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="8" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B8" s="275" t="s">
+        <v>444</v>
+      </c>
+      <c r="C8" s="270" t="s">
         <v>445</v>
-      </c>
-      <c r="C8" s="270" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="9" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C9" s="276" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="10" spans="2:5" s="275" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="277" t="s">
+        <v>387</v>
+      </c>
+      <c r="C10" s="270" t="s">
         <v>388</v>
-      </c>
-      <c r="C10" s="270" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="11" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B11" s="270"/>
       <c r="C11" s="276" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="12" spans="2:5" s="275" customFormat="1" ht="22.8" x14ac:dyDescent="0.2">
       <c r="B12" s="278" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C12" s="275" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="13" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C13" s="276" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="14" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B14" s="275" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C14" s="275" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="15" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C15" s="276" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="16" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B16" s="278" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C16" s="275" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="17" spans="2:3" s="275" customFormat="1" ht="22.8" x14ac:dyDescent="0.2">
       <c r="C17" s="276" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="18" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B18" s="275" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C18" s="275" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="19" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C19" s="276" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="20" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B20" s="275" t="s">
+        <v>394</v>
+      </c>
+      <c r="C20" s="275" t="s">
         <v>395</v>
-      </c>
-      <c r="C20" s="275" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="21" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C21" s="276" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="22" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B22" s="275" t="s">
+        <v>424</v>
+      </c>
+      <c r="C22" s="275" t="s">
         <v>425</v>
-      </c>
-      <c r="C22" s="275" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="23" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C23" s="276" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="24" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B24" s="275" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C24" s="275" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="25" spans="2:3" s="275" customFormat="1" ht="22.8" x14ac:dyDescent="0.2">
       <c r="C25" s="276" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="26" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B26" s="275" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C26" s="275" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="27" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C27" s="269" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="28" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -18867,7 +18867,7 @@
   <sheetData>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="I2" s="106" t="s">
         <v>20</v>
@@ -18886,10 +18886,10 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C6" s="409" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="D6" s="410"/>
       <c r="E6" s="410"/>
@@ -18961,14 +18961,14 @@
       <c r="H12" s="55"/>
     </row>
     <row r="13" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="391" t="s">
+      <c r="A13" s="404" t="s">
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C13" s="406" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D13" s="407"/>
       <c r="E13" s="55"/>
@@ -18977,12 +18977,12 @@
       <c r="H13" s="55"/>
     </row>
     <row r="14" spans="1:9" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="391"/>
+      <c r="A14" s="404"/>
       <c r="B14" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C14" s="406" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="D14" s="407"/>
       <c r="E14" s="55"/>
@@ -19000,7 +19000,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C16" s="152">
         <v>25000</v>
@@ -19044,7 +19044,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B20" s="298" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C20" s="151">
         <v>2024</v>
@@ -19105,13 +19105,13 @@
         <v>34</v>
       </c>
       <c r="C27" s="153" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F27" s="274">
         <f>Grunddaten!G46</f>
@@ -19123,7 +19123,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B29" s="154" t="s">
-        <v>36</v>
+        <v>632</v>
       </c>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
@@ -19147,17 +19147,17 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B31" s="170" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F31" s="10"/>
       <c r="G31" s="10"/>
       <c r="I31" s="7"/>
       <c r="J31" s="146" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K31" s="8"/>
       <c r="L31" s="8"/>
@@ -19169,14 +19169,14 @@
         <v>11</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C32" s="171">
         <v>50</v>
       </c>
       <c r="D32" s="242"/>
       <c r="E32" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F32" s="172"/>
       <c r="G32" s="173"/>
@@ -19192,7 +19192,7 @@
     </row>
     <row r="33" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B33" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C33" s="10">
         <f>100-J32</f>
@@ -19332,7 +19332,7 @@
     </row>
     <row r="2" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C2" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D2" s="2"/>
       <c r="J2" s="7"/>
@@ -19353,7 +19353,7 @@
     </row>
     <row r="4" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C4" s="155" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D4" s="156"/>
       <c r="E4" s="156"/>
@@ -19383,7 +19383,7 @@
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C6" s="88" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D6" s="88"/>
       <c r="E6" s="161">
@@ -19409,23 +19409,23 @@
     </row>
     <row r="7" spans="2:18" s="91" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C7" s="162" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D7" s="162"/>
       <c r="E7" s="139" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F7" s="139" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G7" s="139" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H7" s="139" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I7" s="139" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J7" s="163"/>
       <c r="K7" s="164"/>
@@ -19439,23 +19439,23 @@
     </row>
     <row r="8" spans="2:18" s="91" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C8" s="162" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D8" s="162"/>
       <c r="E8" s="139" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F8" s="139" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G8" s="139" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H8" s="139" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I8" s="139" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J8" s="163"/>
       <c r="K8" s="235"/>
@@ -19472,23 +19472,23 @@
     </row>
     <row r="9" spans="2:18" s="91" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C9" s="162" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D9" s="162"/>
       <c r="E9" s="140" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" s="140" t="s">
         <v>54</v>
       </c>
-      <c r="F9" s="140" t="s">
+      <c r="G9" s="140" t="s">
         <v>55</v>
       </c>
-      <c r="G9" s="140" t="s">
+      <c r="H9" s="140" t="s">
         <v>56</v>
       </c>
-      <c r="H9" s="140" t="s">
+      <c r="I9" s="140" t="s">
         <v>57</v>
-      </c>
-      <c r="I9" s="140" t="s">
-        <v>58</v>
       </c>
       <c r="J9" s="238"/>
       <c r="K9" s="236"/>
@@ -19502,28 +19502,28 @@
     </row>
     <row r="10" spans="2:18" s="91" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C10" s="162" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D10" s="162"/>
       <c r="E10" s="140" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="F10" s="140" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="G10" s="140" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H10" s="140" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="I10" s="140" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J10" s="238"/>
       <c r="K10" s="236"/>
       <c r="L10" s="432" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="M10" s="432"/>
       <c r="N10" s="236"/>
@@ -19534,27 +19534,27 @@
     </row>
     <row r="11" spans="2:18" s="91" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C11" s="162" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D11" s="162"/>
       <c r="E11" s="141" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="F11" s="141" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="G11" s="141" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H11" s="141" t="s">
+        <v>548</v>
+      </c>
+      <c r="I11" s="141" t="s">
         <v>549</v>
-      </c>
-      <c r="I11" s="141" t="s">
-        <v>550</v>
       </c>
       <c r="J11" s="238"/>
       <c r="K11" s="434" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L11" s="434"/>
       <c r="M11" s="434"/>
@@ -19566,27 +19566,27 @@
     </row>
     <row r="12" spans="2:18" s="91" customFormat="1" ht="55.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C12" s="165" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D12" s="88"/>
       <c r="E12" s="141" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="F12" s="141" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="G12" s="141" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H12" s="141" t="s">
+        <v>550</v>
+      </c>
+      <c r="I12" s="141" t="s">
         <v>551</v>
-      </c>
-      <c r="I12" s="141" t="s">
-        <v>552</v>
       </c>
       <c r="J12" s="164"/>
       <c r="K12" s="433" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L12" s="433"/>
       <c r="M12" s="433"/>
@@ -19598,23 +19598,23 @@
     </row>
     <row r="13" spans="2:18" s="91" customFormat="1" ht="55.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C13" s="165" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D13" s="384"/>
       <c r="E13" s="139" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="F13" s="139" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="G13" s="139" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H13" s="139" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="I13" s="139" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="J13" s="164"/>
       <c r="K13" s="366"/>
@@ -19662,10 +19662,10 @@
     </row>
     <row r="15" spans="2:18" s="91" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C15" s="162" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15" s="263" t="s">
         <v>65</v>
-      </c>
-      <c r="D15" s="263" t="s">
-        <v>66</v>
       </c>
       <c r="E15" s="361"/>
       <c r="F15" s="364"/>
@@ -19673,7 +19673,7 @@
       <c r="H15" s="361"/>
       <c r="I15" s="361"/>
       <c r="J15" s="264" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K15" s="164"/>
       <c r="L15" s="164"/>
@@ -19686,13 +19686,13 @@
     </row>
     <row r="16" spans="2:18" s="91" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="431" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16" s="429" t="s">
         <v>68</v>
       </c>
-      <c r="C16" s="429" t="s">
+      <c r="D16" s="359" t="s">
         <v>69</v>
-      </c>
-      <c r="D16" s="359" t="s">
-        <v>70</v>
       </c>
       <c r="E16" s="365">
         <v>4.9000000000000004</v>
@@ -19718,7 +19718,7 @@
       <c r="B17" s="431"/>
       <c r="C17" s="430"/>
       <c r="D17" s="166" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E17" s="357"/>
       <c r="F17" s="257"/>
@@ -19742,10 +19742,10 @@
     <row r="18" spans="2:18" s="91" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="431"/>
       <c r="C18" s="162" t="s">
+        <v>71</v>
+      </c>
+      <c r="D18" s="166" t="s">
         <v>72</v>
-      </c>
-      <c r="D18" s="166" t="s">
-        <v>73</v>
       </c>
       <c r="E18" s="258">
         <v>130</v>
@@ -19771,10 +19771,10 @@
     <row r="19" spans="2:18" s="91" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="431"/>
       <c r="C19" s="162" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19" s="166" t="s">
         <v>74</v>
-      </c>
-      <c r="D19" s="166" t="s">
-        <v>75</v>
       </c>
       <c r="E19" s="258">
         <v>58.6</v>
@@ -19803,10 +19803,10 @@
     <row r="20" spans="2:18" s="91" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="431"/>
       <c r="C20" s="162" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D20" s="166" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E20" s="258">
         <v>0.42</v>
@@ -19832,10 +19832,10 @@
     <row r="21" spans="2:18" s="91" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="431"/>
       <c r="C21" s="162" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" s="166" t="s">
         <v>77</v>
-      </c>
-      <c r="D21" s="166" t="s">
-        <v>78</v>
       </c>
       <c r="E21" s="260"/>
       <c r="F21" s="261"/>
@@ -19854,10 +19854,10 @@
     </row>
     <row r="22" spans="2:18" s="91" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C22" s="162" t="s">
+        <v>78</v>
+      </c>
+      <c r="D22" s="168" t="s">
         <v>79</v>
-      </c>
-      <c r="D22" s="168" t="s">
-        <v>80</v>
       </c>
       <c r="E22" s="257"/>
       <c r="F22" s="257"/>
@@ -19880,7 +19880,7 @@
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D23" s="228" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E23" s="389">
         <f>IF(AND(OR(Energie1="nicht verfügbar",COUNTIF(EnList1,Energie1)&lt;&gt;1),Antriebsart1&lt;&gt;0),1,0)</f>
@@ -19913,7 +19913,7 @@
     </row>
     <row r="24" spans="2:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C24" s="77" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D24" s="228"/>
       <c r="E24" s="389"/>
@@ -19928,14 +19928,14 @@
       <c r="R24" s="7"/>
     </row>
     <row r="25" spans="2:18" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="391" t="s">
+      <c r="B25" s="404" t="s">
         <v>11</v>
       </c>
       <c r="C25" s="331" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D25" s="322" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E25" s="256">
         <v>160</v>
@@ -19959,10 +19959,10 @@
       <c r="R25" s="7"/>
     </row>
     <row r="26" spans="2:18" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="391"/>
+      <c r="B26" s="404"/>
       <c r="C26" s="331"/>
       <c r="D26" s="322" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E26" s="256"/>
       <c r="F26" s="256"/>
@@ -19976,10 +19976,10 @@
       <c r="R26" s="7"/>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B27" s="391"/>
+      <c r="B27" s="404"/>
       <c r="C27" s="335"/>
       <c r="D27" s="322" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E27" s="256"/>
       <c r="F27" s="256"/>
@@ -19994,7 +19994,7 @@
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D28" s="228" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E28" s="389">
         <f>IF(OR(AND(COUNT(E16:E22)&lt;7,Antriebsart1="Plug-In-Hybrid (PHEV)"),AND(COUNT(E17,E22)&lt;2,Antriebsart1="Vollelektrisch (BEV)"),AND(COUNT(E16,E18:E20)&lt;4,Antriebsart1="Verbrenner")),1,0)</f>
@@ -20027,7 +20027,7 @@
     </row>
     <row r="29" spans="2:18" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E29" s="426" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F29" s="427"/>
       <c r="G29" s="427"/>
@@ -20036,7 +20036,7 @@
     </row>
     <row r="30" spans="2:18" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E30" s="421" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F30" s="408"/>
       <c r="G30" s="408"/>
@@ -20052,7 +20052,7 @@
     </row>
     <row r="33" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C33" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
   </sheetData>
@@ -20445,7 +20445,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B1" s="118" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C1" s="118"/>
       <c r="D1" s="118"/>
@@ -20459,7 +20459,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="65" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C2" s="227"/>
       <c r="D2" s="230" t="str">
@@ -20487,7 +20487,7 @@
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="18"/>
       <c r="B4" s="154" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -20502,7 +20502,7 @@
     <row r="6" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="18"/>
       <c r="B6" s="12" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C6" s="439" t="str">
         <f>IF(Projektname=0,"",Projektname)</f>
@@ -20584,7 +20584,7 @@
       <c r="B12" s="12"/>
       <c r="C12" s="76"/>
       <c r="E12" s="58" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F12" s="85">
         <f>Fahrleistung</f>
@@ -20624,7 +20624,7 @@
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="18"/>
       <c r="B15" s="293" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C15" s="21"/>
       <c r="D15" s="21"/>
@@ -20636,7 +20636,7 @@
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="18"/>
       <c r="B16" s="37" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C16" s="23"/>
       <c r="D16" s="24">
@@ -20683,10 +20683,10 @@
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="18"/>
       <c r="B18" s="177" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C18" s="178" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" s="179">
         <f>IF(FinArt="Kauf",Gesamtpreis1,"")</f>
@@ -20719,7 +20719,7 @@
         <v>Wertminderung</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D19" s="41">
         <f>Erg.Fzg._1!$C$54+Erg.Fzg._1!$C$55</f>
@@ -20745,10 +20745,10 @@
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="336"/>
       <c r="B20" s="45" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D20" s="41">
         <f>Erg.Fzg._1!$C$56</f>
@@ -20776,10 +20776,10 @@
         <v>11</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D21" s="43">
         <f>Erg.Fzg._1!$C$57</f>
@@ -20805,10 +20805,10 @@
     <row r="22" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="437"/>
       <c r="B22" s="27" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C22" s="28" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D22" s="43">
         <f>Erg.Fzg._1!C41*Haltedauer</f>
@@ -20835,10 +20835,10 @@
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="438"/>
       <c r="B23" s="45" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C23" s="325" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D23" s="326">
         <f>Erg.Fzg._1!$C$59</f>
@@ -20960,10 +20960,10 @@
     <row r="27" spans="1:9" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="18"/>
       <c r="B27" s="49" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C27" s="50" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D27" s="51">
         <f>IF(SUM(D19:D26)=0,"",SUM(D19:D26))</f>
@@ -20989,7 +20989,7 @@
     <row r="28" spans="1:9" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="18"/>
       <c r="B28" s="75" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C28" s="50"/>
       <c r="D28" s="51">
@@ -21017,10 +21017,10 @@
     <row r="29" spans="1:9" ht="20.399999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A29" s="18"/>
       <c r="B29" s="108" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C29" s="66" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D29" s="231">
         <f>IF(AND(COUNTIF(D19:D23,0)&gt;0,Antriebsart1="Plug-In-Hybrid (PHEV)"),1,IF(AND(COUNTIF(D19:D23,0)&gt;1,Antriebsart1&lt;&gt;0),1,0))</f>
@@ -21050,10 +21050,10 @@
     <row r="30" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="33"/>
       <c r="B30" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="C30" s="316" t="s">
         <v>95</v>
-      </c>
-      <c r="C30" s="316" t="s">
-        <v>96</v>
       </c>
       <c r="D30" s="314">
         <f>Erg.Fzg._1!$C$65</f>
@@ -21079,10 +21079,10 @@
     <row r="31" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="309"/>
       <c r="B31" s="98" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C31" s="317" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D31" s="318">
         <f>Erg.Fzg._1!$C$66</f>
@@ -21109,10 +21109,10 @@
     <row r="32" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="309"/>
       <c r="B32" s="310" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C32" s="311" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D32" s="312">
         <f>SUM(D30:D31)</f>
@@ -21138,7 +21138,7 @@
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B34" s="293" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C34" s="21"/>
       <c r="D34" s="21"/>
@@ -21269,7 +21269,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B1" s="118" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C1" s="118"/>
       <c r="D1" s="118"/>
@@ -21283,7 +21283,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="65" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C2" s="227"/>
       <c r="D2" s="230" t="str">
@@ -21311,7 +21311,7 @@
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="18"/>
       <c r="B4" s="154" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -21326,7 +21326,7 @@
     <row r="6" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="18"/>
       <c r="B6" s="12" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C6" s="439" t="str">
         <f>IF(Projektname=0,"",Projektname)</f>
@@ -21408,7 +21408,7 @@
       <c r="B12" s="12"/>
       <c r="C12" s="76"/>
       <c r="E12" s="58" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F12" s="85">
         <f>Fahrleistung</f>
@@ -21448,7 +21448,7 @@
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="18"/>
       <c r="B15" s="293" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C15" s="21"/>
       <c r="D15" s="21"/>
@@ -21460,7 +21460,7 @@
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="18"/>
       <c r="B16" s="37" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C16" s="23"/>
       <c r="D16" s="24">
@@ -21509,10 +21509,10 @@
         <v>11</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" s="43">
         <f>Erg.Fzg._1!$C$57-D19</f>
@@ -21538,10 +21538,10 @@
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="437"/>
       <c r="B19" s="27" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C19" s="28" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D19" s="43">
         <f>(Erg.Fzg._1!$C$35+Erg.Fzg._1!$C$36)*Haltedauer</f>
@@ -21567,10 +21567,10 @@
     <row r="20" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="437"/>
       <c r="B20" s="27" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C20" s="28" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D20" s="43">
         <f>Erg.Fzg._1!C41*Haltedauer</f>
@@ -21597,10 +21597,10 @@
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="437"/>
       <c r="B21" s="29" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C21" s="46" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D21" s="47">
         <f>Erg.Fzg._1!$C$59</f>
@@ -21626,10 +21626,10 @@
     <row r="22" spans="1:9" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="18"/>
       <c r="B22" s="49" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C22" s="50" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D22" s="51">
         <f>IF(SUM(D18:D21)=0,"",SUM(D18:D21))</f>
@@ -21655,7 +21655,7 @@
     <row r="23" spans="1:9" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="18"/>
       <c r="B23" s="75" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C23" s="50"/>
       <c r="D23" s="51">
@@ -21683,10 +21683,10 @@
     <row r="24" spans="1:9" ht="20.399999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A24" s="18"/>
       <c r="B24" s="108" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C24" s="66" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D24" s="231">
         <f>IF(AND(COUNTIF(D18:D21,0)&gt;0,Antriebsart1="Plug-In-Hybrid (PHEV)"),1,IF(AND(COUNTIF(D18:D21,0)&gt;1,Antriebsart1="Verbrenner"),1,IF(AND(COUNTIF(D18:D21,0)&gt;2,Antriebsart1&lt;&gt;""),1,0)))</f>
@@ -21716,10 +21716,10 @@
     <row r="25" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="33"/>
       <c r="B25" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="C25" s="31" t="s">
         <v>95</v>
-      </c>
-      <c r="C25" s="31" t="s">
-        <v>96</v>
       </c>
       <c r="D25" s="32">
         <f>Erg.Fzg._1!$C$65</f>
@@ -21745,10 +21745,10 @@
     <row r="26" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="33"/>
       <c r="B26" s="98" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C26" s="99" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D26" s="35">
         <f>Erg.Fzg._1!$C$66</f>
@@ -21775,10 +21775,10 @@
     <row r="27" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="33"/>
       <c r="B27" s="310" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C27" s="311" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D27" s="312">
         <f>SUM(D25:D26)</f>
@@ -21804,7 +21804,7 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B29" s="293" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C29" s="21"/>
       <c r="D29" s="21"/>
@@ -21943,7 +21943,7 @@
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="119"/>
       <c r="B2" s="189" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C2" s="119"/>
       <c r="D2" s="119"/>
@@ -21972,7 +21972,7 @@
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="119"/>
       <c r="B4" s="293" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C4" s="354"/>
       <c r="D4" s="354"/>
@@ -21984,7 +21984,7 @@
       <c r="J4" s="119"/>
     </row>
     <row r="5" spans="1:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="391" t="s">
+      <c r="A5" s="404" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="219"/>
@@ -21996,448 +21996,448 @@
       <c r="H5" s="219"/>
       <c r="I5" s="190"/>
       <c r="J5" s="119"/>
-      <c r="L5" s="467" t="s">
-        <v>408</v>
-      </c>
-      <c r="M5" s="467"/>
-      <c r="N5" s="467"/>
+      <c r="L5" s="448" t="s">
+        <v>407</v>
+      </c>
+      <c r="M5" s="448"/>
+      <c r="N5" s="448"/>
     </row>
     <row r="6" spans="1:14" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A6" s="391"/>
+      <c r="A6" s="404"/>
       <c r="B6" s="220" t="s">
+        <v>101</v>
+      </c>
+      <c r="C6" s="220" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="221" t="s">
+        <v>519</v>
+      </c>
+      <c r="E6" s="221" t="s">
+        <v>520</v>
+      </c>
+      <c r="F6" s="221" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="220" t="s">
-        <v>45</v>
-      </c>
-      <c r="D6" s="221" t="s">
-        <v>520</v>
-      </c>
-      <c r="E6" s="221" t="s">
-        <v>521</v>
-      </c>
-      <c r="F6" s="221" t="s">
+      <c r="G6" s="226" t="s">
         <v>103</v>
       </c>
-      <c r="G6" s="226" t="s">
+      <c r="H6" s="221" t="s">
         <v>104</v>
       </c>
-      <c r="H6" s="221" t="s">
+      <c r="I6" s="306" t="s">
         <v>105</v>
       </c>
-      <c r="I6" s="306" t="s">
-        <v>106</v>
-      </c>
       <c r="J6" s="119"/>
-      <c r="L6" s="467"/>
-      <c r="M6" s="467"/>
-      <c r="N6" s="467"/>
+      <c r="L6" s="448"/>
+      <c r="M6" s="448"/>
+      <c r="N6" s="448"/>
     </row>
     <row r="7" spans="1:14" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A7" s="352"/>
-      <c r="B7" s="454" t="s">
-        <v>107</v>
-      </c>
-      <c r="C7" s="460" t="s">
-        <v>47</v>
+      <c r="B7" s="449" t="s">
+        <v>106</v>
+      </c>
+      <c r="C7" s="452" t="s">
+        <v>46</v>
       </c>
       <c r="D7" s="370" t="s">
+        <v>521</v>
+      </c>
+      <c r="E7" s="386" t="s">
         <v>522</v>
-      </c>
-      <c r="E7" s="386" t="s">
-        <v>523</v>
       </c>
       <c r="F7" s="223">
         <v>230</v>
       </c>
       <c r="G7" s="272"/>
       <c r="H7" s="222" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I7" s="307">
         <f t="shared" ref="I7:I25" si="0">IF(ISBLANK(G7),F7,G7)</f>
         <v>230</v>
       </c>
       <c r="J7" s="119"/>
-      <c r="L7" s="467"/>
-      <c r="M7" s="467"/>
-      <c r="N7" s="467"/>
+      <c r="L7" s="448"/>
+      <c r="M7" s="448"/>
+      <c r="N7" s="448"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="352"/>
-      <c r="B8" s="455"/>
-      <c r="C8" s="461"/>
-      <c r="D8" s="458" t="s">
-        <v>524</v>
+      <c r="B8" s="450"/>
+      <c r="C8" s="453"/>
+      <c r="D8" s="455" t="s">
+        <v>523</v>
       </c>
       <c r="E8" s="387" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="F8" s="223">
         <v>150</v>
       </c>
       <c r="G8" s="272"/>
       <c r="H8" s="222" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I8" s="307">
         <f t="shared" si="0"/>
         <v>150</v>
       </c>
       <c r="J8" s="119"/>
-      <c r="L8" s="467"/>
-      <c r="M8" s="467"/>
-      <c r="N8" s="467"/>
+      <c r="L8" s="448"/>
+      <c r="M8" s="448"/>
+      <c r="N8" s="448"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="352"/>
-      <c r="B9" s="455"/>
-      <c r="C9" s="461"/>
-      <c r="D9" s="458"/>
+      <c r="B9" s="450"/>
+      <c r="C9" s="453"/>
+      <c r="D9" s="455"/>
       <c r="E9" s="386" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="F9" s="223">
         <v>160</v>
       </c>
       <c r="G9" s="272"/>
       <c r="H9" s="222" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I9" s="307">
         <f t="shared" si="0"/>
         <v>160</v>
       </c>
       <c r="J9" s="119"/>
-      <c r="L9" s="467"/>
-      <c r="M9" s="467"/>
-      <c r="N9" s="467"/>
+      <c r="L9" s="448"/>
+      <c r="M9" s="448"/>
+      <c r="N9" s="448"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="352"/>
-      <c r="B10" s="455"/>
-      <c r="C10" s="461"/>
-      <c r="D10" s="458"/>
+      <c r="B10" s="450"/>
+      <c r="C10" s="453"/>
+      <c r="D10" s="455"/>
       <c r="E10" s="387" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="F10" s="223">
         <v>190</v>
       </c>
       <c r="G10" s="272"/>
       <c r="H10" s="222" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I10" s="307">
         <f t="shared" si="0"/>
         <v>190</v>
       </c>
       <c r="J10" s="119"/>
-      <c r="L10" s="467"/>
-      <c r="M10" s="467"/>
-      <c r="N10" s="467"/>
+      <c r="L10" s="448"/>
+      <c r="M10" s="448"/>
+      <c r="N10" s="448"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="352"/>
-      <c r="B11" s="455"/>
-      <c r="C11" s="462"/>
-      <c r="D11" s="459"/>
+      <c r="B11" s="450"/>
+      <c r="C11" s="454"/>
+      <c r="D11" s="456"/>
       <c r="E11" s="386" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="F11" s="223">
         <v>210</v>
       </c>
       <c r="G11" s="272"/>
       <c r="H11" s="222" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I11" s="307">
         <f t="shared" si="0"/>
         <v>210</v>
       </c>
       <c r="J11" s="119"/>
-      <c r="L11" s="467"/>
-      <c r="M11" s="467"/>
-      <c r="N11" s="467"/>
+      <c r="L11" s="448"/>
+      <c r="M11" s="448"/>
+      <c r="N11" s="448"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="352"/>
-      <c r="B12" s="456"/>
+      <c r="B12" s="451"/>
       <c r="C12" s="222" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D12" s="223" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E12" s="386" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F12" s="223">
         <v>40</v>
       </c>
       <c r="G12" s="272"/>
       <c r="H12" s="222" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I12" s="307">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="J12" s="119"/>
-      <c r="L12" s="467"/>
-      <c r="M12" s="467"/>
-      <c r="N12" s="467"/>
+      <c r="L12" s="448"/>
+      <c r="M12" s="448"/>
+      <c r="N12" s="448"/>
     </row>
     <row r="13" spans="1:14" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A13" s="352"/>
-      <c r="B13" s="454" t="s">
+      <c r="B13" s="449" t="s">
+        <v>111</v>
+      </c>
+      <c r="C13" s="452" t="s">
         <v>112</v>
       </c>
-      <c r="C13" s="460" t="s">
-        <v>113</v>
-      </c>
       <c r="D13" s="371" t="s">
+        <v>521</v>
+      </c>
+      <c r="E13" s="386" t="s">
         <v>522</v>
-      </c>
-      <c r="E13" s="386" t="s">
-        <v>523</v>
       </c>
       <c r="F13" s="223">
         <v>32</v>
       </c>
       <c r="G13" s="272"/>
       <c r="H13" s="222" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I13" s="307">
         <f>IF(ISBLANK(G13),F13,G13)</f>
         <v>32</v>
       </c>
       <c r="J13" s="119"/>
-      <c r="L13" s="467"/>
-      <c r="M13" s="467"/>
-      <c r="N13" s="467"/>
+      <c r="L13" s="448"/>
+      <c r="M13" s="448"/>
+      <c r="N13" s="448"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="352"/>
-      <c r="B14" s="455"/>
-      <c r="C14" s="461"/>
-      <c r="D14" s="457" t="s">
-        <v>524</v>
+      <c r="B14" s="450"/>
+      <c r="C14" s="453"/>
+      <c r="D14" s="463" t="s">
+        <v>523</v>
       </c>
       <c r="E14" s="386" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="F14" s="223">
         <v>20</v>
       </c>
       <c r="G14" s="272"/>
       <c r="H14" s="222" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I14" s="307">
         <f>IF(ISBLANK(G14),F14,G14)</f>
         <v>20</v>
       </c>
       <c r="J14" s="119"/>
-      <c r="L14" s="467"/>
-      <c r="M14" s="467"/>
-      <c r="N14" s="467"/>
+      <c r="L14" s="448"/>
+      <c r="M14" s="448"/>
+      <c r="N14" s="448"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="352"/>
-      <c r="B15" s="455"/>
-      <c r="C15" s="461"/>
-      <c r="D15" s="458"/>
+      <c r="B15" s="450"/>
+      <c r="C15" s="453"/>
+      <c r="D15" s="455"/>
       <c r="E15" s="386" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="F15" s="223">
         <v>28</v>
       </c>
       <c r="G15" s="272"/>
       <c r="H15" s="222" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I15" s="307">
         <f t="shared" ref="I15:I16" si="1">IF(ISBLANK(G15),F15,G15)</f>
         <v>28</v>
       </c>
       <c r="J15" s="119"/>
-      <c r="L15" s="467"/>
-      <c r="M15" s="467"/>
-      <c r="N15" s="467"/>
+      <c r="L15" s="448"/>
+      <c r="M15" s="448"/>
+      <c r="N15" s="448"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="352"/>
-      <c r="B16" s="455"/>
-      <c r="C16" s="462"/>
-      <c r="D16" s="459"/>
+      <c r="B16" s="450"/>
+      <c r="C16" s="454"/>
+      <c r="D16" s="456"/>
       <c r="E16" s="386" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="F16" s="223">
         <v>32</v>
       </c>
       <c r="G16" s="272"/>
       <c r="H16" s="222" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I16" s="307">
         <f t="shared" si="1"/>
         <v>32</v>
       </c>
       <c r="J16" s="119"/>
-      <c r="L16" s="467"/>
-      <c r="M16" s="467"/>
-      <c r="N16" s="467"/>
+      <c r="L16" s="448"/>
+      <c r="M16" s="448"/>
+      <c r="N16" s="448"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="437" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="455"/>
+      <c r="B17" s="450"/>
       <c r="C17" s="222" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D17" s="223" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E17" s="223" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F17" s="223" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="G17" s="272"/>
       <c r="H17" s="222" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I17" s="307" t="str">
         <f>IF(ISBLANK(G17),"keine",G17)</f>
         <v>keine</v>
       </c>
       <c r="J17" s="119"/>
-      <c r="L17" s="467"/>
-      <c r="M17" s="467"/>
-      <c r="N17" s="467"/>
+      <c r="L17" s="448"/>
+      <c r="M17" s="448"/>
+      <c r="N17" s="448"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="437"/>
-      <c r="B18" s="455"/>
+      <c r="B18" s="450"/>
       <c r="C18" s="222" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D18" s="223" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E18" s="223" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F18" s="223" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="G18" s="272"/>
       <c r="H18" s="222" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I18" s="307" t="str">
         <f>IF(ISBLANK(G18),"keine",G18)</f>
         <v>keine</v>
       </c>
       <c r="J18" s="119"/>
-      <c r="L18" s="467"/>
-      <c r="M18" s="467"/>
-      <c r="N18" s="467"/>
+      <c r="L18" s="448"/>
+      <c r="M18" s="448"/>
+      <c r="N18" s="448"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="437"/>
-      <c r="B19" s="456"/>
+      <c r="B19" s="451"/>
       <c r="C19" s="222" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="D19" s="223" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E19" s="223" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F19" s="223" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="G19" s="272"/>
       <c r="H19" s="222" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I19" s="307" t="str">
         <f>IF(ISBLANK(G19),"keine",G19)</f>
         <v>keine</v>
       </c>
       <c r="J19" s="119"/>
-      <c r="L19" s="467"/>
-      <c r="M19" s="467"/>
-      <c r="N19" s="467"/>
+      <c r="L19" s="448"/>
+      <c r="M19" s="448"/>
+      <c r="N19" s="448"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="352"/>
       <c r="B20" s="378"/>
       <c r="C20" s="380"/>
-      <c r="D20" s="463" t="s">
-        <v>528</v>
-      </c>
-      <c r="E20" s="464"/>
+      <c r="D20" s="464" t="s">
+        <v>527</v>
+      </c>
+      <c r="E20" s="465"/>
       <c r="F20" s="381"/>
       <c r="G20" s="382"/>
       <c r="H20" s="379"/>
       <c r="I20" s="307"/>
       <c r="J20" s="119"/>
-      <c r="L20" s="467"/>
-      <c r="M20" s="467"/>
-      <c r="N20" s="467"/>
+      <c r="L20" s="448"/>
+      <c r="M20" s="448"/>
+      <c r="N20" s="448"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="352"/>
-      <c r="B21" s="454" t="s">
+      <c r="B21" s="449" t="s">
+        <v>108</v>
+      </c>
+      <c r="C21" s="452" t="s">
         <v>109</v>
       </c>
-      <c r="C21" s="460" t="s">
-        <v>110</v>
-      </c>
-      <c r="D21" s="465" t="s">
-        <v>525</v>
-      </c>
-      <c r="E21" s="466"/>
+      <c r="D21" s="466" t="s">
+        <v>524</v>
+      </c>
+      <c r="E21" s="467"/>
       <c r="F21" s="386">
         <v>64</v>
       </c>
       <c r="G21" s="272"/>
       <c r="H21" s="222" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I21" s="307">
         <f>IF(ISBLANK(G21),F21,G21)</f>
         <v>64</v>
       </c>
       <c r="J21" s="119"/>
-      <c r="L21" s="467"/>
-      <c r="M21" s="467"/>
-      <c r="N21" s="467"/>
+      <c r="L21" s="448"/>
+      <c r="M21" s="448"/>
+      <c r="N21" s="448"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="352"/>
-      <c r="B22" s="455"/>
-      <c r="C22" s="461"/>
-      <c r="D22" s="465" t="s">
-        <v>526</v>
-      </c>
-      <c r="E22" s="466"/>
+      <c r="B22" s="450"/>
+      <c r="C22" s="453"/>
+      <c r="D22" s="466" t="s">
+        <v>525</v>
+      </c>
+      <c r="E22" s="467"/>
       <c r="F22" s="386">
         <v>84</v>
       </c>
       <c r="G22" s="272"/>
       <c r="H22" s="222" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I22" s="307">
         <f t="shared" ref="I22:I23" si="2">IF(ISBLANK(G22),F22,G22)</f>
@@ -22445,91 +22445,91 @@
       </c>
       <c r="J22" s="119"/>
       <c r="K22" s="383"/>
-      <c r="L22" s="467"/>
-      <c r="M22" s="467"/>
-      <c r="N22" s="467"/>
+      <c r="L22" s="448"/>
+      <c r="M22" s="448"/>
+      <c r="N22" s="448"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="352"/>
-      <c r="B23" s="456"/>
-      <c r="C23" s="462"/>
-      <c r="D23" s="465" t="s">
-        <v>527</v>
-      </c>
-      <c r="E23" s="466"/>
+      <c r="B23" s="451"/>
+      <c r="C23" s="454"/>
+      <c r="D23" s="466" t="s">
+        <v>526</v>
+      </c>
+      <c r="E23" s="467"/>
       <c r="F23" s="386">
         <v>100</v>
       </c>
       <c r="G23" s="272"/>
       <c r="H23" s="222" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I23" s="307">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
       <c r="J23" s="119"/>
-      <c r="L23" s="467"/>
-      <c r="M23" s="467"/>
-      <c r="N23" s="467"/>
+      <c r="L23" s="448"/>
+      <c r="M23" s="448"/>
+      <c r="N23" s="448"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="352"/>
       <c r="B24" s="367" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C24" s="369" t="s">
-        <v>110</v>
-      </c>
-      <c r="D24" s="465" t="s">
-        <v>529</v>
-      </c>
-      <c r="E24" s="466"/>
+        <v>109</v>
+      </c>
+      <c r="D24" s="466" t="s">
+        <v>528</v>
+      </c>
+      <c r="E24" s="467"/>
       <c r="F24" s="388">
         <v>3.6</v>
       </c>
       <c r="G24" s="272"/>
       <c r="H24" s="222" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I24" s="307">
         <f>IF(ISBLANK(G24),F24,G24)</f>
         <v>3.6</v>
       </c>
       <c r="J24" s="119"/>
-      <c r="L24" s="467"/>
-      <c r="M24" s="467"/>
-      <c r="N24" s="467"/>
+      <c r="L24" s="448"/>
+      <c r="M24" s="448"/>
+      <c r="N24" s="448"/>
     </row>
     <row r="25" spans="1:14" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A25" s="353"/>
       <c r="B25" s="356" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C25" s="225" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D25" s="223" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E25" s="223" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F25" s="224">
         <v>60</v>
       </c>
       <c r="G25" s="273"/>
       <c r="H25" s="225" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I25" s="307">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
       <c r="J25" s="191"/>
-      <c r="L25" s="467"/>
-      <c r="M25" s="467"/>
-      <c r="N25" s="467"/>
+      <c r="L25" s="448"/>
+      <c r="M25" s="448"/>
+      <c r="N25" s="448"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="119"/>
@@ -22558,13 +22558,13 @@
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="193"/>
       <c r="B29" s="192" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C29" s="192"/>
       <c r="D29" s="192"/>
       <c r="E29" s="192"/>
       <c r="F29" s="193" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G29" s="193"/>
       <c r="H29" s="193"/>
@@ -22588,7 +22588,7 @@
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="196"/>
       <c r="B31" s="293" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C31" s="339"/>
       <c r="D31" s="339"/>
@@ -22616,17 +22616,17 @@
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="196"/>
       <c r="B33" s="346" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C33" s="327"/>
       <c r="D33" s="327"/>
       <c r="E33" s="327"/>
       <c r="F33" s="296" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G33" s="347"/>
       <c r="H33" s="295" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I33" s="194"/>
       <c r="J33" s="195"/>
@@ -22640,23 +22640,23 @@
       <c r="E34" s="327"/>
       <c r="F34" s="209"/>
       <c r="G34" s="210" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H34" s="294"/>
       <c r="I34" s="308" t="s">
+        <v>118</v>
+      </c>
+      <c r="J34" s="198" t="s">
         <v>119</v>
       </c>
-      <c r="J34" s="198" t="s">
+      <c r="K34" s="255" t="s">
         <v>120</v>
-      </c>
-      <c r="K34" s="255" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35" s="204"/>
       <c r="B35" s="212" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C35" s="372"/>
       <c r="D35" s="375"/>
@@ -22666,21 +22666,21 @@
       </c>
       <c r="G35" s="243"/>
       <c r="H35" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I35" s="308">
         <f>IF(ISNUMBER(G35),G35,F35)/100</f>
         <v>0.41399999999999998</v>
       </c>
       <c r="J35" s="199" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="K35" s="254"/>
     </row>
     <row r="36" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" s="204"/>
       <c r="B36" s="215" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C36" s="373"/>
       <c r="D36" s="376"/>
@@ -22690,21 +22690,21 @@
       </c>
       <c r="G36" s="243"/>
       <c r="H36" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I36" s="308">
         <f>IF(ISNUMBER(G36),G36,F36)/100</f>
         <v>0.59</v>
       </c>
       <c r="J36" s="199" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K36" s="254"/>
     </row>
     <row r="37" spans="1:11" ht="14.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="205"/>
       <c r="B37" s="216" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C37" s="374"/>
       <c r="D37" s="377"/>
@@ -22720,9 +22720,9 @@
       <c r="K37" s="254"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="450"/>
+      <c r="A38" s="459"/>
       <c r="B38" s="212" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C38" s="372"/>
       <c r="D38" s="375"/>
@@ -22732,21 +22732,21 @@
       </c>
       <c r="G38" s="243"/>
       <c r="H38" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I38" s="308">
         <f t="shared" ref="I38:I40" si="3">IF(ISNUMBER(G38),G38,F38)</f>
         <v>1.6719999999999999</v>
       </c>
       <c r="J38" s="199" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="K38" s="254"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="450"/>
+      <c r="A39" s="459"/>
       <c r="B39" s="212" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C39" s="372"/>
       <c r="D39" s="375"/>
@@ -22756,21 +22756,21 @@
       </c>
       <c r="G39" s="243"/>
       <c r="H39" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I39" s="308">
         <f t="shared" si="3"/>
         <v>1.788</v>
       </c>
       <c r="J39" s="199" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="K39" s="254"/>
     </row>
     <row r="40" spans="1:11" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A40" s="205"/>
       <c r="B40" s="212" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C40" s="372"/>
       <c r="D40" s="375"/>
@@ -22780,14 +22780,14 @@
       </c>
       <c r="G40" s="243"/>
       <c r="H40" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I40" s="308">
         <f t="shared" si="3"/>
         <v>1.3</v>
       </c>
       <c r="J40" s="199" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="K40" s="254"/>
     </row>
@@ -22820,7 +22820,7 @@
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="193"/>
       <c r="B43" s="293" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C43" s="339"/>
       <c r="D43" s="339"/>
@@ -22834,17 +22834,17 @@
     </row>
     <row r="44" spans="1:11" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="193"/>
-      <c r="B44" s="451" t="s">
-        <v>129</v>
-      </c>
-      <c r="C44" s="452"/>
-      <c r="D44" s="452"/>
-      <c r="E44" s="452"/>
-      <c r="F44" s="452"/>
-      <c r="G44" s="452"/>
-      <c r="H44" s="453"/>
+      <c r="B44" s="460" t="s">
+        <v>128</v>
+      </c>
+      <c r="C44" s="461"/>
+      <c r="D44" s="461"/>
+      <c r="E44" s="461"/>
+      <c r="F44" s="461"/>
+      <c r="G44" s="461"/>
+      <c r="H44" s="462"/>
       <c r="I44" s="308" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J44" s="202"/>
       <c r="K44" s="202"/>
@@ -22857,10 +22857,10 @@
       <c r="E45" s="327"/>
       <c r="F45" s="327"/>
       <c r="G45" s="342" t="s">
+        <v>103</v>
+      </c>
+      <c r="H45" s="343" t="s">
         <v>104</v>
-      </c>
-      <c r="H45" s="343" t="s">
-        <v>105</v>
       </c>
       <c r="I45" s="308"/>
       <c r="J45" s="195"/>
@@ -22869,7 +22869,7 @@
     <row r="46" spans="1:11" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A46" s="207"/>
       <c r="B46" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C46" s="327"/>
       <c r="D46" s="327"/>
@@ -22887,7 +22887,7 @@
         <v>860</v>
       </c>
       <c r="J46" s="199" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="K46" s="254"/>
     </row>
@@ -22907,7 +22907,7 @@
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="193"/>
       <c r="B48" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C48" s="327"/>
       <c r="D48" s="327"/>
@@ -22917,21 +22917,21 @@
       </c>
       <c r="G48" s="243"/>
       <c r="H48" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I48" s="308">
         <f>IF(ISNUMBER(G48),G48,F48)</f>
         <v>0.02</v>
       </c>
       <c r="J48" s="199" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K48" s="254"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="193"/>
       <c r="B49" s="215" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C49" s="72"/>
       <c r="D49" s="72"/>
@@ -22941,14 +22941,14 @@
       </c>
       <c r="G49" s="243"/>
       <c r="H49" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I49" s="308">
         <f>IF(ISNUMBER(G49),G49,F49)</f>
         <v>0.15</v>
       </c>
       <c r="J49" s="199" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K49" s="254"/>
     </row>
@@ -22981,7 +22981,7 @@
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="193"/>
       <c r="B52" s="293" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C52" s="340"/>
       <c r="D52" s="340"/>
@@ -22995,10 +22995,10 @@
     </row>
     <row r="53" spans="1:11" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A53" s="193"/>
-      <c r="B53" s="448" t="s">
-        <v>409</v>
-      </c>
-      <c r="C53" s="449"/>
+      <c r="B53" s="457" t="s">
+        <v>408</v>
+      </c>
+      <c r="C53" s="458"/>
       <c r="D53" s="368"/>
       <c r="E53" s="368"/>
       <c r="F53" s="218">
@@ -23006,21 +23006,21 @@
       </c>
       <c r="G53" s="243"/>
       <c r="H53" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I53" s="308">
         <f>IF(ISNUMBER(G53),G53,F53)</f>
         <v>84</v>
       </c>
       <c r="J53" s="199" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K53" s="254"/>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="193"/>
       <c r="B54" s="246" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C54" s="247"/>
       <c r="D54" s="247"/>
@@ -23048,11 +23048,6 @@
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="19">
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="L5:N25"/>
-    <mergeCell ref="B7:B12"/>
-    <mergeCell ref="C7:C11"/>
-    <mergeCell ref="D8:D11"/>
     <mergeCell ref="B53:C53"/>
     <mergeCell ref="A38:A39"/>
     <mergeCell ref="B44:H44"/>
@@ -23067,6 +23062,11 @@
     <mergeCell ref="D22:E22"/>
     <mergeCell ref="D23:E23"/>
     <mergeCell ref="D24:E24"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="L5:N25"/>
+    <mergeCell ref="B7:B12"/>
+    <mergeCell ref="C7:C11"/>
+    <mergeCell ref="D8:D11"/>
   </mergeCells>
   <conditionalFormatting sqref="K35">
     <cfRule type="expression" dxfId="14" priority="10">
@@ -23150,7 +23150,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>20</v>
@@ -23163,7 +23163,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B4" s="154" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C4" s="89"/>
       <c r="D4" s="89"/>
@@ -23177,7 +23177,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C6" s="54">
         <v>1</v>
@@ -23189,7 +23189,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C7" s="102" t="str">
         <f>IF(Anbieter1=0,"",Anbieter1)</f>
@@ -23209,14 +23209,14 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C9" s="102"/>
       <c r="F9" s="125"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C10" s="102" t="str">
         <f>IF(Hersteller1=0,"",Hersteller1)</f>
@@ -23227,7 +23227,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C11" s="102" t="str">
         <f>IF(Modell1=0,"",Modell1)</f>
@@ -23238,7 +23238,7 @@
     </row>
     <row r="12" spans="1:7" ht="43.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="56" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C12" s="102" t="str">
         <f>IF(Zusatzinfo1=0,"",Zusatzinfo1)</f>
@@ -23249,7 +23249,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B13" s="57" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="102" t="str">
         <f>IF(Antriebsart1=0,"",Antriebsart1)</f>
@@ -23260,7 +23260,7 @@
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="107"/>
       <c r="B14" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C14" s="102" t="str">
         <f>IF(Energie1=0,"",Energie1)</f>
@@ -23277,7 +23277,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B16" s="154" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -23291,7 +23291,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B18" s="72" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C18" s="288">
         <f>0.0057*(ReichwPHEV1/23)^3-0.0838*(ReichwPHEV1/23)^2+0.4261*(ReichwPHEV1/23)+ 0.1633</f>
@@ -23302,33 +23302,33 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C19" s="289">
         <f>Verbrauch1/(1-0.9*C18)</f>
         <v>5.7442293940424145</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F19" s="125"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B20" s="72" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C20" s="290">
         <f>VerbEl_WLTP1/C18</f>
         <v>0</v>
       </c>
       <c r="D20" s="184" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F20" s="125"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B21" s="186" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C21" s="291">
         <f>0.0021*(ReichwPHEV1/23)^3-0.0358*(ReichwPHEV1/23)^2+0.2607*(ReichwPHEV1/23)- 0.0267</f>
@@ -23342,14 +23342,14 @@
         <v>11</v>
       </c>
       <c r="B22" s="470" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C22" s="292">
         <f>C19*(1-0.9*C21)</f>
         <v>5.8822632263812533</v>
       </c>
       <c r="D22" s="185" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F22" s="125"/>
     </row>
@@ -23361,7 +23361,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="183" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F23" s="125"/>
     </row>
@@ -23372,7 +23372,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B25" s="154" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C25" s="89"/>
       <c r="D25" s="89"/>
@@ -23383,7 +23383,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B27" s="60" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C27" s="61"/>
       <c r="D27" s="60"/>
@@ -23391,39 +23391,39 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C28" s="279">
         <f>IF(Antriebsart1="Vollelektrisch (BEV)",0,IFERROR(VLOOKUP(Energie1,EnKostList,8,FALSE),0)*IF(Antriebsart1="Plug-In-Hybrid (PHEV)",VerbPHEV1,Verbrauch1)/100*Fahrleistung)</f>
         <v>2048.1999999999998</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F28" s="125"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C29" s="279">
         <f>IF(Antriebsart1="Verbrenner",0,VLOOKUP("Strom",EnKostList,8,FALSE)*IF(Antriebsart1="Plug-In-Hybrid (PHEV)",VerbElPHEV1,VerbEl_WLTP1)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="64" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C30" s="280">
         <f>SUM(C28:C29)</f>
         <v>2048.1999999999998</v>
       </c>
       <c r="D30" s="64" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="14.4" thickTop="1" x14ac:dyDescent="0.25">
@@ -23432,7 +23432,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B32" s="60" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C32" s="145" t="str">
         <f>CONCATENATE("Energieträger: ",Energie1)</f>
@@ -23443,63 +23443,63 @@
     </row>
     <row r="33" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B33" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C33" s="279">
         <f>IF(Antriebsart1="Plug-In-Hybrid (PHEV)",VerbPHEV1*VLOOKUP(Energie1,CO2List,2,FALSE)/100,CO2_1)*Fahrleistung/1000000</f>
         <v>3.25</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F33" s="107"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C34" s="279">
         <f>C33*Kost_THG</f>
         <v>2795</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B35" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C35" s="279">
         <f>IF(Energie1="Strom",0,NOX_1*Fahrleistung*Kost_NOX/1000)</f>
         <v>29.3</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B36" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C36" s="279">
         <f>IF(Energie1="Strom",0,Partikel1*Fahrleistung*Kost_Partikel/1000)</f>
         <v>1.575</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="64" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C37" s="280">
         <f>SUM(C34:C36)</f>
         <v>2825.875</v>
       </c>
       <c r="D37" s="64" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="14.4" thickTop="1" x14ac:dyDescent="0.25">
@@ -23507,7 +23507,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B39" s="60" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C39" s="145" t="str">
         <f>CONCATENATE("Energieträger: ",Energie1,IF(Antriebsart1="Plug-In-Hybrid (PHEV)","+Strom",""))</f>
@@ -23517,32 +23517,32 @@
     </row>
     <row r="40" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B40" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C40" s="279">
         <f>IFERROR(IF(Antriebsart1="Vollelektrisch (BEV)",VLOOKUP("Strom",CO2List,3,FALSE)*VerbEl_WLTP1/100*Fahrleistung/1000000,IF(Antriebsart1="Verbrenner",VLOOKUP(Energie1,CO2List,3,FALSE)*Verbrauch1/100*Fahrleistung/1000000,VLOOKUP(Energie1,CO2List,3,FALSE)*VerbPHEV1/100*Fahrleistung/1000000+VLOOKUP("Strom",CO2List,3,FALSE)*VerbElPHEV1/100*Fahrleistung/1000000)),0)</f>
         <v>1.0188889401600001</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F40" s="107"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B41" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C41" s="279">
         <f>C40*Kost_THG</f>
         <v>876.24448853760009</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B43" s="154" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C43" s="89"/>
       <c r="D43" s="89"/>
@@ -23556,53 +23556,53 @@
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="107"/>
       <c r="B45" s="90" t="s">
+        <v>158</v>
+      </c>
+      <c r="C45" s="134" t="s">
         <v>159</v>
       </c>
-      <c r="C45" s="134" t="s">
-        <v>160</v>
-      </c>
       <c r="D45" s="62"/>
     </row>
     <row r="46" spans="1:6" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="391" t="s">
+      <c r="A46" s="404" t="s">
         <v>11</v>
       </c>
       <c r="B46" s="468" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C46" s="281">
         <f>IF(OR(Antriebsart1="Vollelektrisch (BEV)",Antriebsart1="Plug-In-Hybrid (PHEV)"),Batterie1*Batterie_THG/1000,0)</f>
         <v>0</v>
       </c>
       <c r="D46" s="131" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E46" s="127"/>
       <c r="F46" s="107"/>
     </row>
     <row r="47" spans="1:6" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="391"/>
+      <c r="A47" s="404"/>
       <c r="B47" s="469"/>
       <c r="C47" s="281">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
         <v>0</v>
       </c>
       <c r="D47" s="130" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E47" s="127"/>
       <c r="F47" s="107"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B48" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C48" s="279">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Kost_THG, C46/Haltedauer*Kost_THG)</f>
         <v>0</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -23621,19 +23621,19 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B54" s="68" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C54" s="282">
         <f>IF(FinArt="Kauf",IF(KaufpreisRech="Kaufpreis",Gesamtpreis1,0),Gesamtpreis1*Haltedauer*12+IF(FinArt="Leasing",LeasSondZahl1,0))</f>
         <v>0</v>
       </c>
       <c r="D54" s="68" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F54" s="58"/>
     </row>
@@ -23642,71 +23642,71 @@
         <v>11</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C55" s="283">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis1-Gesamtpreis1*(-0.2*LN(Haltedauer)+0.667),0)</f>
         <v>26555.355418182582</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F55" s="58"/>
     </row>
     <row r="56" spans="1:6" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C56" s="283">
         <f>C30*Haltedauer</f>
         <v>14337.399999999998</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F56" s="58"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C57" s="283">
         <f>C37*Haltedauer</f>
         <v>19781.125</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F57" s="58"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C58" s="283">
         <f>C41*Haltedauer</f>
         <v>6133.7114197632009</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F58" s="58"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B59" s="329" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C59" s="330">
         <f>C48*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D59" s="329" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="391" t="s">
+      <c r="A60" s="404" t="s">
         <v>11</v>
       </c>
       <c r="B60" s="327" t="str">
@@ -23724,7 +23724,7 @@
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="391"/>
+      <c r="A61" s="404"/>
       <c r="B61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
@@ -23740,7 +23740,7 @@
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="391"/>
+      <c r="A62" s="404"/>
       <c r="B62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
@@ -23757,14 +23757,14 @@
     </row>
     <row r="63" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B63" s="64" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C63" s="284">
         <f>SUM(C54:C62)</f>
         <v>67927.591837945787</v>
       </c>
       <c r="D63" s="64" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F63" s="58"/>
     </row>
@@ -23773,26 +23773,26 @@
     </row>
     <row r="65" spans="2:4" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B65" s="68" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C65" s="285">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Haltedauer, C46)</f>
         <v>0</v>
       </c>
       <c r="D65" s="68" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="66" spans="2:4" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B66" s="72" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C66" s="286">
         <f>C33*Haltedauer+C40*Haltedauer</f>
         <v>29.882222581120001</v>
       </c>
       <c r="D66" s="72" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -23842,7 +23842,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>20</v>
@@ -23855,7 +23855,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B4" s="154" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -23871,7 +23871,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C6" s="54">
         <v>2</v>
@@ -23884,7 +23884,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C7" s="102" t="str">
         <f>IF(Anbieter2=0,"",Anbieter2)</f>
@@ -23906,7 +23906,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C9" s="102"/>
       <c r="E9" s="125"/>
@@ -23914,7 +23914,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C10" s="102" t="str">
         <f>IF(Hersteller2=0,"",Hersteller2)</f>
@@ -23926,7 +23926,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C11" s="102" t="str">
         <f>IF(Modell2=0,"",Modell2)</f>
@@ -23938,7 +23938,7 @@
     </row>
     <row r="12" spans="1:6" ht="43.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="56" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C12" s="102" t="str">
         <f>IF(Zusatzinfo2=0,"",Zusatzinfo2)</f>
@@ -23950,7 +23950,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B13" s="57" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="102" t="str">
         <f>IF(Antriebsart2=0,"",Antriebsart2)</f>
@@ -23961,7 +23961,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C14" s="102" t="str">
         <f>IF(Energie2=0,"",Energie2)</f>
@@ -23977,7 +23977,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B16" s="154" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -23993,7 +23993,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B18" s="72" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C18" s="288">
         <f>0.0057*(ReichwPHEV2/23)^3-0.0838*(ReichwPHEV2/23)^2+0.4261*(ReichwPHEV2/23)+ 0.1633</f>
@@ -24005,35 +24005,35 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C19" s="289">
         <f>Verbrauch2/(1-0.9*C18)</f>
         <v>6.6820627644983182</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E19" s="125"/>
       <c r="F19" s="125"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B20" s="72" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C20" s="290">
         <f>VerbEl_WLTP2/C18</f>
         <v>0</v>
       </c>
       <c r="D20" s="184" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E20" s="125"/>
       <c r="F20" s="125"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B21" s="186" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C21" s="291">
         <f>0.0021*(ReichwPHEV2/23)^3-0.0358*(ReichwPHEV2/23)^2+0.2607*(ReichwPHEV2/23)- 0.0267</f>
@@ -24048,14 +24048,14 @@
         <v>11</v>
       </c>
       <c r="B22" s="470" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C22" s="292">
         <f>C19*(1-0.9*C21)</f>
         <v>6.8426327327292125</v>
       </c>
       <c r="D22" s="185" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E22" s="125"/>
       <c r="F22" s="125"/>
@@ -24068,7 +24068,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="183" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E23" s="125"/>
       <c r="F23" s="125"/>
@@ -24080,7 +24080,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B25" s="154" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
@@ -24093,7 +24093,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B27" s="60" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C27" s="61"/>
       <c r="D27" s="60"/>
@@ -24102,42 +24102,42 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C28" s="279">
         <f>IF(Antriebsart2="Vollelektrisch (BEV)",0,IFERROR(VLOOKUP(Energie2,EnKostList,8,FALSE),0)*IF(Antriebsart2="Plug-In-Hybrid (PHEV)",VerbPHEV2,Verbrauch2)/100*Fahrleistung)</f>
         <v>2382.6</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E28" s="125"/>
       <c r="F28" s="125"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C29" s="279">
         <f>IF(Antriebsart2="Verbrenner",0,VLOOKUP("Strom",EnKostList,8,FALSE)*IF(Antriebsart2="Plug-In-Hybrid (PHEV)",VerbElPHEV2,VerbEl_WLTP2)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E29" s="125"/>
       <c r="F29" s="125"/>
     </row>
     <row r="30" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="64" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C30" s="280">
         <f>SUM(C28:C29)</f>
         <v>2382.6</v>
       </c>
       <c r="D30" s="64" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E30" s="125"/>
       <c r="F30" s="125"/>
@@ -24150,7 +24150,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B32" s="60" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C32" s="145" t="str">
         <f>CONCATENATE("Energieträger: ",Energie2)</f>
@@ -24162,70 +24162,70 @@
     </row>
     <row r="33" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B33" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C33" s="279">
         <f>IF(Antriebsart2="Plug-In-Hybrid (PHEV)",VerbPHEV2*VLOOKUP(Energie2,CO2List,2,FALSE)/100,CO2_2)*Fahrleistung/1000000</f>
         <v>3.7250000000000001</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E33" s="125"/>
       <c r="F33" s="125"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C34" s="279">
         <f>C33*Kost_THG</f>
         <v>3203.5</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E34" s="125"/>
       <c r="F34" s="125"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B35" s="7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C35" s="287">
         <f>IF(Energie2="Strom",0,NOX_2*Fahrleistung*Kost_NOX/1000)</f>
         <v>21.2</v>
       </c>
       <c r="D35" s="65" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E35" s="125"/>
       <c r="F35" s="125"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B36" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C36" s="287">
         <f>IF(Energie2="Strom",0,Partikel2*Fahrleistung*Kost_Partikel/1000)</f>
         <v>1.125</v>
       </c>
       <c r="D36" s="65" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E36" s="125"/>
       <c r="F36" s="125"/>
     </row>
     <row r="37" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="64" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C37" s="280">
         <f>SUM(C34:C36)</f>
         <v>3225.8249999999998</v>
       </c>
       <c r="D37" s="64" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E37" s="125"/>
       <c r="F37" s="125"/>
@@ -24238,7 +24238,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B39" s="60" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C39" s="145" t="str">
         <f>CONCATENATE("Energieträger: ",Energie2,IF(Antriebsart2="Plug-In-Hybrid (PHEV)","+Strom",""))</f>
@@ -24250,28 +24250,28 @@
     </row>
     <row r="40" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B40" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C40" s="279">
         <f>IFERROR(IF(Antriebsart2="Vollelektrisch (BEV)",VLOOKUP("Strom",CO2List,3,FALSE)*VerbEl_WLTP2/100*Fahrleistung/1000000,IF(Antriebsart2="Verbrenner",VLOOKUP(Energie2,CO2List,3,FALSE)*Verbrauch2/100*Fahrleistung/1000000,VLOOKUP(Energie2,CO2List,3,FALSE)*VerbPHEV2/100*Fahrleistung/1000000+VLOOKUP("Strom",CO2List,3,FALSE)*VerbElPHEV2/100*Fahrleistung/1000000)),0)</f>
         <v>1.1852381548800002</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E40" s="125"/>
       <c r="F40" s="125"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B41" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C41" s="279">
         <f>C40*Kost_THG</f>
         <v>1019.3048131968002</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E41" s="125"/>
       <c r="F41" s="125"/>
@@ -24282,7 +24282,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B43" s="154" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
@@ -24299,55 +24299,55 @@
     <row r="45" spans="1:6" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="107"/>
       <c r="B45" s="90" t="s">
+        <v>158</v>
+      </c>
+      <c r="C45" s="134" t="s">
         <v>159</v>
-      </c>
-      <c r="C45" s="134" t="s">
-        <v>160</v>
       </c>
       <c r="D45" s="62"/>
       <c r="E45" s="125"/>
       <c r="F45" s="125"/>
     </row>
     <row r="46" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A46" s="391" t="s">
+      <c r="A46" s="404" t="s">
         <v>11</v>
       </c>
       <c r="B46" s="468" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C46" s="281">
         <f>IF(OR(Antriebsart2="Vollelektrisch (BEV)",Antriebsart2="Plug-In-Hybrid (PHEV)"),Batterie2*Batterie_THG/1000,0)</f>
         <v>0</v>
       </c>
       <c r="D46" s="131" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E46" s="127"/>
       <c r="F46" s="125"/>
     </row>
     <row r="47" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="391"/>
+      <c r="A47" s="404"/>
       <c r="B47" s="469"/>
       <c r="C47" s="281">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
         <v>0</v>
       </c>
       <c r="D47" s="130" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E47" s="127"/>
       <c r="F47" s="125"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B48" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C48" s="279">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Kost_THG, C46/Haltedauer*Kost_THG)</f>
         <v>0</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E48" s="125"/>
       <c r="F48" s="125"/>
@@ -24371,20 +24371,20 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="54" spans="1:6" s="70" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="68" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C54" s="282">
         <f>IF(FinArt="Kauf",IF(KaufpreisRech="Kaufpreis",Gesamtpreis2,0),Gesamtpreis2*Haltedauer*12+IF(FinArt="Leasing",LeasSondZahl2,0))</f>
         <v>0</v>
       </c>
       <c r="D54" s="68" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E54" s="69"/>
       <c r="F54" s="58"/>
@@ -24394,72 +24394,72 @@
         <v>11</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C55" s="283">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis2-Gesamtpreis2*(-0.2*LN(Haltedauer)+0.667),0)</f>
         <v>25515.413295254653</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E55" s="125"/>
       <c r="F55" s="73"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B56" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C56" s="283">
         <f>C30*Haltedauer</f>
         <v>16678.2</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F56" s="73"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C57" s="283">
         <f>C37*Haltedauer</f>
         <v>22580.774999999998</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F57" s="58"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C58" s="283">
         <f>C41*Haltedauer</f>
         <v>7135.1336923776016</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F58" s="58"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B59" s="329" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C59" s="330">
         <f>C48*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D59" s="329" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="391" t="s">
+      <c r="A60" s="404" t="s">
         <v>11</v>
       </c>
       <c r="B60" s="327" t="str">
@@ -24477,7 +24477,7 @@
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="391"/>
+      <c r="A61" s="404"/>
       <c r="B61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
@@ -24493,7 +24493,7 @@
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="391"/>
+      <c r="A62" s="404"/>
       <c r="B62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
@@ -24510,14 +24510,14 @@
     </row>
     <row r="63" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B63" s="64" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C63" s="284">
         <f>SUM(C54:C62)</f>
         <v>72861.521987632252</v>
       </c>
       <c r="D63" s="64" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E63" s="14"/>
       <c r="F63" s="58"/>
@@ -24532,26 +24532,26 @@
     </row>
     <row r="65" spans="2:5" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B65" s="68" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C65" s="285">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Haltedauer, C46)</f>
         <v>0</v>
       </c>
       <c r="D65" s="68" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="66" spans="2:5" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B66" s="72" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C66" s="286">
         <f>C33*Haltedauer+C40*Haltedauer</f>
         <v>34.371667084160002</v>
       </c>
       <c r="D66" s="72" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E66" s="71"/>
     </row>
@@ -24602,7 +24602,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>20</v>
@@ -24615,7 +24615,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B4" s="154" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -24631,7 +24631,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C6" s="54">
         <v>3</v>
@@ -24644,7 +24644,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C7" s="102" t="str">
         <f>IF(Anbieter3=0,"",Anbieter3)</f>
@@ -24666,7 +24666,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C9" s="102"/>
       <c r="E9" s="125"/>
@@ -24674,7 +24674,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C10" s="102" t="str">
         <f>IF(Hersteller3=0,"",Hersteller3)</f>
@@ -24686,7 +24686,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C11" s="102" t="str">
         <f>IF(Modell3=0,"",Modell3)</f>
@@ -24698,7 +24698,7 @@
     </row>
     <row r="12" spans="1:6" ht="43.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="56" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C12" s="102" t="str">
         <f>IF(Zusatzinfo3=0,"",Zusatzinfo3)</f>
@@ -24710,7 +24710,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B13" s="57" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="102" t="str">
         <f>IF(Antriebsart3=0,"",Antriebsart3)</f>
@@ -24721,7 +24721,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C14" s="102" t="str">
         <f>IF(Energie3=0,"",Energie3)</f>
@@ -24737,7 +24737,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B16" s="154" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -24753,7 +24753,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B18" s="72" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C18" s="288">
         <f>0.0057*(ReichwPHEV3/23)^3-0.0838*(ReichwPHEV3/23)^2+0.4261*(ReichwPHEV3/23)+ 0.1633</f>
@@ -24765,35 +24765,35 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C19" s="289">
         <f>Verbrauch3/(1-0.9*C18)</f>
         <v>8.9094170193310909</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E19" s="125"/>
       <c r="F19" s="125"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B20" s="72" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C20" s="290">
         <f>VerbEl_WLTP3/C18</f>
         <v>0</v>
       </c>
       <c r="D20" s="184" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E20" s="125"/>
       <c r="F20" s="125"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B21" s="186" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C21" s="291">
         <f>0.0021*(ReichwPHEV3/23)^3-0.0358*(ReichwPHEV3/23)^2+0.2607*(ReichwPHEV3/23)- 0.0267</f>
@@ -24808,14 +24808,14 @@
         <v>11</v>
       </c>
       <c r="B22" s="470" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C22" s="292">
         <f>C19*(1-0.9*C21)</f>
         <v>9.1235103103056172</v>
       </c>
       <c r="D22" s="185" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E22" s="125"/>
       <c r="F22" s="125"/>
@@ -24828,7 +24828,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="183" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E23" s="125"/>
       <c r="F23" s="125"/>
@@ -24840,7 +24840,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B25" s="154" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
@@ -24853,7 +24853,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B27" s="60" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C27" s="61"/>
       <c r="D27" s="60"/>
@@ -24862,42 +24862,42 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C28" s="279">
         <f>IF(Antriebsart3="Vollelektrisch (BEV)",0,IFERROR(VLOOKUP(Energie3,EnKostList,8,FALSE),0)*IF(Antriebsart3="Plug-In-Hybrid (PHEV)",VerbPHEV3,Verbrauch3)/100*Fahrleistung)</f>
         <v>3176.7999999999997</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E28" s="125"/>
       <c r="F28" s="125"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C29" s="279">
         <f>IF(Antriebsart3="Verbrenner",0,VLOOKUP("Strom",EnKostList,8,FALSE)*IF(Antriebsart3="Plug-In-Hybrid (PHEV)",VerbElPHEV3,VerbEl_WLTP3)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E29" s="125"/>
       <c r="F29" s="125"/>
     </row>
     <row r="30" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="64" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C30" s="280">
         <f>SUM(C28:C29)</f>
         <v>3176.7999999999997</v>
       </c>
       <c r="D30" s="64" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E30" s="125"/>
       <c r="F30" s="125"/>
@@ -24910,7 +24910,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B32" s="60" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C32" s="145" t="str">
         <f>CONCATENATE("Energieträger: ",Energie3)</f>
@@ -24922,70 +24922,70 @@
     </row>
     <row r="33" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B33" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C33" s="279">
         <f>IF(Antriebsart3="Plug-In-Hybrid (PHEV)",VerbPHEV3*VLOOKUP(Energie3,CO2List,2,FALSE)/100,CO2_3)*Fahrleistung/1000000</f>
         <v>4.95</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E33" s="125"/>
       <c r="F33" s="125"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C34" s="279">
         <f>C33*Kost_THG</f>
         <v>4257</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E34" s="125"/>
       <c r="F34" s="125"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B35" s="7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C35" s="287">
         <f>IF(Energie3="Strom",0,NOX_3*Fahrleistung*Kost_NOX/1000)</f>
         <v>21.1</v>
       </c>
       <c r="D35" s="65" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E35" s="125"/>
       <c r="F35" s="125"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B36" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C36" s="287">
         <f>IF(Energie3="Strom",0,Partikel3*Fahrleistung*Kost_Partikel/1000)</f>
         <v>1.875</v>
       </c>
       <c r="D36" s="65" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E36" s="125"/>
       <c r="F36" s="125"/>
     </row>
     <row r="37" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="64" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C37" s="280">
         <f>SUM(C34:C36)</f>
         <v>4279.9750000000004</v>
       </c>
       <c r="D37" s="64" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E37" s="125"/>
       <c r="F37" s="125"/>
@@ -24998,7 +24998,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B39" s="60" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C39" s="145" t="str">
         <f>CONCATENATE("Energieträger: ",Energie3,IF(Antriebsart3="Plug-In-Hybrid (PHEV)","+Strom",""))</f>
@@ -25010,28 +25010,28 @@
     </row>
     <row r="40" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B40" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C40" s="279">
         <f>IFERROR(IF(Antriebsart3="Vollelektrisch (BEV)",VLOOKUP("Strom",CO2List,3,FALSE)*VerbEl_WLTP3/100*Fahrleistung/1000000,IF(Antriebsart3="Verbrenner",VLOOKUP(Energie3,CO2List,3,FALSE)*Verbrauch3/100*Fahrleistung/1000000,VLOOKUP(Energie3,CO2List,3,FALSE)*VerbPHEV3/100*Fahrleistung/1000000+VLOOKUP("Strom",CO2List,3,FALSE)*VerbElPHEV3/100*Fahrleistung/1000000)),0)</f>
         <v>1.58031753984</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E40" s="125"/>
       <c r="F40" s="125"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B41" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C41" s="279">
         <f>C40*Kost_THG</f>
         <v>1359.0730842624</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E41" s="125"/>
       <c r="F41" s="125"/>
@@ -25042,7 +25042,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B43" s="154" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
@@ -25059,55 +25059,55 @@
     <row r="45" spans="1:6" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="107"/>
       <c r="B45" s="90" t="s">
+        <v>158</v>
+      </c>
+      <c r="C45" s="134" t="s">
         <v>159</v>
-      </c>
-      <c r="C45" s="134" t="s">
-        <v>160</v>
       </c>
       <c r="D45" s="62"/>
       <c r="E45" s="125"/>
       <c r="F45" s="125"/>
     </row>
     <row r="46" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A46" s="391" t="s">
+      <c r="A46" s="404" t="s">
         <v>11</v>
       </c>
       <c r="B46" s="468" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C46" s="281">
         <f>IF(OR(Antriebsart3="Vollelektrisch (BEV)",Antriebsart3="Plug-In-Hybrid (PHEV)"),Batterie3*Batterie_THG/1000,0)</f>
         <v>0</v>
       </c>
       <c r="D46" s="131" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E46" s="127"/>
       <c r="F46" s="133"/>
     </row>
     <row r="47" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="391"/>
+      <c r="A47" s="404"/>
       <c r="B47" s="469"/>
       <c r="C47" s="281">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
         <v>0</v>
       </c>
       <c r="D47" s="130" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E47" s="127"/>
       <c r="F47" s="133"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B48" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C48" s="279">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Kost_THG, C46/Haltedauer*Kost_THG)</f>
         <v>0</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E48" s="125"/>
       <c r="F48" s="125"/>
@@ -25131,20 +25131,20 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="54" spans="1:6" s="70" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="68" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C54" s="282">
         <f>IF(FinArt="Kauf",IF(KaufpreisRech="Kaufpreis",Gesamtpreis3,0),Gesamtpreis3*Haltedauer*12+IF(FinArt="Leasing",LeasSondZahl3,0))</f>
         <v>0</v>
       </c>
       <c r="D54" s="68" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E54" s="69"/>
       <c r="F54" s="58"/>
@@ -25154,72 +25154,72 @@
         <v>11</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C55" s="283">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis3-Gesamtpreis3*(-0.2*LN(Haltedauer)+0.667),0)</f>
         <v>25739.289724496084</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E55" s="125"/>
       <c r="F55" s="73"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B56" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C56" s="283">
         <f>C30*Haltedauer</f>
         <v>22237.599999999999</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F56" s="73"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C57" s="283">
         <f>C37*Haltedauer</f>
         <v>29959.825000000004</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F57" s="58"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C58" s="283">
         <f>C41*Haltedauer</f>
         <v>9513.5115898368003</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F58" s="58"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B59" s="327" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C59" s="328">
         <f>C48*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D59" s="327" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="391" t="s">
+      <c r="A60" s="404" t="s">
         <v>11</v>
       </c>
       <c r="B60" s="327" t="str">
@@ -25237,7 +25237,7 @@
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="391"/>
+      <c r="A61" s="404"/>
       <c r="B61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
@@ -25253,7 +25253,7 @@
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="391"/>
+      <c r="A62" s="404"/>
       <c r="B62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
@@ -25270,14 +25270,14 @@
     </row>
     <row r="63" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B63" s="64" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C63" s="284">
         <f>SUM(C54:C62)</f>
         <v>88654.226314332889</v>
       </c>
       <c r="D63" s="64" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E63" s="14"/>
       <c r="F63" s="58"/>
@@ -25292,26 +25292,26 @@
     </row>
     <row r="65" spans="2:5" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B65" s="68" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C65" s="285">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Haltedauer, C46)</f>
         <v>0</v>
       </c>
       <c r="D65" s="68" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="66" spans="2:5" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B66" s="72" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C66" s="286">
         <f>C33*Haltedauer+C40*Haltedauer</f>
         <v>45.712222778879998</v>
       </c>
       <c r="D66" s="72" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E66" s="71"/>
     </row>
@@ -25569,15 +25569,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3" xsi:nil="true"/>
@@ -25586,6 +25577,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -25608,26 +25608,26 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{651615EB-DE44-4BF4-BD1E-846AB7A3DA36}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="5e4dc333-02c0-4d6f-a03d-d04a548a7be7"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92A2CDCF-36F6-4C30-8F9B-D45880CB8E7E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{651615EB-DE44-4BF4-BD1E-846AB7A3DA36}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="5e4dc333-02c0-4d6f-a03d-d04a548a7be7"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/src/assets/downloads/LZK-Rechner_LNF_V1.0_Beispiel.xlsx
+++ b/src/assets/downloads/LZK-Rechner_LNF_V1.0_Beispiel.xlsx
@@ -5,10 +5,10 @@
   <workbookPr updateLinks="never"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Julia Pelzeter\Downloads\Online-Tool\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ifeu2.sharepoint.com/sites/DBUBeschaffungBerlin/Freigegebene Dokumente/General/Folgeprojekt/03_Arbeitsdokumente/B2 - LZK-Rechner LNF/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9AFBD6D-EC2F-4E54-A5D3-9191262F3CBA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="8_{7D517AF7-4619-43FA-847D-E38F8B66F015}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{1AEC688A-F306-4865-95FD-2095E607FE8B}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" tabRatio="887" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2626,49 +2626,6 @@
     <t>Gesellschaftliche Kosten von Umweltbelastungen - Klimakosten von Treibhausgas-Emissionen (02.07.2024)</t>
   </si>
   <si>
-    <r>
-      <t>Der Excel-Rechner ist</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> ohne Passwort</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> geschützt. Der Blattschutz kann unter "Überprüfen -&gt; Blattschutz aufheben" aufgehoben werden.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Das Tool kann grundsätzlich nach eigenen Bedürfnissen über die vorgesehenen Anpassungsmöglichkeiten hinaus angepasst werden. 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Es ist jedoch zu berücksichtigen, dass dadurch Berechnungsfehler entstehen können.</t>
-    </r>
-  </si>
-  <si>
     <t>Angaben zu den Energiekosten</t>
   </si>
   <si>
@@ -3525,6 +3482,49 @@
   </si>
   <si>
     <t>Ladeverhalten Elektrofahrzeug</t>
+  </si>
+  <si>
+    <r>
+      <t>Der Excel-Rechner ist</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> ohne Passwort</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> geschützt. Der Blattschutz kann unter "Überprüfen -&gt; Blattschutz aufheben" aufgehoben werden.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Das Tool kann grundsätzlich nach eigenen Bedürfnissen über die vorgesehenen Anpassungsmöglichkeiten hinaus angepasst werden. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Es ist jedoch zu berücksichtigen, dass dadurch Berechnungsfehler entstehen können. Die Verantwortung liegt bei der Person, die den Rechner angepasst hat.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -14366,7 +14366,7 @@
   <sheetData>
     <row r="2" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B2" s="16" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C2" s="16"/>
       <c r="D2" s="16"/>
@@ -14376,7 +14376,7 @@
       <c r="H2" s="16"/>
       <c r="I2" s="16"/>
       <c r="J2" s="268" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.25">
@@ -14399,7 +14399,7 @@
     </row>
     <row r="5" spans="2:10" ht="163.19999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="391" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C5" s="391"/>
       <c r="D5" s="391"/>
@@ -14447,7 +14447,7 @@
       <c r="D9" s="245"/>
       <c r="E9" s="245"/>
       <c r="F9" s="392" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="G9" s="392"/>
       <c r="H9" s="392"/>
@@ -14467,7 +14467,7 @@
       <c r="D11" s="245"/>
       <c r="E11" s="245"/>
       <c r="F11" s="393" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G11" s="394"/>
       <c r="H11" s="394"/>
@@ -14630,7 +14630,7 @@
       <c r="D28" s="245"/>
       <c r="E28" s="245"/>
       <c r="F28" s="401" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G28" s="401"/>
       <c r="H28" s="401"/>
@@ -14826,9 +14826,9 @@
       <c r="I45" s="114"/>
       <c r="J45" s="114"/>
     </row>
-    <row r="46" spans="2:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:11" ht="58.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="402" t="s">
-        <v>402</v>
+        <v>632</v>
       </c>
       <c r="C46" s="402"/>
       <c r="D46" s="402"/>
@@ -15003,7 +15003,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>20</v>
@@ -15555,7 +15555,7 @@
         <v>11</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C55" s="283">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis4-Gesamtpreis4*(-0.2*LN(Haltedauer)+0.667),0)</f>
@@ -15763,7 +15763,7 @@
     </row>
     <row r="2" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>20</v>
@@ -16319,7 +16319,7 @@
         <v>11</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C55" s="283">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis5-Gesamtpreis5*(-0.2*LN(Haltedauer)+0.667),0)</f>
@@ -16530,7 +16530,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B4" s="154" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
@@ -16592,7 +16592,7 @@
     </row>
     <row r="10" spans="1:9" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="92" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C10" s="10"/>
       <c r="D10" s="10"/>
@@ -16694,14 +16694,14 @@
     </row>
     <row r="18" spans="1:37" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="92" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D18" s="106"/>
       <c r="E18" s="10"/>
     </row>
     <row r="20" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B20" s="154" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
@@ -16717,13 +16717,13 @@
         <v>119</v>
       </c>
       <c r="J21" s="135" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="K21" s="135"/>
       <c r="L21" s="135"/>
       <c r="M21" s="135"/>
       <c r="O21" s="137" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="P21" s="137"/>
       <c r="Q21" s="137"/>
@@ -16865,7 +16865,7 @@
         <v>180</v>
       </c>
       <c r="I24" s="58" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="J24" s="300">
         <v>445</v>
@@ -17044,12 +17044,12 @@
     </row>
     <row r="39" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="234" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="40" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="234" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="41" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17065,12 +17065,12 @@
     </row>
     <row r="44" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="2" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="45" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="267" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="I45" s="106"/>
     </row>
@@ -17085,10 +17085,10 @@
     </row>
     <row r="50" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B50" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.25">
@@ -17096,7 +17096,7 @@
         <v>200</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.25">
@@ -17104,7 +17104,7 @@
         <v>201</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="53" spans="2:4" x14ac:dyDescent="0.25">
@@ -17112,7 +17112,7 @@
         <v>202</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.25">
@@ -17120,7 +17120,7 @@
         <v>30</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="55" spans="2:4" x14ac:dyDescent="0.25">
@@ -17128,7 +17128,7 @@
         <v>203</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.25">
@@ -17136,23 +17136,23 @@
         <v>204</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="57" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.25">
@@ -17160,15 +17160,15 @@
         <v>205</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="60" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B60" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>630</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>631</v>
       </c>
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.25">
@@ -17176,7 +17176,7 @@
         <v>206</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="62" spans="2:4" x14ac:dyDescent="0.25">
@@ -17264,7 +17264,7 @@
         <v>227</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="73" spans="2:4" x14ac:dyDescent="0.25">
@@ -17272,7 +17272,7 @@
         <v>229</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="74" spans="2:4" x14ac:dyDescent="0.25">
@@ -17280,7 +17280,7 @@
         <v>231</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="75" spans="2:4" x14ac:dyDescent="0.25">
@@ -17288,7 +17288,7 @@
         <v>233</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="76" spans="2:4" x14ac:dyDescent="0.25">
@@ -17296,7 +17296,7 @@
         <v>235</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="77" spans="2:4" x14ac:dyDescent="0.25">
@@ -17381,7 +17381,7 @@
     </row>
     <row r="87" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B87" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>258</v>
@@ -17389,7 +17389,7 @@
     </row>
     <row r="88" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B88" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>260</v>
@@ -17397,7 +17397,7 @@
     </row>
     <row r="89" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B89" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>262</v>
@@ -17405,7 +17405,7 @@
     </row>
     <row r="90" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B90" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>264</v>
@@ -17413,7 +17413,7 @@
     </row>
     <row r="91" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B91" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>266</v>
@@ -17781,146 +17781,146 @@
     </row>
     <row r="137" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B137" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="138" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B138" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="139" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B139" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="140" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B140" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="141" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B141" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="142" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B142" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="143" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B143" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="144" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B144" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="145" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B145" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="146" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B146" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="147" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B147" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="148" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B148" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="149" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B149" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="150" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B150" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="151" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B151" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="152" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B152" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="153" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B153" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="154" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B154" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="155" spans="2:4" x14ac:dyDescent="0.25">
@@ -17968,7 +17968,7 @@
         <v>374</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="161" spans="2:4" x14ac:dyDescent="0.25">
@@ -17976,7 +17976,7 @@
         <v>357</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="162" spans="2:4" x14ac:dyDescent="0.25">
@@ -17984,7 +17984,7 @@
         <v>358</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="163" spans="2:4" x14ac:dyDescent="0.25">
@@ -17992,7 +17992,7 @@
         <v>359</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="164" spans="2:4" x14ac:dyDescent="0.25">
@@ -18000,71 +18000,71 @@
         <v>360</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="165" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B165" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="166" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B166" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="167" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B167" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="168" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B168" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="D168" s="1" t="s">
         <v>604</v>
-      </c>
-      <c r="D168" s="1" t="s">
-        <v>605</v>
       </c>
     </row>
     <row r="169" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B169" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="D169" s="1" t="s">
         <v>606</v>
-      </c>
-      <c r="D169" s="1" t="s">
-        <v>607</v>
       </c>
     </row>
     <row r="170" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B170" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="171" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B171" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="D171" s="1" t="s">
         <v>609</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="172" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B172" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="173" spans="2:4" x14ac:dyDescent="0.25">
@@ -18072,63 +18072,63 @@
         <v>361</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="174" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B174" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="D174" s="1" t="s">
         <v>612</v>
-      </c>
-      <c r="D174" s="1" t="s">
-        <v>613</v>
       </c>
     </row>
     <row r="175" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B175" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="176" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B176" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="D176" s="1" t="s">
         <v>615</v>
-      </c>
-      <c r="D176" s="1" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="177" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B177" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="178" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B178" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="179" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B179" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="D179" s="1" t="s">
         <v>619</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="180" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B180" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="D180" s="1" t="s">
         <v>621</v>
-      </c>
-      <c r="D180" s="1" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="181" spans="2:4" x14ac:dyDescent="0.25">
@@ -18136,7 +18136,7 @@
         <v>362</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="182" spans="2:4" x14ac:dyDescent="0.25">
@@ -18144,7 +18144,7 @@
         <v>363</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="183" spans="2:4" x14ac:dyDescent="0.25">
@@ -18152,7 +18152,7 @@
         <v>189</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="184" spans="2:4" x14ac:dyDescent="0.25">
@@ -18160,7 +18160,7 @@
         <v>364</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="185" spans="2:4" x14ac:dyDescent="0.25">
@@ -18168,7 +18168,7 @@
         <v>369</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="186" spans="2:4" x14ac:dyDescent="0.25">
@@ -18176,7 +18176,7 @@
         <v>190</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="187" spans="2:4" x14ac:dyDescent="0.25">
@@ -18184,7 +18184,7 @@
         <v>365</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="188" spans="2:4" x14ac:dyDescent="0.25">
@@ -18192,7 +18192,7 @@
         <v>370</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="189" spans="2:4" x14ac:dyDescent="0.25">
@@ -18200,7 +18200,7 @@
         <v>191</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="190" spans="2:4" x14ac:dyDescent="0.25">
@@ -18208,7 +18208,7 @@
         <v>366</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="191" spans="2:4" x14ac:dyDescent="0.25">
@@ -18216,7 +18216,7 @@
         <v>371</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="192" spans="2:4" x14ac:dyDescent="0.25">
@@ -18224,7 +18224,7 @@
         <v>193</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="193" spans="2:4" x14ac:dyDescent="0.25">
@@ -18232,7 +18232,7 @@
         <v>367</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="194" spans="2:4" x14ac:dyDescent="0.25">
@@ -18240,7 +18240,7 @@
         <v>372</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="195" spans="2:4" x14ac:dyDescent="0.25">
@@ -18248,7 +18248,7 @@
         <v>194</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="196" spans="2:4" x14ac:dyDescent="0.25">
@@ -18256,7 +18256,7 @@
         <v>368</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="197" spans="2:4" x14ac:dyDescent="0.25">
@@ -18264,7 +18264,7 @@
         <v>373</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="198" spans="2:4" x14ac:dyDescent="0.25">
@@ -18272,7 +18272,7 @@
         <v>375</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="199" spans="2:4" x14ac:dyDescent="0.25">
@@ -18280,7 +18280,7 @@
         <v>376</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="200" spans="2:4" x14ac:dyDescent="0.25">
@@ -18288,7 +18288,7 @@
         <v>377</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="201" spans="2:4" x14ac:dyDescent="0.25">
@@ -18296,7 +18296,7 @@
         <v>378</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="202" spans="2:4" x14ac:dyDescent="0.25">
@@ -18312,7 +18312,7 @@
         <v>381</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="204" spans="2:4" x14ac:dyDescent="0.25">
@@ -18320,31 +18320,31 @@
         <v>382</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="205" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B205" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="D205" s="1" t="s">
         <v>623</v>
-      </c>
-      <c r="D205" s="1" t="s">
-        <v>624</v>
       </c>
     </row>
     <row r="206" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B206" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="D206" s="1" t="s">
         <v>625</v>
-      </c>
-      <c r="D206" s="1" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="207" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B207" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="D207" s="1" t="s">
         <v>627</v>
-      </c>
-      <c r="D207" s="1" t="s">
-        <v>628</v>
       </c>
     </row>
   </sheetData>
@@ -18476,7 +18476,7 @@
         <v>190</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.25">
@@ -18540,7 +18540,7 @@
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B29" s="3" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C29" s="3"/>
       <c r="D29" s="5"/>
@@ -18549,17 +18549,17 @@
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B30" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B33" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C33" s="3"/>
       <c r="D33" s="5"/>
@@ -18568,32 +18568,32 @@
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B35" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B36" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B37" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B38" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B40" s="3" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C40" s="3"/>
       <c r="D40" s="5"/>
@@ -18602,17 +18602,17 @@
     </row>
     <row r="41" spans="2:6" ht="27.6" x14ac:dyDescent="0.25">
       <c r="B41" s="385" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="42" spans="2:6" ht="27.6" x14ac:dyDescent="0.25">
       <c r="B42" s="385" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="43" spans="2:6" ht="27.6" x14ac:dyDescent="0.25">
       <c r="B43" s="385" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.25">
@@ -18666,7 +18666,7 @@
     </row>
     <row r="4" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B4" s="275" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C4" s="275" t="s">
         <v>384</v>
@@ -18679,23 +18679,23 @@
     </row>
     <row r="6" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B6" s="275" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C6" s="275" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="7" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C7" s="276" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="8" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B8" s="275" t="s">
+        <v>443</v>
+      </c>
+      <c r="C8" s="270" t="s">
         <v>444</v>
-      </c>
-      <c r="C8" s="270" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="9" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
@@ -18732,15 +18732,15 @@
     </row>
     <row r="14" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B14" s="275" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C14" s="275" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="15" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C15" s="276" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="16" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
@@ -18758,15 +18758,15 @@
     </row>
     <row r="18" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B18" s="275" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C18" s="275" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="19" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C19" s="276" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="20" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
@@ -18784,20 +18784,20 @@
     </row>
     <row r="22" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B22" s="275" t="s">
+        <v>423</v>
+      </c>
+      <c r="C22" s="275" t="s">
         <v>424</v>
-      </c>
-      <c r="C22" s="275" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="23" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C23" s="276" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="24" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B24" s="275" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C24" s="275" t="s">
         <v>401</v>
@@ -18810,15 +18810,15 @@
     </row>
     <row r="26" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B26" s="275" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C26" s="275" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="27" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C27" s="269" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="28" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -18867,7 +18867,7 @@
   <sheetData>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="I2" s="106" t="s">
         <v>20</v>
@@ -18886,10 +18886,10 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C6" s="409" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="D6" s="410"/>
       <c r="E6" s="410"/>
@@ -18965,10 +18965,10 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C13" s="406" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D13" s="407"/>
       <c r="E13" s="55"/>
@@ -18979,10 +18979,10 @@
     <row r="14" spans="1:9" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="404"/>
       <c r="B14" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C14" s="406" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D14" s="407"/>
       <c r="E14" s="55"/>
@@ -19000,7 +19000,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C16" s="152">
         <v>25000</v>
@@ -19044,7 +19044,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B20" s="298" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C20" s="151">
         <v>2024</v>
@@ -19111,7 +19111,7 @@
         <v>35</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F27" s="274">
         <f>Grunddaten!G46</f>
@@ -19123,7 +19123,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B29" s="154" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
@@ -19332,7 +19332,7 @@
     </row>
     <row r="2" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C2" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D2" s="2"/>
       <c r="J2" s="7"/>
@@ -19506,16 +19506,16 @@
       </c>
       <c r="D10" s="162"/>
       <c r="E10" s="140" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="F10" s="140" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="G10" s="140" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H10" s="140" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="I10" s="140" t="s">
         <v>59</v>
@@ -19523,7 +19523,7 @@
       <c r="J10" s="238"/>
       <c r="K10" s="236"/>
       <c r="L10" s="432" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="M10" s="432"/>
       <c r="N10" s="236"/>
@@ -19538,19 +19538,19 @@
       </c>
       <c r="D11" s="162"/>
       <c r="E11" s="141" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="F11" s="141" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="G11" s="141" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H11" s="141" t="s">
+        <v>547</v>
+      </c>
+      <c r="I11" s="141" t="s">
         <v>548</v>
-      </c>
-      <c r="I11" s="141" t="s">
-        <v>549</v>
       </c>
       <c r="J11" s="238"/>
       <c r="K11" s="434" t="s">
@@ -19570,19 +19570,19 @@
       </c>
       <c r="D12" s="88"/>
       <c r="E12" s="141" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="F12" s="141" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="G12" s="141" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H12" s="141" t="s">
+        <v>549</v>
+      </c>
+      <c r="I12" s="141" t="s">
         <v>550</v>
-      </c>
-      <c r="I12" s="141" t="s">
-        <v>551</v>
       </c>
       <c r="J12" s="164"/>
       <c r="K12" s="433" t="s">
@@ -19598,23 +19598,23 @@
     </row>
     <row r="13" spans="2:18" s="91" customFormat="1" ht="55.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C13" s="165" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D13" s="384"/>
       <c r="E13" s="139" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F13" s="139" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="G13" s="139" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H13" s="139" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="I13" s="139" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="J13" s="164"/>
       <c r="K13" s="366"/>
@@ -19913,7 +19913,7 @@
     </row>
     <row r="24" spans="2:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C24" s="77" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D24" s="228"/>
       <c r="E24" s="389"/>
@@ -19932,7 +19932,7 @@
         <v>11</v>
       </c>
       <c r="C25" s="331" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D25" s="322" t="s">
         <v>150</v>
@@ -20052,7 +20052,7 @@
     </row>
     <row r="33" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C33" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
   </sheetData>
@@ -20445,7 +20445,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B1" s="118" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C1" s="118"/>
       <c r="D1" s="118"/>
@@ -20459,7 +20459,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="65" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C2" s="227"/>
       <c r="D2" s="230" t="str">
@@ -20502,7 +20502,7 @@
     <row r="6" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="18"/>
       <c r="B6" s="12" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C6" s="439" t="str">
         <f>IF(Projektname=0,"",Projektname)</f>
@@ -20584,7 +20584,7 @@
       <c r="B12" s="12"/>
       <c r="C12" s="76"/>
       <c r="E12" s="58" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="F12" s="85">
         <f>Fahrleistung</f>
@@ -21079,7 +21079,7 @@
     <row r="31" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="309"/>
       <c r="B31" s="98" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C31" s="317" t="s">
         <v>95</v>
@@ -21109,10 +21109,10 @@
     <row r="32" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="309"/>
       <c r="B32" s="310" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C32" s="311" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D32" s="312">
         <f>SUM(D30:D31)</f>
@@ -21269,7 +21269,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B1" s="118" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C1" s="118"/>
       <c r="D1" s="118"/>
@@ -21283,7 +21283,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="65" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C2" s="227"/>
       <c r="D2" s="230" t="str">
@@ -21326,7 +21326,7 @@
     <row r="6" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="18"/>
       <c r="B6" s="12" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C6" s="439" t="str">
         <f>IF(Projektname=0,"",Projektname)</f>
@@ -21408,7 +21408,7 @@
       <c r="B12" s="12"/>
       <c r="C12" s="76"/>
       <c r="E12" s="58" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="F12" s="85">
         <f>Fahrleistung</f>
@@ -21448,7 +21448,7 @@
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="18"/>
       <c r="B15" s="293" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C15" s="21"/>
       <c r="D15" s="21"/>
@@ -21745,7 +21745,7 @@
     <row r="26" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="33"/>
       <c r="B26" s="98" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C26" s="99" t="s">
         <v>95</v>
@@ -21775,10 +21775,10 @@
     <row r="27" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="33"/>
       <c r="B27" s="310" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C27" s="311" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D27" s="312">
         <f>SUM(D25:D26)</f>
@@ -21804,7 +21804,7 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B29" s="293" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C29" s="21"/>
       <c r="D29" s="21"/>
@@ -21972,7 +21972,7 @@
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="119"/>
       <c r="B4" s="293" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C4" s="354"/>
       <c r="D4" s="354"/>
@@ -21997,7 +21997,7 @@
       <c r="I5" s="190"/>
       <c r="J5" s="119"/>
       <c r="L5" s="448" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="M5" s="448"/>
       <c r="N5" s="448"/>
@@ -22011,10 +22011,10 @@
         <v>44</v>
       </c>
       <c r="D6" s="221" t="s">
+        <v>518</v>
+      </c>
+      <c r="E6" s="221" t="s">
         <v>519</v>
-      </c>
-      <c r="E6" s="221" t="s">
-        <v>520</v>
       </c>
       <c r="F6" s="221" t="s">
         <v>102</v>
@@ -22042,10 +22042,10 @@
         <v>46</v>
       </c>
       <c r="D7" s="370" t="s">
+        <v>520</v>
+      </c>
+      <c r="E7" s="386" t="s">
         <v>521</v>
-      </c>
-      <c r="E7" s="386" t="s">
-        <v>522</v>
       </c>
       <c r="F7" s="223">
         <v>230</v>
@@ -22068,10 +22068,10 @@
       <c r="B8" s="450"/>
       <c r="C8" s="453"/>
       <c r="D8" s="455" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E8" s="387" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="F8" s="223">
         <v>150</v>
@@ -22095,7 +22095,7 @@
       <c r="C9" s="453"/>
       <c r="D9" s="455"/>
       <c r="E9" s="386" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="F9" s="223">
         <v>160</v>
@@ -22119,7 +22119,7 @@
       <c r="C10" s="453"/>
       <c r="D10" s="455"/>
       <c r="E10" s="387" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="F10" s="223">
         <v>190</v>
@@ -22143,7 +22143,7 @@
       <c r="C11" s="454"/>
       <c r="D11" s="456"/>
       <c r="E11" s="386" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="F11" s="223">
         <v>210</v>
@@ -22168,10 +22168,10 @@
         <v>107</v>
       </c>
       <c r="D12" s="223" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="E12" s="386" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F12" s="223">
         <v>40</v>
@@ -22198,10 +22198,10 @@
         <v>112</v>
       </c>
       <c r="D13" s="371" t="s">
+        <v>520</v>
+      </c>
+      <c r="E13" s="386" t="s">
         <v>521</v>
-      </c>
-      <c r="E13" s="386" t="s">
-        <v>522</v>
       </c>
       <c r="F13" s="223">
         <v>32</v>
@@ -22224,10 +22224,10 @@
       <c r="B14" s="450"/>
       <c r="C14" s="453"/>
       <c r="D14" s="463" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E14" s="386" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="F14" s="223">
         <v>20</v>
@@ -22251,7 +22251,7 @@
       <c r="C15" s="453"/>
       <c r="D15" s="455"/>
       <c r="E15" s="386" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="F15" s="223">
         <v>28</v>
@@ -22275,7 +22275,7 @@
       <c r="C16" s="454"/>
       <c r="D16" s="456"/>
       <c r="E16" s="386" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="F16" s="223">
         <v>32</v>
@@ -22302,13 +22302,13 @@
         <v>46</v>
       </c>
       <c r="D17" s="223" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="E17" s="223" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F17" s="223" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="G17" s="272"/>
       <c r="H17" s="222" t="s">
@@ -22327,16 +22327,16 @@
       <c r="A18" s="437"/>
       <c r="B18" s="450"/>
       <c r="C18" s="222" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D18" s="223" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="E18" s="223" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F18" s="223" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="G18" s="272"/>
       <c r="H18" s="222" t="s">
@@ -22355,16 +22355,16 @@
       <c r="A19" s="437"/>
       <c r="B19" s="451"/>
       <c r="C19" s="222" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D19" s="223" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="E19" s="223" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F19" s="223" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="G19" s="272"/>
       <c r="H19" s="222" t="s">
@@ -22384,7 +22384,7 @@
       <c r="B20" s="378"/>
       <c r="C20" s="380"/>
       <c r="D20" s="464" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="E20" s="465"/>
       <c r="F20" s="381"/>
@@ -22405,7 +22405,7 @@
         <v>109</v>
       </c>
       <c r="D21" s="466" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E21" s="467"/>
       <c r="F21" s="386">
@@ -22429,7 +22429,7 @@
       <c r="B22" s="450"/>
       <c r="C22" s="453"/>
       <c r="D22" s="466" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E22" s="467"/>
       <c r="F22" s="386">
@@ -22454,7 +22454,7 @@
       <c r="B23" s="451"/>
       <c r="C23" s="454"/>
       <c r="D23" s="466" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="E23" s="467"/>
       <c r="F23" s="386">
@@ -22482,7 +22482,7 @@
         <v>109</v>
       </c>
       <c r="D24" s="466" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E24" s="467"/>
       <c r="F24" s="388">
@@ -22510,10 +22510,10 @@
         <v>107</v>
       </c>
       <c r="D25" s="223" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="E25" s="223" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F25" s="224">
         <v>60</v>
@@ -22588,7 +22588,7 @@
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="196"/>
       <c r="B31" s="293" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C31" s="339"/>
       <c r="D31" s="339"/>
@@ -22673,7 +22673,7 @@
         <v>0.41399999999999998</v>
       </c>
       <c r="J35" s="199" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="K35" s="254"/>
     </row>
@@ -22697,7 +22697,7 @@
         <v>0.59</v>
       </c>
       <c r="J36" s="199" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K36" s="254"/>
     </row>
@@ -22739,7 +22739,7 @@
         <v>1.6719999999999999</v>
       </c>
       <c r="J38" s="199" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="K38" s="254"/>
     </row>
@@ -22763,7 +22763,7 @@
         <v>1.788</v>
       </c>
       <c r="J39" s="199" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="K39" s="254"/>
     </row>
@@ -22787,7 +22787,7 @@
         <v>1.3</v>
       </c>
       <c r="J40" s="199" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="K40" s="254"/>
     </row>
@@ -22887,7 +22887,7 @@
         <v>860</v>
       </c>
       <c r="J46" s="199" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="K46" s="254"/>
     </row>
@@ -22996,7 +22996,7 @@
     <row r="53" spans="1:11" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A53" s="193"/>
       <c r="B53" s="457" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C53" s="458"/>
       <c r="D53" s="368"/>
@@ -23150,7 +23150,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>20</v>
@@ -23642,7 +23642,7 @@
         <v>11</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C55" s="283">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis1-Gesamtpreis1*(-0.2*LN(Haltedauer)+0.667),0)</f>
@@ -23842,7 +23842,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>20</v>
@@ -24394,7 +24394,7 @@
         <v>11</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C55" s="283">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis2-Gesamtpreis2*(-0.2*LN(Haltedauer)+0.667),0)</f>
@@ -24602,7 +24602,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>20</v>
@@ -25154,7 +25154,7 @@
         <v>11</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C55" s="283">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis3-Gesamtpreis3*(-0.2*LN(Haltedauer)+0.667),0)</f>
@@ -25610,13 +25610,13 @@
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{651615EB-DE44-4BF4-BD1E-846AB7A3DA36}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="5e4dc333-02c0-4d6f-a03d-d04a548a7be7"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>

--- a/src/assets/downloads/LZK-Rechner_LNF_V1.0_Beispiel.xlsx
+++ b/src/assets/downloads/LZK-Rechner_LNF_V1.0_Beispiel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ifeu2.sharepoint.com/sites/DBUBeschaffungBerlin/Freigegebene Dokumente/General/Folgeprojekt/03_Arbeitsdokumente/B2 - LZK-Rechner LNF/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="8_{7D517AF7-4619-43FA-847D-E38F8B66F015}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{1AEC688A-F306-4865-95FD-2095E607FE8B}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="8_{7D517AF7-4619-43FA-847D-E38F8B66F015}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{D064AF6B-52D0-415E-91D1-C2CBEDC80345}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" tabRatio="887" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12771,7 +12771,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="10143914" y="2432685"/>
+          <a:off x="10471574" y="2432685"/>
           <a:ext cx="1631979" cy="972820"/>
           <a:chOff x="8390255" y="2565400"/>
           <a:chExt cx="1643409" cy="965200"/>
@@ -19313,7 +19313,7 @@
     <col min="1" max="1" width="2.109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="5.109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="31.5546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.44140625" style="1" customWidth="1"/>
     <col min="5" max="9" width="16.77734375" style="1" customWidth="1"/>
     <col min="10" max="10" width="3.33203125" style="1" customWidth="1"/>
     <col min="11" max="11" width="7.109375" style="7" customWidth="1"/>
@@ -19632,7 +19632,7 @@
         <v>Fahrzeuggesamtpreis (brutto)</v>
       </c>
       <c r="D14" s="166" t="str">
-        <f>IF(ISBLANK(FinArt), "Input_Projekt", VLOOKUP(FinArt,FinArtList,2,FALSE))</f>
+        <f>IF(ISBLANK(FinArt), "Input_Beschaffung", VLOOKUP(FinArt,FinArtList,2,FALSE))</f>
         <v>EUR</v>
       </c>
       <c r="E14" s="142">
@@ -25611,12 +25611,12 @@
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{651615EB-DE44-4BF4-BD1E-846AB7A3DA36}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="5e4dc333-02c0-4d6f-a03d-d04a548a7be7"/>
+    <ds:schemaRef ds:uri="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3"/>
+    <ds:schemaRef ds:uri="5e4dc333-02c0-4d6f-a03d-d04a548a7be7"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>

--- a/src/assets/downloads/LZK-Rechner_LNF_V1.0_Beispiel.xlsx
+++ b/src/assets/downloads/LZK-Rechner_LNF_V1.0_Beispiel.xlsx
@@ -5,12 +5,12 @@
   <workbookPr updateLinks="never"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ifeu2.sharepoint.com/sites/DBUBeschaffungBerlin/Freigegebene Dokumente/General/Folgeprojekt/03_Arbeitsdokumente/B2 - LZK-Rechner LNF/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Julia Pelzeter\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="8_{7D517AF7-4619-43FA-847D-E38F8B66F015}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{D064AF6B-52D0-415E-91D1-C2CBEDC80345}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{580FBBF9-6E3E-4F9E-B154-698BF741C0CB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" tabRatio="887" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="11124" tabRatio="887" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Anleitung" sheetId="27" r:id="rId1"/>
@@ -195,7 +195,7 @@
     <definedName name="Zusatzinfo5">Eingabe_Angebotswerte!$I$12</definedName>
     <definedName name="Zustaendig">Input_Beschaffung!$C$10</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterate="1" iterateCount="1000"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -2684,9 +2684,6 @@
     <t>UBA (2024b)</t>
   </si>
   <si>
-    <t>https://www.umweltbundesamt.de/sites/default/files/medien/11850/publikationen/23_2024_cc_strommix_07_2024.pdf</t>
-  </si>
-  <si>
     <t>Entwicklung der spezifischen Treibhausgas-Emissionen des deutschen Strommix in den Jahren 1990 - 2023</t>
   </si>
   <si>
@@ -3525,6 +3522,9 @@
       </rPr>
       <t>Es ist jedoch zu berücksichtigen, dass dadurch Berechnungsfehler entstehen können. Die Verantwortung liegt bei der Person, die den Rechner angepasst hat.</t>
     </r>
+  </si>
+  <si>
+    <t>https://www.umweltbundesamt.de/publikationen/entwicklung-der-spezifischen-treibhausgas-10</t>
   </si>
 </sst>
 </file>
@@ -4900,7 +4900,7 @@
     <xf numFmtId="166" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="474">
+  <cellXfs count="473">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5524,9 +5524,6 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5839,6 +5836,15 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
@@ -5873,15 +5879,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="13" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
@@ -6027,65 +6024,65 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -12771,8 +12768,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="10471574" y="2432685"/>
-          <a:ext cx="1631979" cy="972820"/>
+          <a:off x="10479194" y="2392680"/>
+          <a:ext cx="1630074" cy="969010"/>
           <a:chOff x="8390255" y="2565400"/>
           <a:chExt cx="1643409" cy="965200"/>
         </a:xfrm>
@@ -14366,7 +14363,7 @@
   <sheetData>
     <row r="2" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B2" s="16" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C2" s="16"/>
       <c r="D2" s="16"/>
@@ -14376,7 +14373,7 @@
       <c r="H2" s="16"/>
       <c r="I2" s="16"/>
       <c r="J2" s="268" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.25">
@@ -14398,17 +14395,17 @@
       <c r="J4" s="115"/>
     </row>
     <row r="5" spans="2:10" ht="163.19999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="391" t="s">
-        <v>529</v>
-      </c>
-      <c r="C5" s="391"/>
-      <c r="D5" s="391"/>
-      <c r="E5" s="391"/>
-      <c r="F5" s="391"/>
-      <c r="G5" s="391"/>
-      <c r="H5" s="391"/>
-      <c r="I5" s="391"/>
-      <c r="J5" s="391"/>
+      <c r="B5" s="393" t="s">
+        <v>528</v>
+      </c>
+      <c r="C5" s="393"/>
+      <c r="D5" s="393"/>
+      <c r="E5" s="393"/>
+      <c r="F5" s="393"/>
+      <c r="G5" s="393"/>
+      <c r="H5" s="393"/>
+      <c r="I5" s="393"/>
+      <c r="J5" s="393"/>
     </row>
     <row r="6" spans="2:10" ht="11.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="245"/>
@@ -14446,13 +14443,13 @@
     <row r="9" spans="2:10" ht="52.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D9" s="245"/>
       <c r="E9" s="245"/>
-      <c r="F9" s="392" t="s">
+      <c r="F9" s="394" t="s">
         <v>410</v>
       </c>
-      <c r="G9" s="392"/>
-      <c r="H9" s="392"/>
-      <c r="I9" s="392"/>
-      <c r="J9" s="392"/>
+      <c r="G9" s="394"/>
+      <c r="H9" s="394"/>
+      <c r="I9" s="394"/>
+      <c r="J9" s="394"/>
     </row>
     <row r="10" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D10" s="245"/>
@@ -14466,31 +14463,31 @@
     <row r="11" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D11" s="245"/>
       <c r="E11" s="245"/>
-      <c r="F11" s="393" t="s">
-        <v>425</v>
-      </c>
-      <c r="G11" s="394"/>
-      <c r="H11" s="394"/>
-      <c r="I11" s="394"/>
-      <c r="J11" s="394"/>
+      <c r="F11" s="395" t="s">
+        <v>424</v>
+      </c>
+      <c r="G11" s="396"/>
+      <c r="H11" s="396"/>
+      <c r="I11" s="396"/>
+      <c r="J11" s="396"/>
     </row>
     <row r="12" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D12" s="245"/>
       <c r="E12" s="245"/>
-      <c r="F12" s="394"/>
-      <c r="G12" s="394"/>
-      <c r="H12" s="394"/>
-      <c r="I12" s="394"/>
-      <c r="J12" s="394"/>
+      <c r="F12" s="396"/>
+      <c r="G12" s="396"/>
+      <c r="H12" s="396"/>
+      <c r="I12" s="396"/>
+      <c r="J12" s="396"/>
     </row>
     <row r="13" spans="2:10" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D13" s="245"/>
       <c r="E13" s="245"/>
-      <c r="F13" s="394"/>
-      <c r="G13" s="394"/>
-      <c r="H13" s="394"/>
-      <c r="I13" s="394"/>
-      <c r="J13" s="394"/>
+      <c r="F13" s="396"/>
+      <c r="G13" s="396"/>
+      <c r="H13" s="396"/>
+      <c r="I13" s="396"/>
+      <c r="J13" s="396"/>
     </row>
     <row r="14" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D14" s="245"/>
@@ -14504,22 +14501,22 @@
     <row r="15" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D15" s="245"/>
       <c r="E15" s="245"/>
-      <c r="F15" s="395" t="s">
+      <c r="F15" s="397" t="s">
         <v>1</v>
       </c>
-      <c r="G15" s="396"/>
-      <c r="H15" s="396"/>
-      <c r="I15" s="396"/>
-      <c r="J15" s="396"/>
+      <c r="G15" s="398"/>
+      <c r="H15" s="398"/>
+      <c r="I15" s="398"/>
+      <c r="J15" s="398"/>
     </row>
     <row r="16" spans="2:10" ht="73.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D16" s="245"/>
       <c r="E16" s="245"/>
-      <c r="F16" s="396"/>
-      <c r="G16" s="396"/>
-      <c r="H16" s="396"/>
-      <c r="I16" s="396"/>
-      <c r="J16" s="396"/>
+      <c r="F16" s="398"/>
+      <c r="G16" s="398"/>
+      <c r="H16" s="398"/>
+      <c r="I16" s="398"/>
+      <c r="J16" s="398"/>
     </row>
     <row r="17" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D17" s="245"/>
@@ -14533,13 +14530,13 @@
     <row r="18" spans="2:10" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D18" s="245"/>
       <c r="E18" s="245"/>
-      <c r="F18" s="397" t="s">
+      <c r="F18" s="399" t="s">
         <v>2</v>
       </c>
-      <c r="G18" s="398"/>
-      <c r="H18" s="398"/>
-      <c r="I18" s="398"/>
-      <c r="J18" s="398"/>
+      <c r="G18" s="400"/>
+      <c r="H18" s="400"/>
+      <c r="I18" s="400"/>
+      <c r="J18" s="400"/>
     </row>
     <row r="19" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D19" s="245"/>
@@ -14553,31 +14550,31 @@
     <row r="20" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D20" s="245"/>
       <c r="E20" s="245"/>
-      <c r="F20" s="399" t="s">
+      <c r="F20" s="401" t="s">
         <v>3</v>
       </c>
-      <c r="G20" s="399"/>
-      <c r="H20" s="399"/>
-      <c r="I20" s="399"/>
-      <c r="J20" s="399"/>
+      <c r="G20" s="401"/>
+      <c r="H20" s="401"/>
+      <c r="I20" s="401"/>
+      <c r="J20" s="401"/>
     </row>
     <row r="21" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D21" s="245"/>
       <c r="E21" s="245"/>
-      <c r="F21" s="399"/>
-      <c r="G21" s="399"/>
-      <c r="H21" s="399"/>
-      <c r="I21" s="399"/>
-      <c r="J21" s="399"/>
+      <c r="F21" s="401"/>
+      <c r="G21" s="401"/>
+      <c r="H21" s="401"/>
+      <c r="I21" s="401"/>
+      <c r="J21" s="401"/>
     </row>
     <row r="22" spans="2:10" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D22" s="245"/>
       <c r="E22" s="245"/>
-      <c r="F22" s="399"/>
-      <c r="G22" s="399"/>
-      <c r="H22" s="399"/>
-      <c r="I22" s="399"/>
-      <c r="J22" s="399"/>
+      <c r="F22" s="401"/>
+      <c r="G22" s="401"/>
+      <c r="H22" s="401"/>
+      <c r="I22" s="401"/>
+      <c r="J22" s="401"/>
     </row>
     <row r="23" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D23" s="245"/>
@@ -14591,22 +14588,22 @@
     <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D24" s="245"/>
       <c r="E24" s="245"/>
-      <c r="F24" s="400" t="s">
+      <c r="F24" s="402" t="s">
         <v>4</v>
       </c>
-      <c r="G24" s="400"/>
-      <c r="H24" s="400"/>
-      <c r="I24" s="400"/>
-      <c r="J24" s="400"/>
+      <c r="G24" s="402"/>
+      <c r="H24" s="402"/>
+      <c r="I24" s="402"/>
+      <c r="J24" s="402"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D25" s="245"/>
       <c r="E25" s="245"/>
-      <c r="F25" s="400"/>
-      <c r="G25" s="400"/>
-      <c r="H25" s="400"/>
-      <c r="I25" s="400"/>
-      <c r="J25" s="400"/>
+      <c r="F25" s="402"/>
+      <c r="G25" s="402"/>
+      <c r="H25" s="402"/>
+      <c r="I25" s="402"/>
+      <c r="J25" s="402"/>
     </row>
     <row r="26" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="245"/>
@@ -14620,49 +14617,49 @@
     <row r="27" spans="2:10" ht="7.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D27" s="245"/>
       <c r="E27" s="245"/>
-      <c r="F27" s="390"/>
-      <c r="G27" s="390"/>
-      <c r="H27" s="390"/>
-      <c r="I27" s="390"/>
-      <c r="J27" s="390"/>
+      <c r="F27" s="392"/>
+      <c r="G27" s="392"/>
+      <c r="H27" s="392"/>
+      <c r="I27" s="392"/>
+      <c r="J27" s="392"/>
     </row>
     <row r="28" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D28" s="245"/>
       <c r="E28" s="245"/>
-      <c r="F28" s="401" t="s">
-        <v>426</v>
-      </c>
-      <c r="G28" s="401"/>
-      <c r="H28" s="401"/>
-      <c r="I28" s="401"/>
-      <c r="J28" s="401"/>
+      <c r="F28" s="403" t="s">
+        <v>425</v>
+      </c>
+      <c r="G28" s="403"/>
+      <c r="H28" s="403"/>
+      <c r="I28" s="403"/>
+      <c r="J28" s="403"/>
     </row>
     <row r="29" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D29" s="245"/>
       <c r="E29" s="245"/>
-      <c r="F29" s="401"/>
-      <c r="G29" s="401"/>
-      <c r="H29" s="401"/>
-      <c r="I29" s="401"/>
-      <c r="J29" s="401"/>
+      <c r="F29" s="403"/>
+      <c r="G29" s="403"/>
+      <c r="H29" s="403"/>
+      <c r="I29" s="403"/>
+      <c r="J29" s="403"/>
     </row>
     <row r="30" spans="2:10" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D30" s="245"/>
       <c r="E30" s="245"/>
-      <c r="F30" s="401"/>
-      <c r="G30" s="401"/>
-      <c r="H30" s="401"/>
-      <c r="I30" s="401"/>
-      <c r="J30" s="401"/>
+      <c r="F30" s="403"/>
+      <c r="G30" s="403"/>
+      <c r="H30" s="403"/>
+      <c r="I30" s="403"/>
+      <c r="J30" s="403"/>
     </row>
     <row r="31" spans="2:10" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D31" s="245"/>
       <c r="E31" s="245"/>
-      <c r="F31" s="402"/>
-      <c r="G31" s="402"/>
-      <c r="H31" s="402"/>
-      <c r="I31" s="402"/>
-      <c r="J31" s="402"/>
+      <c r="F31" s="391"/>
+      <c r="G31" s="391"/>
+      <c r="H31" s="391"/>
+      <c r="I31" s="391"/>
+      <c r="J31" s="391"/>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="250" t="s">
@@ -14711,15 +14708,15 @@
     <row r="36" spans="2:11" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="116"/>
       <c r="C36" s="113"/>
-      <c r="D36" s="402" t="s">
+      <c r="D36" s="391" t="s">
         <v>7</v>
       </c>
-      <c r="E36" s="402"/>
-      <c r="F36" s="402"/>
-      <c r="G36" s="402"/>
-      <c r="H36" s="402"/>
-      <c r="I36" s="402"/>
-      <c r="J36" s="402"/>
+      <c r="E36" s="391"/>
+      <c r="F36" s="391"/>
+      <c r="G36" s="391"/>
+      <c r="H36" s="391"/>
+      <c r="I36" s="391"/>
+      <c r="J36" s="391"/>
     </row>
     <row r="37" spans="2:11" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="117"/>
@@ -14735,24 +14732,24 @@
     <row r="38" spans="2:11" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="241"/>
       <c r="C38" s="113"/>
-      <c r="D38" s="390" t="s">
+      <c r="D38" s="392" t="s">
         <v>8</v>
       </c>
-      <c r="E38" s="390"/>
-      <c r="F38" s="390"/>
-      <c r="G38" s="390"/>
-      <c r="H38" s="390"/>
-      <c r="I38" s="390"/>
-      <c r="J38" s="390"/>
+      <c r="E38" s="392"/>
+      <c r="F38" s="392"/>
+      <c r="G38" s="392"/>
+      <c r="H38" s="392"/>
+      <c r="I38" s="392"/>
+      <c r="J38" s="392"/>
     </row>
     <row r="39" spans="2:11" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D39" s="390"/>
-      <c r="E39" s="390"/>
-      <c r="F39" s="390"/>
-      <c r="G39" s="390"/>
-      <c r="H39" s="390"/>
-      <c r="I39" s="390"/>
-      <c r="J39" s="390"/>
+      <c r="D39" s="392"/>
+      <c r="E39" s="392"/>
+      <c r="F39" s="392"/>
+      <c r="G39" s="392"/>
+      <c r="H39" s="392"/>
+      <c r="I39" s="392"/>
+      <c r="J39" s="392"/>
     </row>
     <row r="40" spans="2:11" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="117"/>
@@ -14770,15 +14767,15 @@
         <v>9</v>
       </c>
       <c r="C41" s="113"/>
-      <c r="D41" s="403" t="s">
+      <c r="D41" s="389" t="s">
         <v>10</v>
       </c>
-      <c r="E41" s="403"/>
-      <c r="F41" s="403"/>
-      <c r="G41" s="403"/>
-      <c r="H41" s="403"/>
-      <c r="I41" s="403"/>
-      <c r="J41" s="403"/>
+      <c r="E41" s="389"/>
+      <c r="F41" s="389"/>
+      <c r="G41" s="389"/>
+      <c r="H41" s="389"/>
+      <c r="I41" s="389"/>
+      <c r="J41" s="389"/>
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" s="113"/>
@@ -14792,30 +14789,30 @@
       <c r="J42" s="245"/>
     </row>
     <row r="43" spans="2:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="404" t="s">
+      <c r="B43" s="390" t="s">
         <v>11</v>
       </c>
       <c r="C43" s="103"/>
-      <c r="D43" s="402" t="s">
+      <c r="D43" s="391" t="s">
         <v>12</v>
       </c>
-      <c r="E43" s="402"/>
-      <c r="F43" s="402"/>
-      <c r="G43" s="402"/>
-      <c r="H43" s="402"/>
-      <c r="I43" s="402"/>
-      <c r="J43" s="402"/>
+      <c r="E43" s="391"/>
+      <c r="F43" s="391"/>
+      <c r="G43" s="391"/>
+      <c r="H43" s="391"/>
+      <c r="I43" s="391"/>
+      <c r="J43" s="391"/>
     </row>
     <row r="44" spans="2:11" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="B44" s="404"/>
+      <c r="B44" s="390"/>
       <c r="C44" s="103"/>
-      <c r="D44" s="402"/>
-      <c r="E44" s="402"/>
-      <c r="F44" s="402"/>
-      <c r="G44" s="402"/>
-      <c r="H44" s="402"/>
-      <c r="I44" s="402"/>
-      <c r="J44" s="402"/>
+      <c r="D44" s="391"/>
+      <c r="E44" s="391"/>
+      <c r="F44" s="391"/>
+      <c r="G44" s="391"/>
+      <c r="H44" s="391"/>
+      <c r="I44" s="391"/>
+      <c r="J44" s="391"/>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="D45" s="112"/>
@@ -14827,17 +14824,17 @@
       <c r="J45" s="114"/>
     </row>
     <row r="46" spans="2:11" ht="58.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="402" t="s">
-        <v>632</v>
-      </c>
-      <c r="C46" s="402"/>
-      <c r="D46" s="402"/>
-      <c r="E46" s="402"/>
-      <c r="F46" s="402"/>
-      <c r="G46" s="402"/>
-      <c r="H46" s="402"/>
-      <c r="I46" s="402"/>
-      <c r="J46" s="402"/>
+      <c r="B46" s="391" t="s">
+        <v>631</v>
+      </c>
+      <c r="C46" s="391"/>
+      <c r="D46" s="391"/>
+      <c r="E46" s="391"/>
+      <c r="F46" s="391"/>
+      <c r="G46" s="391"/>
+      <c r="H46" s="391"/>
+      <c r="I46" s="391"/>
+      <c r="J46" s="391"/>
       <c r="K46" s="107"/>
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.25">
@@ -14872,17 +14869,17 @@
       <c r="J49" s="112"/>
     </row>
     <row r="50" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="402" t="s">
+      <c r="B50" s="391" t="s">
         <v>14</v>
       </c>
-      <c r="C50" s="402"/>
-      <c r="D50" s="402"/>
-      <c r="E50" s="402"/>
-      <c r="F50" s="402"/>
-      <c r="G50" s="402"/>
-      <c r="H50" s="402"/>
-      <c r="I50" s="402"/>
-      <c r="J50" s="402"/>
+      <c r="C50" s="391"/>
+      <c r="D50" s="391"/>
+      <c r="E50" s="391"/>
+      <c r="F50" s="391"/>
+      <c r="G50" s="391"/>
+      <c r="H50" s="391"/>
+      <c r="I50" s="391"/>
+      <c r="J50" s="391"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D51" s="114"/>
@@ -14945,11 +14942,6 @@
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="17">
-    <mergeCell ref="D41:J41"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="D43:J44"/>
-    <mergeCell ref="B46:J46"/>
-    <mergeCell ref="B50:J50"/>
     <mergeCell ref="D38:J39"/>
     <mergeCell ref="B5:J5"/>
     <mergeCell ref="F9:J9"/>
@@ -14962,6 +14954,11 @@
     <mergeCell ref="F28:J30"/>
     <mergeCell ref="F31:J31"/>
     <mergeCell ref="D36:J36"/>
+    <mergeCell ref="D41:J41"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="D43:J44"/>
+    <mergeCell ref="B46:J46"/>
+    <mergeCell ref="B50:J50"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F9:J9" location="Input_Beschaffung!A1" display="Geben Sie die übergeordneten Informationen zu Ihrem Beschaffungsfall ein. Hier können Informationen wie die erwartete jährliche Fahrleistung, die Art der Beschaffung (Kauf/Leasing) und weitere Informationen eingegeben werden." xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -15003,7 +15000,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>20</v>
@@ -15156,7 +15153,7 @@
       <c r="B18" s="72" t="s">
         <v>143</v>
       </c>
-      <c r="C18" s="288">
+      <c r="C18" s="287">
         <f>0.0057*(ReichwPHEV4/23)^3-0.0838*(ReichwPHEV4/23)^2+0.4261*(ReichwPHEV4/23)+ 0.1633</f>
         <v>0.1633</v>
       </c>
@@ -15168,7 +15165,7 @@
       <c r="B19" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C19" s="289">
+      <c r="C19" s="288">
         <f>Verbrauch4/(1-0.9*C18)</f>
         <v>0</v>
       </c>
@@ -15182,7 +15179,7 @@
       <c r="B20" s="72" t="s">
         <v>145</v>
       </c>
-      <c r="C20" s="290">
+      <c r="C20" s="289">
         <f>VerbEl_WLTP4/C18</f>
         <v>152.48009797917942</v>
       </c>
@@ -15196,7 +15193,7 @@
       <c r="B21" s="186" t="s">
         <v>146</v>
       </c>
-      <c r="C21" s="291">
+      <c r="C21" s="290">
         <f>0.0021*(ReichwPHEV4/23)^3-0.0358*(ReichwPHEV4/23)^2+0.2607*(ReichwPHEV4/23)- 0.0267</f>
         <v>-2.6700000000000002E-2</v>
       </c>
@@ -15205,13 +15202,13 @@
       <c r="F21" s="125"/>
     </row>
     <row r="22" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="471" t="s">
+      <c r="A22" s="470" t="s">
         <v>11</v>
       </c>
-      <c r="B22" s="470" t="s">
+      <c r="B22" s="469" t="s">
         <v>147</v>
       </c>
-      <c r="C22" s="292">
+      <c r="C22" s="291">
         <f>C19*(1-0.9*C21)</f>
         <v>0</v>
       </c>
@@ -15222,9 +15219,9 @@
       <c r="F22" s="125"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="471"/>
-      <c r="B23" s="430"/>
-      <c r="C23" s="292">
+      <c r="A23" s="470"/>
+      <c r="B23" s="429"/>
+      <c r="C23" s="291">
         <f>C20*C21</f>
         <v>-4.0712186160440904</v>
       </c>
@@ -15265,7 +15262,7 @@
       <c r="B28" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C28" s="279">
+      <c r="C28" s="278">
         <f>IF(Antriebsart4="Vollelektrisch (BEV)",0,IFERROR(VLOOKUP(Energie4,EnKostList,8,FALSE),0)*IF(Antriebsart4="Plug-In-Hybrid (PHEV)",VerbPHEV4,Verbrauch4)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
@@ -15279,7 +15276,7 @@
       <c r="B29" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C29" s="279">
+      <c r="C29" s="278">
         <f>IF(Antriebsart4="Verbrenner",0,VLOOKUP("Strom",EnKostList,8,FALSE)*IF(Antriebsart4="Plug-In-Hybrid (PHEV)",VerbElPHEV4,VerbEl_WLTP4)/100*Fahrleistung)</f>
         <v>3124.95</v>
       </c>
@@ -15293,7 +15290,7 @@
       <c r="B30" s="64" t="s">
         <v>91</v>
       </c>
-      <c r="C30" s="280">
+      <c r="C30" s="279">
         <f>SUM(C28:C29)</f>
         <v>3124.95</v>
       </c>
@@ -15325,7 +15322,7 @@
       <c r="B33" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C33" s="279">
+      <c r="C33" s="278">
         <f>IF(Antriebsart4="Plug-In-Hybrid (PHEV)",VerbPHEV4*VLOOKUP(Energie4,CO2List,2,FALSE)/100,CO2_4)*Fahrleistung/1000000</f>
         <v>0</v>
       </c>
@@ -15339,7 +15336,7 @@
       <c r="B34" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C34" s="279">
+      <c r="C34" s="278">
         <f>C33*Kost_THG</f>
         <v>0</v>
       </c>
@@ -15353,7 +15350,7 @@
       <c r="B35" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="C35" s="287">
+      <c r="C35" s="286">
         <f>IF(Energie4="Strom",0,NOX_4*Fahrleistung*Kost_NOX/1000)</f>
         <v>0</v>
       </c>
@@ -15367,7 +15364,7 @@
       <c r="B36" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="C36" s="287">
+      <c r="C36" s="286">
         <f>IF(Energie4="Strom",0,Partikel4*Fahrleistung*Kost_Partikel/1000)</f>
         <v>0</v>
       </c>
@@ -15381,7 +15378,7 @@
       <c r="B37" s="64" t="s">
         <v>91</v>
       </c>
-      <c r="C37" s="280">
+      <c r="C37" s="279">
         <f>SUM(C34:C36)</f>
         <v>0</v>
       </c>
@@ -15413,7 +15410,7 @@
       <c r="B40" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C40" s="279">
+      <c r="C40" s="278">
         <f>IFERROR(IF(Antriebsart4="Vollelektrisch (BEV)",VLOOKUP("Strom",CO2List,3,FALSE)*VerbEl_WLTP4/100*Fahrleistung/1000000,IF(Antriebsart4="Verbrenner",VLOOKUP(Energie4,CO2List,3,FALSE)*Verbrauch4/100*Fahrleistung/1000000,VLOOKUP(Energie4,CO2List,3,FALSE)*VerbPHEV4/100*Fahrleistung/1000000+VLOOKUP("Strom",CO2List,3,FALSE)*VerbElPHEV4/100*Fahrleistung/1000000)),0)</f>
         <v>1.8114749999999993</v>
       </c>
@@ -15427,7 +15424,7 @@
       <c r="B41" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C41" s="279">
+      <c r="C41" s="278">
         <f>C40*Kost_THG</f>
         <v>1557.8684999999994</v>
       </c>
@@ -15470,13 +15467,13 @@
       <c r="F45" s="125"/>
     </row>
     <row r="46" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A46" s="404" t="s">
+      <c r="A46" s="390" t="s">
         <v>11</v>
       </c>
-      <c r="B46" s="468" t="s">
+      <c r="B46" s="467" t="s">
         <v>152</v>
       </c>
-      <c r="C46" s="281">
+      <c r="C46" s="280">
         <f>IF(OR(Antriebsart4="Vollelektrisch (BEV)",Antriebsart4="Plug-In-Hybrid (PHEV)"),Batterie4*Batterie_THG/1000,0)</f>
         <v>4.2</v>
       </c>
@@ -15487,9 +15484,9 @@
       <c r="F46" s="125"/>
     </row>
     <row r="47" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="404"/>
-      <c r="B47" s="469"/>
-      <c r="C47" s="281">
+      <c r="A47" s="390"/>
+      <c r="B47" s="468"/>
+      <c r="C47" s="280">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
         <v>19.09090909090909</v>
       </c>
@@ -15503,7 +15500,7 @@
       <c r="B48" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C48" s="279">
+      <c r="C48" s="278">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Kost_THG, C46/Haltedauer*Kost_THG)</f>
         <v>410.45454545454544</v>
       </c>
@@ -15540,7 +15537,7 @@
       <c r="B54" s="68" t="s">
         <v>164</v>
       </c>
-      <c r="C54" s="282">
+      <c r="C54" s="281">
         <f>IF(FinArt="Kauf",IF(KaufpreisRech="Kaufpreis",Gesamtpreis4,0),Gesamtpreis4*Haltedauer*12+IF(FinArt="Leasing",LeasSondZahl4,0))</f>
         <v>0</v>
       </c>
@@ -15551,13 +15548,13 @@
       <c r="F54" s="58"/>
     </row>
     <row r="55" spans="1:6" s="71" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A55" s="305" t="s">
+      <c r="A55" s="304" t="s">
         <v>11</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="C55" s="283">
+        <v>438</v>
+      </c>
+      <c r="C55" s="282">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis4-Gesamtpreis4*(-0.2*LN(Haltedauer)+0.667),0)</f>
         <v>33044.160956034983</v>
       </c>
@@ -15571,7 +15568,7 @@
       <c r="B56" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C56" s="283">
+      <c r="C56" s="282">
         <f>C30*Haltedauer</f>
         <v>21874.649999999998</v>
       </c>
@@ -15584,7 +15581,7 @@
       <c r="B57" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C57" s="283">
+      <c r="C57" s="282">
         <f>C37*Haltedauer</f>
         <v>0</v>
       </c>
@@ -15597,7 +15594,7 @@
       <c r="B58" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C58" s="283">
+      <c r="C58" s="282">
         <f>C41*Haltedauer</f>
         <v>10905.079499999996</v>
       </c>
@@ -15607,10 +15604,10 @@
       <c r="F58" s="58"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B59" s="333" t="s">
+      <c r="B59" s="332" t="s">
         <v>90</v>
       </c>
-      <c r="C59" s="334">
+      <c r="C59" s="333">
         <f>C48*Haltedauer</f>
         <v>2873.181818181818</v>
       </c>
@@ -15620,50 +15617,50 @@
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="404" t="s">
+      <c r="A60" s="390" t="s">
         <v>11</v>
       </c>
-      <c r="B60" s="327" t="str">
+      <c r="B60" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", Zusatzangabe_x)</f>
         <v>Kfz-Steuer</v>
       </c>
-      <c r="C60" s="328">
+      <c r="C60" s="327">
         <f>IF(ISBLANK(Zusatzangabe_x), "", Zusatzangabe_x4*Haltedauer)</f>
         <v>0</v>
       </c>
-      <c r="D60" s="327" t="str">
+      <c r="D60" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", "EUR")</f>
         <v>EUR</v>
       </c>
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="404"/>
-      <c r="B61" s="327" t="str">
+      <c r="A61" s="390"/>
+      <c r="B61" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
       </c>
-      <c r="C61" s="328" t="str">
+      <c r="C61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y4*Haltedauer)</f>
         <v/>
       </c>
-      <c r="D61" s="327" t="str">
+      <c r="D61" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", "EUR")</f>
         <v/>
       </c>
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="404"/>
-      <c r="B62" s="327" t="str">
+      <c r="A62" s="390"/>
+      <c r="B62" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
       </c>
-      <c r="C62" s="328" t="str">
+      <c r="C62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z4*Haltedauer)</f>
         <v/>
       </c>
-      <c r="D62" s="327" t="str">
+      <c r="D62" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", "EUR")</f>
         <v/>
       </c>
@@ -15673,7 +15670,7 @@
       <c r="B63" s="64" t="s">
         <v>91</v>
       </c>
-      <c r="C63" s="284">
+      <c r="C63" s="283">
         <f>SUM(C54:C62)</f>
         <v>68697.0722742168</v>
       </c>
@@ -15695,7 +15692,7 @@
       <c r="B65" s="68" t="s">
         <v>166</v>
       </c>
-      <c r="C65" s="285">
+      <c r="C65" s="284">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Haltedauer, C46)</f>
         <v>3.3409090909090908</v>
       </c>
@@ -15707,7 +15704,7 @@
       <c r="B66" s="72" t="s">
         <v>96</v>
       </c>
-      <c r="C66" s="286">
+      <c r="C66" s="285">
         <f>C33*Haltedauer+C40*Haltedauer</f>
         <v>12.680324999999995</v>
       </c>
@@ -15763,7 +15760,7 @@
     </row>
     <row r="2" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>20</v>
@@ -15919,7 +15916,7 @@
       <c r="B18" s="72" t="s">
         <v>143</v>
       </c>
-      <c r="C18" s="288">
+      <c r="C18" s="287">
         <f>0.0057*(ReichwPHEV5/23)^3-0.0838*(ReichwPHEV5/23)^2+0.4261*(ReichwPHEV5/23)+ 0.1633</f>
         <v>0.1633</v>
       </c>
@@ -15931,7 +15928,7 @@
       <c r="B19" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C19" s="289">
+      <c r="C19" s="288">
         <f>Verbrauch5/(1-0.9*C18)</f>
         <v>0</v>
       </c>
@@ -15945,7 +15942,7 @@
       <c r="B20" s="72" t="s">
         <v>145</v>
       </c>
-      <c r="C20" s="290">
+      <c r="C20" s="289">
         <f>VerbEl_WLTP5/C18</f>
         <v>113.90079608083283</v>
       </c>
@@ -15959,7 +15956,7 @@
       <c r="B21" s="186" t="s">
         <v>146</v>
       </c>
-      <c r="C21" s="291">
+      <c r="C21" s="290">
         <f>0.0021*(ReichwPHEV5/23)^3-0.0358*(ReichwPHEV5/23)^2+0.2607*(ReichwPHEV5/23)- 0.0267</f>
         <v>-2.6700000000000002E-2</v>
       </c>
@@ -15968,13 +15965,13 @@
       <c r="F21" s="125"/>
     </row>
     <row r="22" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="471" t="s">
+      <c r="A22" s="470" t="s">
         <v>11</v>
       </c>
-      <c r="B22" s="470" t="s">
+      <c r="B22" s="469" t="s">
         <v>147</v>
       </c>
-      <c r="C22" s="292">
+      <c r="C22" s="291">
         <f>C19*(1-0.9*C21)</f>
         <v>0</v>
       </c>
@@ -15985,9 +15982,9 @@
       <c r="F22" s="125"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="471"/>
-      <c r="B23" s="430"/>
-      <c r="C23" s="292">
+      <c r="A23" s="470"/>
+      <c r="B23" s="429"/>
+      <c r="C23" s="291">
         <f>C20*C21</f>
         <v>-3.0411512553582369</v>
       </c>
@@ -16028,7 +16025,7 @@
       <c r="B28" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C28" s="279">
+      <c r="C28" s="278">
         <f>IF(Antriebsart5="Vollelektrisch (BEV)",0,IFERROR(VLOOKUP(Energie5,EnKostList,8,FALSE),0)*IF(Antriebsart5="Plug-In-Hybrid (PHEV)",VerbPHEV5,Verbrauch5)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
@@ -16042,7 +16039,7 @@
       <c r="B29" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C29" s="279">
+      <c r="C29" s="278">
         <f>IF(Antriebsart5="Verbrenner",0,VLOOKUP("Strom",EnKostList,8,FALSE)*IF(Antriebsart5="Plug-In-Hybrid (PHEV)",VerbElPHEV5,VerbEl_WLTP5)/100*Fahrleistung)</f>
         <v>2334.3000000000002</v>
       </c>
@@ -16056,7 +16053,7 @@
       <c r="B30" s="64" t="s">
         <v>91</v>
       </c>
-      <c r="C30" s="280">
+      <c r="C30" s="279">
         <f>SUM(C28:C29)</f>
         <v>2334.3000000000002</v>
       </c>
@@ -16089,7 +16086,7 @@
       <c r="B33" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C33" s="279">
+      <c r="C33" s="278">
         <f>IF(Antriebsart5="Plug-In-Hybrid (PHEV)",VerbPHEV5*VLOOKUP(Energie5,CO2List,2,FALSE)/100,CO2_5)*Fahrleistung/1000000</f>
         <v>0</v>
       </c>
@@ -16103,7 +16100,7 @@
       <c r="B34" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C34" s="279">
+      <c r="C34" s="278">
         <f>C33*Kost_THG</f>
         <v>0</v>
       </c>
@@ -16117,7 +16114,7 @@
       <c r="B35" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="C35" s="287">
+      <c r="C35" s="286">
         <f>IF(Energie5="Strom",0,NOX_5*Fahrleistung*Kost_NOX/1000)</f>
         <v>0</v>
       </c>
@@ -16131,7 +16128,7 @@
       <c r="B36" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="C36" s="287">
+      <c r="C36" s="286">
         <f>IF(Energie5="Strom",0,Partikel5*Fahrleistung*Kost_Partikel/1000)</f>
         <v>0</v>
       </c>
@@ -16145,7 +16142,7 @@
       <c r="B37" s="64" t="s">
         <v>91</v>
       </c>
-      <c r="C37" s="280">
+      <c r="C37" s="279">
         <f>SUM(C34:C36)</f>
         <v>0</v>
       </c>
@@ -16177,7 +16174,7 @@
       <c r="B40" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C40" s="279">
+      <c r="C40" s="278">
         <f>IFERROR(IF(Antriebsart5="Vollelektrisch (BEV)",VLOOKUP("Strom",CO2List,3,FALSE)*VerbEl_WLTP5/100*Fahrleistung/1000000,IF(Antriebsart5="Verbrenner",VLOOKUP(Energie5,CO2List,3,FALSE)*Verbrauch5/100*Fahrleistung/1000000,VLOOKUP(Energie5,CO2List,3,FALSE)*VerbPHEV5/100*Fahrleistung/1000000+VLOOKUP("Strom",CO2List,3,FALSE)*VerbElPHEV5/100*Fahrleistung/1000000)),0)</f>
         <v>1.3531500000000001</v>
       </c>
@@ -16191,7 +16188,7 @@
       <c r="B41" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C41" s="279">
+      <c r="C41" s="278">
         <f>C40*Kost_THG</f>
         <v>1163.7090000000001</v>
       </c>
@@ -16234,13 +16231,13 @@
       <c r="F45" s="125"/>
     </row>
     <row r="46" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A46" s="404" t="s">
+      <c r="A46" s="390" t="s">
         <v>11</v>
       </c>
-      <c r="B46" s="468" t="s">
+      <c r="B46" s="467" t="s">
         <v>152</v>
       </c>
-      <c r="C46" s="281">
+      <c r="C46" s="280">
         <f>IF(OR(Antriebsart5="Vollelektrisch (BEV)",Antriebsart5="Plug-In-Hybrid (PHEV)"),Batterie5*Batterie_THG/1000,0)</f>
         <v>6.3</v>
       </c>
@@ -16251,9 +16248,9 @@
       <c r="F46" s="125"/>
     </row>
     <row r="47" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="404"/>
-      <c r="B47" s="469"/>
-      <c r="C47" s="281">
+      <c r="A47" s="390"/>
+      <c r="B47" s="468"/>
+      <c r="C47" s="280">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
         <v>28.636363636363637</v>
       </c>
@@ -16267,7 +16264,7 @@
       <c r="B48" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C48" s="279">
+      <c r="C48" s="278">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Kost_THG, C46/Haltedauer*Kost_THG)</f>
         <v>615.68181818181824</v>
       </c>
@@ -16304,7 +16301,7 @@
       <c r="B54" s="68" t="s">
         <v>164</v>
       </c>
-      <c r="C54" s="282">
+      <c r="C54" s="281">
         <f>IF(FinArt="Kauf",IF(KaufpreisRech="Kaufpreis",Gesamtpreis5,0),Gesamtpreis5*Haltedauer*12+IF(FinArt="Leasing",LeasSondZahl5,0))</f>
         <v>0</v>
       </c>
@@ -16315,13 +16312,13 @@
       <c r="F54" s="58"/>
     </row>
     <row r="55" spans="1:6" s="71" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A55" s="305" t="s">
+      <c r="A55" s="304" t="s">
         <v>11</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="C55" s="283">
+        <v>438</v>
+      </c>
+      <c r="C55" s="282">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis5-Gesamtpreis5*(-0.2*LN(Haltedauer)+0.667),0)</f>
         <v>26805.952582527021</v>
       </c>
@@ -16335,7 +16332,7 @@
       <c r="B56" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C56" s="283">
+      <c r="C56" s="282">
         <f>C30*Haltedauer</f>
         <v>16340.100000000002</v>
       </c>
@@ -16348,7 +16345,7 @@
       <c r="B57" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C57" s="283">
+      <c r="C57" s="282">
         <f>C37*Haltedauer</f>
         <v>0</v>
       </c>
@@ -16361,7 +16358,7 @@
       <c r="B58" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C58" s="283">
+      <c r="C58" s="282">
         <f>C41*Haltedauer</f>
         <v>8145.9630000000006</v>
       </c>
@@ -16371,63 +16368,63 @@
       <c r="F58" s="58"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B59" s="329" t="s">
+      <c r="B59" s="328" t="s">
         <v>90</v>
       </c>
-      <c r="C59" s="330">
+      <c r="C59" s="329">
         <f>C48*Haltedauer</f>
         <v>4309.7727272727279</v>
       </c>
-      <c r="D59" s="329" t="s">
+      <c r="D59" s="328" t="s">
         <v>65</v>
       </c>
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="404" t="s">
+      <c r="A60" s="390" t="s">
         <v>11</v>
       </c>
-      <c r="B60" s="327" t="str">
+      <c r="B60" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", Zusatzangabe_x)</f>
         <v>Kfz-Steuer</v>
       </c>
-      <c r="C60" s="328">
+      <c r="C60" s="327">
         <f>IF(ISBLANK(Zusatzangabe_x), "", Zusatzangabe_x5*Haltedauer)</f>
         <v>0</v>
       </c>
-      <c r="D60" s="327" t="str">
+      <c r="D60" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", "EUR")</f>
         <v>EUR</v>
       </c>
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="404"/>
-      <c r="B61" s="327" t="str">
+      <c r="A61" s="390"/>
+      <c r="B61" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
       </c>
-      <c r="C61" s="328" t="str">
+      <c r="C61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y5*Haltedauer)</f>
         <v/>
       </c>
-      <c r="D61" s="327" t="str">
+      <c r="D61" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", "EUR")</f>
         <v/>
       </c>
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="404"/>
-      <c r="B62" s="327" t="str">
+      <c r="A62" s="390"/>
+      <c r="B62" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
       </c>
-      <c r="C62" s="328" t="str">
+      <c r="C62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z5*Haltedauer)</f>
         <v/>
       </c>
-      <c r="D62" s="327" t="str">
+      <c r="D62" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", "EUR")</f>
         <v/>
       </c>
@@ -16437,7 +16434,7 @@
       <c r="B63" s="64" t="s">
         <v>91</v>
       </c>
-      <c r="C63" s="284">
+      <c r="C63" s="283">
         <f>SUM(C54:C62)</f>
         <v>55601.788309799755</v>
       </c>
@@ -16459,7 +16456,7 @@
       <c r="B65" s="68" t="s">
         <v>166</v>
       </c>
-      <c r="C65" s="285">
+      <c r="C65" s="284">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Haltedauer, C46)</f>
         <v>5.0113636363636367</v>
       </c>
@@ -16471,7 +16468,7 @@
       <c r="B66" s="72" t="s">
         <v>96</v>
       </c>
-      <c r="C66" s="286">
+      <c r="C66" s="285">
         <f>C33*Haltedauer+C40*Haltedauer</f>
         <v>9.4720500000000012</v>
       </c>
@@ -16530,7 +16527,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B4" s="154" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
@@ -16552,7 +16549,7 @@
       <c r="B7" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C7" s="302">
+      <c r="C7" s="301">
         <v>74.027000000000001</v>
       </c>
       <c r="D7" s="10">
@@ -16566,7 +16563,7 @@
       <c r="B8" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C8" s="302">
+      <c r="C8" s="301">
         <v>72.787000000000006</v>
       </c>
       <c r="D8" s="10">
@@ -16580,7 +16577,7 @@
       <c r="B9" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C9" s="302">
+      <c r="C9" s="301">
         <v>56.220999999999997</v>
       </c>
       <c r="D9" s="10">
@@ -16592,7 +16589,7 @@
     </row>
     <row r="10" spans="1:9" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="92" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C10" s="10"/>
       <c r="D10" s="10"/>
@@ -16622,15 +16619,15 @@
       <c r="B14" s="110" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="472" t="s">
+      <c r="C14" s="471" t="s">
         <v>173</v>
       </c>
-      <c r="D14" s="472"/>
-      <c r="E14" s="473" t="s">
+      <c r="D14" s="471"/>
+      <c r="E14" s="472" t="s">
         <v>174</v>
       </c>
-      <c r="F14" s="473"/>
-      <c r="G14" s="304"/>
+      <c r="F14" s="472"/>
+      <c r="G14" s="303"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="66"/>
@@ -16684,7 +16681,7 @@
       <c r="D17" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="E17" s="303">
+      <c r="E17" s="302">
         <v>46.5</v>
       </c>
       <c r="F17" s="111" t="s">
@@ -16694,14 +16691,14 @@
     </row>
     <row r="18" spans="1:37" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="92" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D18" s="106"/>
       <c r="E18" s="10"/>
     </row>
     <row r="20" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B20" s="154" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
@@ -16723,7 +16720,7 @@
       <c r="L21" s="135"/>
       <c r="M21" s="135"/>
       <c r="O21" s="137" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="P21" s="137"/>
       <c r="Q21" s="137"/>
@@ -16752,7 +16749,7 @@
       <c r="C23" s="58">
         <v>0</v>
       </c>
-      <c r="D23" s="299">
+      <c r="D23" s="298">
         <f>SUMIFS(J24:AE24, J23:AE23, "&gt;=" &amp; Anschaffungsjahr, J23:AE23,  "&lt;" &amp; Anschaffungsjahr + ROUND(Haltedauer, 0))/ROUND(Haltedauer, 0)</f>
         <v>290.99999999999994</v>
       </c>
@@ -16865,15 +16862,15 @@
         <v>180</v>
       </c>
       <c r="I24" s="58" t="s">
-        <v>455</v>
-      </c>
-      <c r="J24" s="300">
+        <v>454</v>
+      </c>
+      <c r="J24" s="299">
         <v>445</v>
       </c>
       <c r="K24" s="96">
         <v>408</v>
       </c>
-      <c r="L24" s="301">
+      <c r="L24" s="300">
         <v>371</v>
       </c>
       <c r="M24" s="96">
@@ -16888,7 +16885,7 @@
       <c r="P24" s="96">
         <v>211.8</v>
       </c>
-      <c r="Q24" s="301">
+      <c r="Q24" s="300">
         <v>172</v>
       </c>
       <c r="R24" s="96">
@@ -16903,7 +16900,7 @@
       <c r="U24" s="96">
         <v>119.2</v>
       </c>
-      <c r="V24" s="301">
+      <c r="V24" s="300">
         <v>106</v>
       </c>
       <c r="W24" s="96">
@@ -16918,7 +16915,7 @@
       <c r="Z24" s="96">
         <v>82</v>
       </c>
-      <c r="AA24" s="301">
+      <c r="AA24" s="300">
         <v>76</v>
       </c>
       <c r="AB24" s="136">
@@ -16948,7 +16945,7 @@
       <c r="AJ24" s="136">
         <v>79.599999999999994</v>
       </c>
-      <c r="AK24" s="301">
+      <c r="AK24" s="300">
         <v>80</v>
       </c>
     </row>
@@ -17044,12 +17041,12 @@
     </row>
     <row r="39" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="234" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="40" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="234" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="41" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17065,12 +17062,12 @@
     </row>
     <row r="44" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="2" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="45" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="267" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="I45" s="106"/>
     </row>
@@ -17088,7 +17085,7 @@
         <v>409</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.25">
@@ -17096,7 +17093,7 @@
         <v>200</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.25">
@@ -17104,7 +17101,7 @@
         <v>201</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="53" spans="2:4" x14ac:dyDescent="0.25">
@@ -17112,7 +17109,7 @@
         <v>202</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.25">
@@ -17120,7 +17117,7 @@
         <v>30</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="55" spans="2:4" x14ac:dyDescent="0.25">
@@ -17128,7 +17125,7 @@
         <v>203</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.25">
@@ -17136,23 +17133,23 @@
         <v>204</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="57" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.25">
@@ -17160,15 +17157,15 @@
         <v>205</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="60" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B60" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>629</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>630</v>
       </c>
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.25">
@@ -17176,7 +17173,7 @@
         <v>206</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="62" spans="2:4" x14ac:dyDescent="0.25">
@@ -17264,7 +17261,7 @@
         <v>227</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="73" spans="2:4" x14ac:dyDescent="0.25">
@@ -17272,7 +17269,7 @@
         <v>229</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="74" spans="2:4" x14ac:dyDescent="0.25">
@@ -17280,7 +17277,7 @@
         <v>231</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="75" spans="2:4" x14ac:dyDescent="0.25">
@@ -17288,7 +17285,7 @@
         <v>233</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="76" spans="2:4" x14ac:dyDescent="0.25">
@@ -17296,7 +17293,7 @@
         <v>235</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="77" spans="2:4" x14ac:dyDescent="0.25">
@@ -17381,7 +17378,7 @@
     </row>
     <row r="87" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B87" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>258</v>
@@ -17389,7 +17386,7 @@
     </row>
     <row r="88" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B88" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>260</v>
@@ -17397,7 +17394,7 @@
     </row>
     <row r="89" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B89" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>262</v>
@@ -17405,7 +17402,7 @@
     </row>
     <row r="90" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B90" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>264</v>
@@ -17413,7 +17410,7 @@
     </row>
     <row r="91" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B91" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>266</v>
@@ -17781,146 +17778,146 @@
     </row>
     <row r="137" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B137" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="138" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B138" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="139" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B139" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="140" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B140" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="141" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B141" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="142" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B142" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="143" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B143" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="144" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B144" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="145" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B145" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="146" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B146" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="147" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B147" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="148" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B148" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="149" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B149" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="150" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B150" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="151" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B151" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="152" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B152" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="153" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B153" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="154" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B154" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="155" spans="2:4" x14ac:dyDescent="0.25">
@@ -17968,7 +17965,7 @@
         <v>374</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="161" spans="2:4" x14ac:dyDescent="0.25">
@@ -17976,7 +17973,7 @@
         <v>357</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="162" spans="2:4" x14ac:dyDescent="0.25">
@@ -17984,7 +17981,7 @@
         <v>358</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="163" spans="2:4" x14ac:dyDescent="0.25">
@@ -17992,7 +17989,7 @@
         <v>359</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="164" spans="2:4" x14ac:dyDescent="0.25">
@@ -18000,71 +17997,71 @@
         <v>360</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="165" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B165" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="166" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B166" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="167" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B167" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="168" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B168" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="D168" s="1" t="s">
         <v>603</v>
-      </c>
-      <c r="D168" s="1" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="169" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B169" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="D169" s="1" t="s">
         <v>605</v>
-      </c>
-      <c r="D169" s="1" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="170" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B170" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="171" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B171" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="D171" s="1" t="s">
         <v>608</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="172" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B172" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="173" spans="2:4" x14ac:dyDescent="0.25">
@@ -18072,63 +18069,63 @@
         <v>361</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="174" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B174" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="D174" s="1" t="s">
         <v>611</v>
-      </c>
-      <c r="D174" s="1" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="175" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B175" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="176" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B176" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="D176" s="1" t="s">
         <v>614</v>
-      </c>
-      <c r="D176" s="1" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="177" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B177" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="178" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B178" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="179" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B179" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="D179" s="1" t="s">
         <v>618</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="180" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B180" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="D180" s="1" t="s">
         <v>620</v>
-      </c>
-      <c r="D180" s="1" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="181" spans="2:4" x14ac:dyDescent="0.25">
@@ -18136,7 +18133,7 @@
         <v>362</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="182" spans="2:4" x14ac:dyDescent="0.25">
@@ -18144,7 +18141,7 @@
         <v>363</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="183" spans="2:4" x14ac:dyDescent="0.25">
@@ -18152,7 +18149,7 @@
         <v>189</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="184" spans="2:4" x14ac:dyDescent="0.25">
@@ -18160,7 +18157,7 @@
         <v>364</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="185" spans="2:4" x14ac:dyDescent="0.25">
@@ -18168,7 +18165,7 @@
         <v>369</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="186" spans="2:4" x14ac:dyDescent="0.25">
@@ -18176,7 +18173,7 @@
         <v>190</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="187" spans="2:4" x14ac:dyDescent="0.25">
@@ -18184,7 +18181,7 @@
         <v>365</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="188" spans="2:4" x14ac:dyDescent="0.25">
@@ -18192,7 +18189,7 @@
         <v>370</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="189" spans="2:4" x14ac:dyDescent="0.25">
@@ -18200,7 +18197,7 @@
         <v>191</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="190" spans="2:4" x14ac:dyDescent="0.25">
@@ -18208,7 +18205,7 @@
         <v>366</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="191" spans="2:4" x14ac:dyDescent="0.25">
@@ -18216,7 +18213,7 @@
         <v>371</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="192" spans="2:4" x14ac:dyDescent="0.25">
@@ -18224,7 +18221,7 @@
         <v>193</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="193" spans="2:4" x14ac:dyDescent="0.25">
@@ -18232,7 +18229,7 @@
         <v>367</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="194" spans="2:4" x14ac:dyDescent="0.25">
@@ -18240,7 +18237,7 @@
         <v>372</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="195" spans="2:4" x14ac:dyDescent="0.25">
@@ -18248,7 +18245,7 @@
         <v>194</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="196" spans="2:4" x14ac:dyDescent="0.25">
@@ -18256,7 +18253,7 @@
         <v>368</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="197" spans="2:4" x14ac:dyDescent="0.25">
@@ -18264,7 +18261,7 @@
         <v>373</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="198" spans="2:4" x14ac:dyDescent="0.25">
@@ -18272,7 +18269,7 @@
         <v>375</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="199" spans="2:4" x14ac:dyDescent="0.25">
@@ -18280,7 +18277,7 @@
         <v>376</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="200" spans="2:4" x14ac:dyDescent="0.25">
@@ -18288,7 +18285,7 @@
         <v>377</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="201" spans="2:4" x14ac:dyDescent="0.25">
@@ -18296,7 +18293,7 @@
         <v>378</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="202" spans="2:4" x14ac:dyDescent="0.25">
@@ -18312,7 +18309,7 @@
         <v>381</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="204" spans="2:4" x14ac:dyDescent="0.25">
@@ -18320,31 +18317,31 @@
         <v>382</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="205" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B205" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="D205" s="1" t="s">
         <v>622</v>
-      </c>
-      <c r="D205" s="1" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="206" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B206" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="D206" s="1" t="s">
         <v>624</v>
-      </c>
-      <c r="D206" s="1" t="s">
-        <v>625</v>
       </c>
     </row>
     <row r="207" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B207" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="D207" s="1" t="s">
         <v>626</v>
-      </c>
-      <c r="D207" s="1" t="s">
-        <v>627</v>
       </c>
     </row>
   </sheetData>
@@ -18476,7 +18473,7 @@
         <v>190</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.25">
@@ -18540,7 +18537,7 @@
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B29" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C29" s="3"/>
       <c r="D29" s="5"/>
@@ -18549,17 +18546,17 @@
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B30" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B33" s="3" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C33" s="3"/>
       <c r="D33" s="5"/>
@@ -18568,32 +18565,32 @@
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B35" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B36" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B37" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B38" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B40" s="3" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C40" s="3"/>
       <c r="D40" s="5"/>
@@ -18601,18 +18598,18 @@
       <c r="F40" s="5"/>
     </row>
     <row r="41" spans="2:6" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="B41" s="385" t="s">
+      <c r="B41" s="384" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="42" spans="2:6" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="B42" s="384" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="42" spans="2:6" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="B42" s="385" t="s">
+    <row r="43" spans="2:6" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="B43" s="384" t="s">
         <v>536</v>
-      </c>
-    </row>
-    <row r="43" spans="2:6" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="B43" s="385" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.25">
@@ -18664,164 +18661,164 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="275" t="s">
+    <row r="4" spans="2:5" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="274" t="s">
+        <v>447</v>
+      </c>
+      <c r="C4" s="274" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C5" s="275" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="274" t="s">
+        <v>417</v>
+      </c>
+      <c r="C6" s="274" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C7" s="275" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="274" t="s">
+        <v>442</v>
+      </c>
+      <c r="C8" s="269" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C9" s="275" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" s="274" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="276" t="s">
+        <v>387</v>
+      </c>
+      <c r="C10" s="269" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="269"/>
+      <c r="C11" s="275" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" s="274" customFormat="1" ht="22.8" x14ac:dyDescent="0.2">
+      <c r="B12" s="277" t="s">
+        <v>136</v>
+      </c>
+      <c r="C12" s="274" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C13" s="275" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="274" t="s">
+        <v>444</v>
+      </c>
+      <c r="C14" s="274" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C15" s="275" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="277" t="s">
+        <v>130</v>
+      </c>
+      <c r="C16" s="274" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" s="274" customFormat="1" ht="22.8" x14ac:dyDescent="0.2">
+      <c r="C17" s="275" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="274" t="s">
+        <v>450</v>
+      </c>
+      <c r="C18" s="274" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C19" s="275" t="s">
         <v>448</v>
       </c>
-      <c r="C4" s="275" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C5" s="276" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="275" t="s">
-        <v>418</v>
-      </c>
-      <c r="C6" s="275" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C7" s="276" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="275" t="s">
-        <v>443</v>
-      </c>
-      <c r="C8" s="270" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C9" s="276" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" s="275" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="277" t="s">
-        <v>387</v>
-      </c>
-      <c r="C10" s="270" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="270"/>
-      <c r="C11" s="276" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" s="275" customFormat="1" ht="22.8" x14ac:dyDescent="0.2">
-      <c r="B12" s="278" t="s">
-        <v>136</v>
-      </c>
-      <c r="C12" s="275" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C13" s="276" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="275" t="s">
-        <v>445</v>
-      </c>
-      <c r="C14" s="275" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C15" s="276" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="278" t="s">
-        <v>130</v>
-      </c>
-      <c r="C16" s="275" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" s="275" customFormat="1" ht="22.8" x14ac:dyDescent="0.2">
-      <c r="C17" s="276" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="275" t="s">
-        <v>451</v>
-      </c>
-      <c r="C18" s="275" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C19" s="276" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="275" t="s">
+    </row>
+    <row r="20" spans="2:3" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="274" t="s">
         <v>394</v>
       </c>
-      <c r="C20" s="275" t="s">
+      <c r="C20" s="274" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="21" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C21" s="276" t="s">
+    <row r="21" spans="2:3" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C21" s="275" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="22" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="275" t="s">
+    <row r="22" spans="2:3" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="274" t="s">
+        <v>422</v>
+      </c>
+      <c r="C22" s="274" t="s">
         <v>423</v>
       </c>
-      <c r="C22" s="275" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C23" s="276" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="275" t="s">
+    </row>
+    <row r="23" spans="2:3" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C23" s="275" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="274" t="s">
         <v>412</v>
       </c>
-      <c r="C24" s="275" t="s">
+      <c r="C24" s="274" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="25" spans="2:3" s="275" customFormat="1" ht="22.8" x14ac:dyDescent="0.2">
-      <c r="C25" s="276" t="s">
+    <row r="25" spans="2:3" s="274" customFormat="1" ht="22.8" x14ac:dyDescent="0.2">
+      <c r="C25" s="275" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="26" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="275" t="s">
+    <row r="26" spans="2:3" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="274" t="s">
         <v>413</v>
       </c>
-      <c r="C26" s="275" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="27" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C27" s="269" t="s">
+      <c r="C26" s="274" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="28" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="2:3" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C27" s="275" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" s="274" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <hyperlinks>
@@ -18835,10 +18832,10 @@
     <hyperlink ref="C21" r:id="rId7" xr:uid="{00000000-0004-0000-0E00-00000C000000}"/>
     <hyperlink ref="C13" r:id="rId8" xr:uid="{00000000-0004-0000-0E00-000000000000}"/>
     <hyperlink ref="C25" r:id="rId9" location="klimakosten-von-treibhausgas-emissionen" xr:uid="{B3B9AAF4-2EEA-4E52-899D-C960C9585C41}"/>
-    <hyperlink ref="C27" r:id="rId10" xr:uid="{68879F68-CC2A-4083-8AC6-87BBA5367FAB}"/>
-    <hyperlink ref="C23" r:id="rId11" xr:uid="{7F88534A-3644-42D1-A0B5-26F368F4C080}"/>
-    <hyperlink ref="C15" r:id="rId12" xr:uid="{00000000-0004-0000-0E00-000008000000}"/>
-    <hyperlink ref="C19" r:id="rId13" xr:uid="{00000000-0004-0000-0E00-000007000000}"/>
+    <hyperlink ref="C23" r:id="rId10" xr:uid="{7F88534A-3644-42D1-A0B5-26F368F4C080}"/>
+    <hyperlink ref="C15" r:id="rId11" xr:uid="{00000000-0004-0000-0E00-000008000000}"/>
+    <hyperlink ref="C19" r:id="rId12" xr:uid="{00000000-0004-0000-0E00-000007000000}"/>
+    <hyperlink ref="C27" r:id="rId13" xr:uid="{9CC21C90-1B21-47AE-8A64-ADE03372D452}"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId14"/>
@@ -18867,7 +18864,7 @@
   <sheetData>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I2" s="106" t="s">
         <v>20</v>
@@ -18886,58 +18883,58 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="C6" s="409" t="s">
-        <v>586</v>
-      </c>
-      <c r="D6" s="410"/>
-      <c r="E6" s="410"/>
-      <c r="F6" s="410"/>
-      <c r="G6" s="410"/>
-      <c r="H6" s="411"/>
+        <v>441</v>
+      </c>
+      <c r="C6" s="408" t="s">
+        <v>585</v>
+      </c>
+      <c r="D6" s="409"/>
+      <c r="E6" s="409"/>
+      <c r="F6" s="409"/>
+      <c r="G6" s="409"/>
+      <c r="H6" s="410"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C7" s="412"/>
-      <c r="D7" s="413"/>
-      <c r="E7" s="413"/>
-      <c r="F7" s="413"/>
-      <c r="G7" s="413"/>
-      <c r="H7" s="414"/>
+      <c r="C7" s="411"/>
+      <c r="D7" s="412"/>
+      <c r="E7" s="412"/>
+      <c r="F7" s="412"/>
+      <c r="G7" s="412"/>
+      <c r="H7" s="413"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C8" s="415"/>
-      <c r="D8" s="416"/>
-      <c r="E8" s="416"/>
-      <c r="F8" s="416"/>
-      <c r="G8" s="416"/>
-      <c r="H8" s="417"/>
+      <c r="C8" s="414"/>
+      <c r="D8" s="415"/>
+      <c r="E8" s="415"/>
+      <c r="F8" s="415"/>
+      <c r="G8" s="415"/>
+      <c r="H8" s="416"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B9" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="418" t="s">
+      <c r="C9" s="417" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="419"/>
-      <c r="E9" s="419"/>
-      <c r="F9" s="419"/>
-      <c r="G9" s="419"/>
-      <c r="H9" s="420"/>
+      <c r="D9" s="418"/>
+      <c r="E9" s="418"/>
+      <c r="F9" s="418"/>
+      <c r="G9" s="418"/>
+      <c r="H9" s="419"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="418" t="s">
+      <c r="C10" s="417" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="419"/>
-      <c r="E10" s="419"/>
-      <c r="F10" s="419"/>
-      <c r="G10" s="419"/>
-      <c r="H10" s="420"/>
+      <c r="D10" s="418"/>
+      <c r="E10" s="418"/>
+      <c r="F10" s="418"/>
+      <c r="G10" s="418"/>
+      <c r="H10" s="419"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
@@ -18961,30 +18958,30 @@
       <c r="H12" s="55"/>
     </row>
     <row r="13" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="404" t="s">
+      <c r="A13" s="390" t="s">
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="C13" s="406" t="s">
-        <v>522</v>
-      </c>
-      <c r="D13" s="407"/>
+        <v>580</v>
+      </c>
+      <c r="C13" s="405" t="s">
+        <v>521</v>
+      </c>
+      <c r="D13" s="406"/>
       <c r="E13" s="55"/>
       <c r="F13" s="55"/>
       <c r="G13" s="55"/>
       <c r="H13" s="55"/>
     </row>
     <row r="14" spans="1:9" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="404"/>
+      <c r="A14" s="390"/>
       <c r="B14" s="1" t="s">
-        <v>583</v>
-      </c>
-      <c r="C14" s="406" t="s">
-        <v>530</v>
-      </c>
-      <c r="D14" s="407"/>
+        <v>582</v>
+      </c>
+      <c r="C14" s="405" t="s">
+        <v>529</v>
+      </c>
+      <c r="D14" s="406"/>
       <c r="E14" s="55"/>
       <c r="F14" s="55"/>
       <c r="G14" s="55"/>
@@ -19000,7 +18997,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C16" s="152">
         <v>25000</v>
@@ -19043,7 +19040,7 @@
       <c r="H19" s="55"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B20" s="298" t="s">
+      <c r="B20" s="297" t="s">
         <v>409</v>
       </c>
       <c r="C20" s="151">
@@ -19056,7 +19053,7 @@
       <c r="H20" s="55"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B21" s="297"/>
+      <c r="B21" s="296"/>
       <c r="C21" s="55"/>
       <c r="D21" s="55"/>
       <c r="E21" s="55"/>
@@ -19083,16 +19080,16 @@
       <c r="A24" s="97" t="s">
         <v>11</v>
       </c>
-      <c r="B24" s="408" t="s">
+      <c r="B24" s="407" t="s">
         <v>32</v>
       </c>
-      <c r="C24" s="405" t="s">
+      <c r="C24" s="404" t="s">
         <v>33</v>
       </c>
-      <c r="D24" s="405"/>
+      <c r="D24" s="404"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B25" s="408"/>
+      <c r="B25" s="407"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B26" s="176"/>
@@ -19113,7 +19110,7 @@
       <c r="E27" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="F27" s="274">
+      <c r="F27" s="273">
         <f>Grunddaten!G46</f>
         <v>0</v>
       </c>
@@ -19123,7 +19120,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B29" s="154" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
@@ -19506,26 +19503,26 @@
       </c>
       <c r="D10" s="162"/>
       <c r="E10" s="140" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F10" s="140" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="G10" s="140" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H10" s="140" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="I10" s="140" t="s">
         <v>59</v>
       </c>
       <c r="J10" s="238"/>
       <c r="K10" s="236"/>
-      <c r="L10" s="432" t="s">
+      <c r="L10" s="431" t="s">
         <v>405</v>
       </c>
-      <c r="M10" s="432"/>
+      <c r="M10" s="431"/>
       <c r="N10" s="236"/>
       <c r="O10" s="164"/>
       <c r="P10" s="164"/>
@@ -19538,27 +19535,27 @@
       </c>
       <c r="D11" s="162"/>
       <c r="E11" s="141" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="F11" s="141" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="G11" s="141" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H11" s="141" t="s">
+        <v>546</v>
+      </c>
+      <c r="I11" s="141" t="s">
         <v>547</v>
       </c>
-      <c r="I11" s="141" t="s">
-        <v>548</v>
-      </c>
       <c r="J11" s="238"/>
-      <c r="K11" s="434" t="s">
+      <c r="K11" s="433" t="s">
         <v>61</v>
       </c>
-      <c r="L11" s="434"/>
-      <c r="M11" s="434"/>
-      <c r="N11" s="434"/>
+      <c r="L11" s="433"/>
+      <c r="M11" s="433"/>
+      <c r="N11" s="433"/>
       <c r="O11" s="164"/>
       <c r="P11" s="164"/>
       <c r="Q11" s="164"/>
@@ -19570,27 +19567,27 @@
       </c>
       <c r="D12" s="88"/>
       <c r="E12" s="141" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="F12" s="141" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="G12" s="141" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H12" s="141" t="s">
+        <v>548</v>
+      </c>
+      <c r="I12" s="141" t="s">
         <v>549</v>
       </c>
-      <c r="I12" s="141" t="s">
-        <v>550</v>
-      </c>
       <c r="J12" s="164"/>
-      <c r="K12" s="433" t="s">
+      <c r="K12" s="432" t="s">
         <v>63</v>
       </c>
-      <c r="L12" s="433"/>
-      <c r="M12" s="433"/>
-      <c r="N12" s="433"/>
+      <c r="L12" s="432"/>
+      <c r="M12" s="432"/>
+      <c r="N12" s="432"/>
       <c r="O12" s="164"/>
       <c r="P12" s="164"/>
       <c r="Q12" s="164"/>
@@ -19598,29 +19595,29 @@
     </row>
     <row r="13" spans="2:18" s="91" customFormat="1" ht="55.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C13" s="165" t="s">
-        <v>582</v>
-      </c>
-      <c r="D13" s="384"/>
+        <v>581</v>
+      </c>
+      <c r="D13" s="383"/>
       <c r="E13" s="139" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F13" s="139" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="G13" s="139" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H13" s="139" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="I13" s="139" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="J13" s="164"/>
-      <c r="K13" s="366"/>
-      <c r="L13" s="366"/>
-      <c r="M13" s="366"/>
-      <c r="N13" s="366"/>
+      <c r="K13" s="365"/>
+      <c r="L13" s="365"/>
+      <c r="M13" s="365"/>
+      <c r="N13" s="365"/>
       <c r="O13" s="164"/>
       <c r="P13" s="164"/>
       <c r="Q13" s="164"/>
@@ -19667,11 +19664,11 @@
       <c r="D15" s="263" t="s">
         <v>65</v>
       </c>
-      <c r="E15" s="361"/>
-      <c r="F15" s="364"/>
-      <c r="G15" s="361"/>
-      <c r="H15" s="361"/>
-      <c r="I15" s="361"/>
+      <c r="E15" s="360"/>
+      <c r="F15" s="363"/>
+      <c r="G15" s="360"/>
+      <c r="H15" s="360"/>
+      <c r="I15" s="360"/>
       <c r="J15" s="264" t="s">
         <v>66</v>
       </c>
@@ -19685,27 +19682,27 @@
       <c r="R15" s="164"/>
     </row>
     <row r="16" spans="2:18" s="91" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="431" t="s">
+      <c r="B16" s="430" t="s">
         <v>67</v>
       </c>
-      <c r="C16" s="429" t="s">
+      <c r="C16" s="428" t="s">
         <v>68</v>
       </c>
-      <c r="D16" s="359" t="s">
+      <c r="D16" s="358" t="s">
         <v>69</v>
       </c>
-      <c r="E16" s="365">
+      <c r="E16" s="364">
         <v>4.9000000000000004</v>
       </c>
       <c r="F16" s="257">
         <v>5.7</v>
       </c>
-      <c r="G16" s="363">
+      <c r="G16" s="362">
         <v>7.6</v>
       </c>
-      <c r="H16" s="363"/>
-      <c r="I16" s="362"/>
-      <c r="J16" s="360"/>
+      <c r="H16" s="362"/>
+      <c r="I16" s="361"/>
+      <c r="J16" s="359"/>
       <c r="K16" s="164"/>
       <c r="L16" s="164"/>
       <c r="M16" s="164"/>
@@ -19715,18 +19712,18 @@
       <c r="R16" s="164"/>
     </row>
     <row r="17" spans="2:18" s="91" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="431"/>
-      <c r="C17" s="430"/>
+      <c r="B17" s="430"/>
+      <c r="C17" s="429"/>
       <c r="D17" s="166" t="s">
         <v>70</v>
       </c>
-      <c r="E17" s="357"/>
+      <c r="E17" s="356"/>
       <c r="F17" s="257"/>
       <c r="G17" s="257"/>
       <c r="H17" s="257">
         <v>24.9</v>
       </c>
-      <c r="I17" s="358">
+      <c r="I17" s="357">
         <v>18.600000000000001</v>
       </c>
       <c r="J17" s="164"/>
@@ -19740,7 +19737,7 @@
       <c r="R17" s="164"/>
     </row>
     <row r="18" spans="2:18" s="91" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="431"/>
+      <c r="B18" s="430"/>
       <c r="C18" s="162" t="s">
         <v>71</v>
       </c>
@@ -19769,7 +19766,7 @@
       <c r="R18" s="164"/>
     </row>
     <row r="19" spans="2:18" s="91" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="431"/>
+      <c r="B19" s="430"/>
       <c r="C19" s="162" t="s">
         <v>73</v>
       </c>
@@ -19801,7 +19798,7 @@
       <c r="R19" s="164"/>
     </row>
     <row r="20" spans="2:18" s="91" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="431"/>
+      <c r="B20" s="430"/>
       <c r="C20" s="162" t="s">
         <v>75</v>
       </c>
@@ -19830,7 +19827,7 @@
       <c r="R20" s="164"/>
     </row>
     <row r="21" spans="2:18" s="91" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="431"/>
+      <c r="B21" s="430"/>
       <c r="C21" s="162" t="s">
         <v>76</v>
       </c>
@@ -19882,23 +19879,23 @@
       <c r="D23" s="228" t="s">
         <v>80</v>
       </c>
-      <c r="E23" s="389">
+      <c r="E23" s="388">
         <f>IF(AND(OR(Energie1="nicht verfügbar",COUNTIF(EnList1,Energie1)&lt;&gt;1),Antriebsart1&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="F23" s="389">
+      <c r="F23" s="388">
         <f>IF(AND(OR(Energie2="nicht verfügbar",COUNTIF(EnList2,Energie2)&lt;&gt;1),Antriebsart2&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="G23" s="389">
+      <c r="G23" s="388">
         <f>IF(AND(OR(Energie3="nicht verfügbar",COUNTIF(EnList3,Energie3)&lt;&gt;1),Antriebsart3&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="H23" s="389">
+      <c r="H23" s="388">
         <f>IF(AND(OR(Energie4="nicht verfügbar",COUNTIF(EnList4,Energie4)&lt;&gt;1),Antriebsart4&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="I23" s="389">
+      <c r="I23" s="388">
         <f>IF(AND(OR(Energie5="nicht verfügbar",COUNTIF(EnList5,Energie5)&lt;&gt;1),Antriebsart5&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
@@ -19913,14 +19910,14 @@
     </row>
     <row r="24" spans="2:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C24" s="77" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D24" s="228"/>
-      <c r="E24" s="389"/>
-      <c r="F24" s="389"/>
-      <c r="G24" s="389"/>
-      <c r="H24" s="389"/>
-      <c r="I24" s="389"/>
+      <c r="E24" s="388"/>
+      <c r="F24" s="388"/>
+      <c r="G24" s="388"/>
+      <c r="H24" s="388"/>
+      <c r="I24" s="388"/>
       <c r="J24" s="146"/>
       <c r="O24" s="7"/>
       <c r="P24" s="7"/>
@@ -19928,13 +19925,13 @@
       <c r="R24" s="7"/>
     </row>
     <row r="25" spans="2:18" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="404" t="s">
+      <c r="B25" s="390" t="s">
         <v>11</v>
       </c>
-      <c r="C25" s="331" t="s">
-        <v>452</v>
-      </c>
-      <c r="D25" s="322" t="s">
+      <c r="C25" s="330" t="s">
+        <v>451</v>
+      </c>
+      <c r="D25" s="321" t="s">
         <v>150</v>
       </c>
       <c r="E25" s="256">
@@ -19959,9 +19956,9 @@
       <c r="R25" s="7"/>
     </row>
     <row r="26" spans="2:18" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="404"/>
-      <c r="C26" s="331"/>
-      <c r="D26" s="322" t="s">
+      <c r="B26" s="390"/>
+      <c r="C26" s="330"/>
+      <c r="D26" s="321" t="s">
         <v>150</v>
       </c>
       <c r="E26" s="256"/>
@@ -19976,9 +19973,9 @@
       <c r="R26" s="7"/>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B27" s="404"/>
-      <c r="C27" s="335"/>
-      <c r="D27" s="322" t="s">
+      <c r="B27" s="390"/>
+      <c r="C27" s="334"/>
+      <c r="D27" s="321" t="s">
         <v>150</v>
       </c>
       <c r="E27" s="256"/>
@@ -19996,23 +19993,23 @@
       <c r="D28" s="228" t="s">
         <v>81</v>
       </c>
-      <c r="E28" s="389">
+      <c r="E28" s="388">
         <f>IF(OR(AND(COUNT(E16:E22)&lt;7,Antriebsart1="Plug-In-Hybrid (PHEV)"),AND(COUNT(E17,E22)&lt;2,Antriebsart1="Vollelektrisch (BEV)"),AND(COUNT(E16,E18:E20)&lt;4,Antriebsart1="Verbrenner")),1,0)</f>
         <v>0</v>
       </c>
-      <c r="F28" s="389">
+      <c r="F28" s="388">
         <f>IF(OR(AND(COUNT(F16:F22)&lt;7,Antriebsart2="Plug-In-Hybrid (PHEV)"),AND(COUNT(F17,F22)&lt;2,Antriebsart2="Vollelektrisch (BEV)"),AND(COUNT(F16,F18:F20)&lt;4,Antriebsart2="Verbrenner")),1,0)</f>
         <v>0</v>
       </c>
-      <c r="G28" s="389">
+      <c r="G28" s="388">
         <f>IF(OR(AND(COUNT(G16:G22)&lt;7,Antriebsart3="Plug-In-Hybrid (PHEV)"),AND(COUNT(G17,G22)&lt;2,Antriebsart3="Vollelektrisch (BEV)"),AND(COUNT(G16,G18:G20)&lt;4,Antriebsart3="Verbrenner")),1,0)</f>
         <v>0</v>
       </c>
-      <c r="H28" s="389">
+      <c r="H28" s="388">
         <f>IF(OR(AND(COUNT(H16:H22)&lt;7,Antriebsart4="Plug-In-Hybrid (PHEV)"),AND(COUNT(H17,H22)&lt;2,Antriebsart4="Vollelektrisch (BEV)"),AND(COUNT(H16,H18:H20)&lt;4,Antriebsart4="Verbrenner")),1,0)</f>
         <v>0</v>
       </c>
-      <c r="I28" s="389">
+      <c r="I28" s="388">
         <f>IF(OR(AND(COUNT(I16:I22)&lt;7,Antriebsart5="Plug-In-Hybrid (PHEV)"),AND(COUNT(I17,I22)&lt;2,Antriebsart5="Vollelektrisch (BEV)"),AND(COUNT(I16,I18:I20)&lt;4,Antriebsart5="Verbrenner")),1,0)</f>
         <v>0</v>
       </c>
@@ -20026,33 +20023,33 @@
       <c r="R28" s="7"/>
     </row>
     <row r="29" spans="2:18" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E29" s="426" t="s">
+      <c r="E29" s="425" t="s">
         <v>82</v>
       </c>
-      <c r="F29" s="427"/>
-      <c r="G29" s="427"/>
-      <c r="H29" s="427"/>
-      <c r="I29" s="428"/>
+      <c r="F29" s="426"/>
+      <c r="G29" s="426"/>
+      <c r="H29" s="426"/>
+      <c r="I29" s="427"/>
     </row>
     <row r="30" spans="2:18" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E30" s="421" t="s">
+      <c r="E30" s="420" t="s">
         <v>83</v>
       </c>
-      <c r="F30" s="408"/>
-      <c r="G30" s="408"/>
-      <c r="H30" s="408"/>
-      <c r="I30" s="422"/>
+      <c r="F30" s="407"/>
+      <c r="G30" s="407"/>
+      <c r="H30" s="407"/>
+      <c r="I30" s="421"/>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="E31" s="423"/>
-      <c r="F31" s="424"/>
-      <c r="G31" s="424"/>
-      <c r="H31" s="424"/>
-      <c r="I31" s="425"/>
+      <c r="E31" s="422"/>
+      <c r="F31" s="423"/>
+      <c r="G31" s="423"/>
+      <c r="H31" s="423"/>
+      <c r="I31" s="424"/>
     </row>
     <row r="33" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C33" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
   </sheetData>
@@ -20445,7 +20442,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B1" s="118" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C1" s="118"/>
       <c r="D1" s="118"/>
@@ -20459,7 +20456,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="65" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C2" s="227"/>
       <c r="D2" s="230" t="str">
@@ -20502,37 +20499,37 @@
     <row r="6" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="18"/>
       <c r="B6" s="12" t="s">
-        <v>442</v>
-      </c>
-      <c r="C6" s="439" t="str">
+        <v>441</v>
+      </c>
+      <c r="C6" s="438" t="str">
         <f>IF(Projektname=0,"",Projektname)</f>
         <v>Los 1 - Kauf von einem leichten Nutzfahrzeug mit einer Zuladung von mind. 800 kg</v>
       </c>
-      <c r="D6" s="440"/>
-      <c r="E6" s="440"/>
-      <c r="F6" s="440"/>
-      <c r="G6" s="440"/>
-      <c r="H6" s="441"/>
+      <c r="D6" s="439"/>
+      <c r="E6" s="439"/>
+      <c r="F6" s="439"/>
+      <c r="G6" s="439"/>
+      <c r="H6" s="440"/>
     </row>
     <row r="7" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="18"/>
       <c r="B7" s="12"/>
-      <c r="C7" s="442"/>
-      <c r="D7" s="443"/>
-      <c r="E7" s="443"/>
-      <c r="F7" s="443"/>
-      <c r="G7" s="443"/>
-      <c r="H7" s="444"/>
+      <c r="C7" s="441"/>
+      <c r="D7" s="442"/>
+      <c r="E7" s="442"/>
+      <c r="F7" s="442"/>
+      <c r="G7" s="442"/>
+      <c r="H7" s="443"/>
     </row>
     <row r="8" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="18"/>
       <c r="B8" s="12"/>
-      <c r="C8" s="445"/>
-      <c r="D8" s="446"/>
-      <c r="E8" s="446"/>
-      <c r="F8" s="446"/>
-      <c r="G8" s="446"/>
-      <c r="H8" s="447"/>
+      <c r="C8" s="444"/>
+      <c r="D8" s="445"/>
+      <c r="E8" s="445"/>
+      <c r="F8" s="445"/>
+      <c r="G8" s="445"/>
+      <c r="H8" s="446"/>
     </row>
     <row r="9" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="18"/>
@@ -20569,11 +20566,11 @@
       <c r="B11" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="435">
+      <c r="C11" s="434">
         <f>IF(Datum=0,"",Datum)</f>
         <v>45588</v>
       </c>
-      <c r="D11" s="436"/>
+      <c r="D11" s="435"/>
       <c r="E11" s="79"/>
       <c r="F11" s="81"/>
       <c r="G11" s="81"/>
@@ -20584,7 +20581,7 @@
       <c r="B12" s="12"/>
       <c r="C12" s="76"/>
       <c r="E12" s="58" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F12" s="85">
         <f>Fahrleistung</f>
@@ -20623,7 +20620,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="18"/>
-      <c r="B15" s="293" t="s">
+      <c r="B15" s="292" t="s">
         <v>85</v>
       </c>
       <c r="C15" s="21"/>
@@ -20711,10 +20708,10 @@
       <c r="I18" s="107"/>
     </row>
     <row r="19" spans="1:9" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A19" s="321" t="s">
+      <c r="A19" s="320" t="s">
         <v>11</v>
       </c>
-      <c r="B19" s="338" t="str">
+      <c r="B19" s="337" t="str">
         <f>IF(FinArt="Kauf",KaufpreisRech,"Fahrzeugkosten (Leasingrate/Miete)")</f>
         <v>Wertminderung</v>
       </c>
@@ -20737,13 +20734,13 @@
         <f>Erg.Fzg._4!$C$54+Erg.Fzg._4!$C$55</f>
         <v>33044.160956034983</v>
       </c>
-      <c r="H19" s="337">
+      <c r="H19" s="336">
         <f>Erg.Fzg._5!$C$54+Erg.Fzg._5!$C$55</f>
         <v>26805.952582527021</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="336"/>
+      <c r="A20" s="335"/>
       <c r="B20" s="45" t="s">
         <v>87</v>
       </c>
@@ -20772,7 +20769,7 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="437" t="s">
+      <c r="A21" s="436" t="s">
         <v>11</v>
       </c>
       <c r="B21" s="27" t="s">
@@ -20803,7 +20800,7 @@
       </c>
     </row>
     <row r="22" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="437"/>
+      <c r="A22" s="436"/>
       <c r="B22" s="27" t="s">
         <v>89</v>
       </c>
@@ -20833,26 +20830,26 @@
       <c r="I22" s="107"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="438"/>
+      <c r="A23" s="437"/>
       <c r="B23" s="45" t="s">
         <v>90</v>
       </c>
-      <c r="C23" s="325" t="s">
+      <c r="C23" s="324" t="s">
         <v>65</v>
       </c>
-      <c r="D23" s="326">
+      <c r="D23" s="325">
         <f>Erg.Fzg._1!$C$59</f>
         <v>0</v>
       </c>
-      <c r="E23" s="326">
+      <c r="E23" s="325">
         <f>Erg.Fzg._2!$C$59</f>
         <v>0</v>
       </c>
-      <c r="F23" s="326">
+      <c r="F23" s="325">
         <f>Erg.Fzg._3!$C$59</f>
         <v>0</v>
       </c>
-      <c r="G23" s="326">
+      <c r="G23" s="325">
         <f>Erg.Fzg._4!$C$59</f>
         <v>2873.181818181818</v>
       </c>
@@ -20862,30 +20859,30 @@
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="437" t="s">
+      <c r="A24" s="436" t="s">
         <v>11</v>
       </c>
-      <c r="B24" s="332" t="str">
+      <c r="B24" s="331" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", Zusatzangabe_x)</f>
         <v>Kfz-Steuer</v>
       </c>
-      <c r="C24" s="323" t="str">
+      <c r="C24" s="322" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", "EUR")</f>
         <v>EUR</v>
       </c>
-      <c r="D24" s="324">
+      <c r="D24" s="323">
         <f>Erg.Fzg._1!$C$60</f>
         <v>1120</v>
       </c>
-      <c r="E24" s="324">
+      <c r="E24" s="323">
         <f>Erg.Fzg._2!$C$60</f>
         <v>952</v>
       </c>
-      <c r="F24" s="324">
+      <c r="F24" s="323">
         <f>Erg.Fzg._3!$C$60</f>
         <v>1204</v>
       </c>
-      <c r="G24" s="324">
+      <c r="G24" s="323">
         <f>Erg.Fzg._4!$C$60</f>
         <v>0</v>
       </c>
@@ -20895,28 +20892,28 @@
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="437"/>
-      <c r="B25" s="332" t="str">
+      <c r="A25" s="436"/>
+      <c r="B25" s="331" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
       </c>
-      <c r="C25" s="323" t="str">
+      <c r="C25" s="322" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", "EUR")</f>
         <v/>
       </c>
-      <c r="D25" s="324" t="str">
+      <c r="D25" s="323" t="str">
         <f>Erg.Fzg._1!$C$61</f>
         <v/>
       </c>
-      <c r="E25" s="324" t="str">
+      <c r="E25" s="323" t="str">
         <f>Erg.Fzg._2!$C$61</f>
         <v/>
       </c>
-      <c r="F25" s="324" t="str">
+      <c r="F25" s="323" t="str">
         <f>Erg.Fzg._3!$C$61</f>
         <v/>
       </c>
-      <c r="G25" s="324" t="str">
+      <c r="G25" s="323" t="str">
         <f>Erg.Fzg._4!$C$61</f>
         <v/>
       </c>
@@ -20927,28 +20924,28 @@
       <c r="I25" s="6"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="437"/>
-      <c r="B26" s="332" t="str">
+      <c r="A26" s="436"/>
+      <c r="B26" s="331" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
       </c>
-      <c r="C26" s="323" t="str">
+      <c r="C26" s="322" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", "EUR")</f>
         <v/>
       </c>
-      <c r="D26" s="324" t="str">
+      <c r="D26" s="323" t="str">
         <f>Erg.Fzg._1!$C$62</f>
         <v/>
       </c>
-      <c r="E26" s="324" t="str">
+      <c r="E26" s="323" t="str">
         <f>Erg.Fzg._2!$C$62</f>
         <v/>
       </c>
-      <c r="F26" s="324" t="str">
+      <c r="F26" s="323" t="str">
         <f>Erg.Fzg._3!$C$62</f>
         <v/>
       </c>
-      <c r="G26" s="324" t="str">
+      <c r="G26" s="323" t="str">
         <f>Erg.Fzg._4!$C$62</f>
         <v/>
       </c>
@@ -21052,92 +21049,92 @@
       <c r="B30" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="C30" s="316" t="s">
+      <c r="C30" s="315" t="s">
         <v>95</v>
       </c>
-      <c r="D30" s="314">
+      <c r="D30" s="313">
         <f>Erg.Fzg._1!$C$65</f>
         <v>0</v>
       </c>
-      <c r="E30" s="314">
+      <c r="E30" s="313">
         <f>Erg.Fzg._2!$C$65</f>
         <v>0</v>
       </c>
-      <c r="F30" s="314">
+      <c r="F30" s="313">
         <f>Erg.Fzg._3!$C$65</f>
         <v>0</v>
       </c>
-      <c r="G30" s="314">
+      <c r="G30" s="313">
         <f>Erg.Fzg._4!$C$65</f>
         <v>3.3409090909090908</v>
       </c>
-      <c r="H30" s="315">
+      <c r="H30" s="314">
         <f>Erg.Fzg._5!$C$65</f>
         <v>5.0113636363636367</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="309"/>
+      <c r="A31" s="308"/>
       <c r="B31" s="98" t="s">
-        <v>453</v>
-      </c>
-      <c r="C31" s="317" t="s">
+        <v>452</v>
+      </c>
+      <c r="C31" s="316" t="s">
         <v>95</v>
       </c>
-      <c r="D31" s="318">
+      <c r="D31" s="317">
         <f>Erg.Fzg._1!$C$66</f>
         <v>29.882222581120001</v>
       </c>
-      <c r="E31" s="318">
+      <c r="E31" s="317">
         <f>Erg.Fzg._2!$C$66</f>
         <v>34.371667084160002</v>
       </c>
-      <c r="F31" s="318">
+      <c r="F31" s="317">
         <f>Erg.Fzg._3!$C$66</f>
         <v>45.712222778879998</v>
       </c>
-      <c r="G31" s="318">
+      <c r="G31" s="317">
         <f>Erg.Fzg._4!$C$66</f>
         <v>12.680324999999995</v>
       </c>
-      <c r="H31" s="319">
+      <c r="H31" s="318">
         <f>Erg.Fzg._5!$C$66</f>
         <v>9.4720500000000012</v>
       </c>
       <c r="I31" s="91"/>
     </row>
     <row r="32" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="309"/>
-      <c r="B32" s="310" t="s">
-        <v>441</v>
-      </c>
-      <c r="C32" s="311" t="s">
+      <c r="A32" s="308"/>
+      <c r="B32" s="309" t="s">
         <v>440</v>
       </c>
-      <c r="D32" s="312">
+      <c r="C32" s="310" t="s">
+        <v>439</v>
+      </c>
+      <c r="D32" s="311">
         <f>SUM(D30:D31)</f>
         <v>29.882222581120001</v>
       </c>
-      <c r="E32" s="312">
+      <c r="E32" s="311">
         <f t="shared" ref="E32:H32" si="2">SUM(E30:E31)</f>
         <v>34.371667084160002</v>
       </c>
-      <c r="F32" s="312">
+      <c r="F32" s="311">
         <f t="shared" si="2"/>
         <v>45.712222778879998</v>
       </c>
-      <c r="G32" s="312">
+      <c r="G32" s="311">
         <f t="shared" si="2"/>
         <v>16.021234090909086</v>
       </c>
-      <c r="H32" s="313">
+      <c r="H32" s="312">
         <f t="shared" si="2"/>
         <v>14.483413636363638</v>
       </c>
       <c r="I32" s="91"/>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B34" s="293" t="s">
+      <c r="B34" s="292" t="s">
         <v>99</v>
       </c>
       <c r="C34" s="21"/>
@@ -21269,7 +21266,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B1" s="118" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C1" s="118"/>
       <c r="D1" s="118"/>
@@ -21279,11 +21276,11 @@
       <c r="H1" s="119"/>
     </row>
     <row r="2" spans="1:10" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A2" s="320" t="s">
+      <c r="A2" s="319" t="s">
         <v>11</v>
       </c>
       <c r="B2" s="65" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C2" s="227"/>
       <c r="D2" s="230" t="str">
@@ -21326,37 +21323,37 @@
     <row r="6" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="18"/>
       <c r="B6" s="12" t="s">
-        <v>442</v>
-      </c>
-      <c r="C6" s="439" t="str">
+        <v>441</v>
+      </c>
+      <c r="C6" s="438" t="str">
         <f>IF(Projektname=0,"",Projektname)</f>
         <v>Los 1 - Kauf von einem leichten Nutzfahrzeug mit einer Zuladung von mind. 800 kg</v>
       </c>
-      <c r="D6" s="440"/>
-      <c r="E6" s="440"/>
-      <c r="F6" s="440"/>
-      <c r="G6" s="440"/>
-      <c r="H6" s="441"/>
+      <c r="D6" s="439"/>
+      <c r="E6" s="439"/>
+      <c r="F6" s="439"/>
+      <c r="G6" s="439"/>
+      <c r="H6" s="440"/>
     </row>
     <row r="7" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="18"/>
       <c r="B7" s="12"/>
-      <c r="C7" s="442"/>
-      <c r="D7" s="443"/>
-      <c r="E7" s="443"/>
-      <c r="F7" s="443"/>
-      <c r="G7" s="443"/>
-      <c r="H7" s="444"/>
+      <c r="C7" s="441"/>
+      <c r="D7" s="442"/>
+      <c r="E7" s="442"/>
+      <c r="F7" s="442"/>
+      <c r="G7" s="442"/>
+      <c r="H7" s="443"/>
     </row>
     <row r="8" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="18"/>
       <c r="B8" s="12"/>
-      <c r="C8" s="445"/>
-      <c r="D8" s="446"/>
-      <c r="E8" s="446"/>
-      <c r="F8" s="446"/>
-      <c r="G8" s="446"/>
-      <c r="H8" s="447"/>
+      <c r="C8" s="444"/>
+      <c r="D8" s="445"/>
+      <c r="E8" s="445"/>
+      <c r="F8" s="445"/>
+      <c r="G8" s="445"/>
+      <c r="H8" s="446"/>
     </row>
     <row r="9" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="18"/>
@@ -21393,11 +21390,11 @@
       <c r="B11" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="435">
+      <c r="C11" s="434">
         <f>IF(Datum=0,"",Datum)</f>
         <v>45588</v>
       </c>
-      <c r="D11" s="436"/>
+      <c r="D11" s="435"/>
       <c r="E11" s="79"/>
       <c r="F11" s="81"/>
       <c r="G11" s="81"/>
@@ -21408,7 +21405,7 @@
       <c r="B12" s="12"/>
       <c r="C12" s="76"/>
       <c r="E12" s="58" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F12" s="85">
         <f>Fahrleistung</f>
@@ -21447,8 +21444,8 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="18"/>
-      <c r="B15" s="293" t="s">
-        <v>432</v>
+      <c r="B15" s="292" t="s">
+        <v>431</v>
       </c>
       <c r="C15" s="21"/>
       <c r="D15" s="21"/>
@@ -21505,7 +21502,7 @@
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="437" t="s">
+      <c r="A18" s="436" t="s">
         <v>11</v>
       </c>
       <c r="B18" s="27" t="s">
@@ -21536,7 +21533,7 @@
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="437"/>
+      <c r="A19" s="436"/>
       <c r="B19" s="27" t="s">
         <v>98</v>
       </c>
@@ -21565,7 +21562,7 @@
       </c>
     </row>
     <row r="20" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="437"/>
+      <c r="A20" s="436"/>
       <c r="B20" s="27" t="s">
         <v>89</v>
       </c>
@@ -21595,7 +21592,7 @@
       <c r="I20" s="107"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="437"/>
+      <c r="A21" s="436"/>
       <c r="B21" s="29" t="s">
         <v>90</v>
       </c>
@@ -21745,7 +21742,7 @@
     <row r="26" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="33"/>
       <c r="B26" s="98" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C26" s="99" t="s">
         <v>95</v>
@@ -21774,37 +21771,37 @@
     </row>
     <row r="27" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="33"/>
-      <c r="B27" s="310" t="s">
-        <v>441</v>
-      </c>
-      <c r="C27" s="311" t="s">
+      <c r="B27" s="309" t="s">
         <v>440</v>
       </c>
-      <c r="D27" s="312">
+      <c r="C27" s="310" t="s">
+        <v>439</v>
+      </c>
+      <c r="D27" s="311">
         <f>SUM(D25:D26)</f>
         <v>29.882222581120001</v>
       </c>
-      <c r="E27" s="312">
+      <c r="E27" s="311">
         <f t="shared" ref="E27:G27" si="2">SUM(E25:E26)</f>
         <v>34.371667084160002</v>
       </c>
-      <c r="F27" s="312">
+      <c r="F27" s="311">
         <f t="shared" si="2"/>
         <v>45.712222778879998</v>
       </c>
-      <c r="G27" s="312">
+      <c r="G27" s="311">
         <f t="shared" si="2"/>
         <v>16.021234090909086</v>
       </c>
-      <c r="H27" s="313">
+      <c r="H27" s="312">
         <f>SUM(H25:H26)</f>
         <v>14.483413636363638</v>
       </c>
       <c r="I27" s="91"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B29" s="293" t="s">
-        <v>433</v>
+      <c r="B29" s="292" t="s">
+        <v>432</v>
       </c>
       <c r="C29" s="21"/>
       <c r="D29" s="21"/>
@@ -21971,20 +21968,20 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="119"/>
-      <c r="B4" s="293" t="s">
+      <c r="B4" s="292" t="s">
         <v>403</v>
       </c>
-      <c r="C4" s="354"/>
-      <c r="D4" s="354"/>
-      <c r="E4" s="354"/>
-      <c r="F4" s="354"/>
-      <c r="G4" s="354"/>
-      <c r="H4" s="355"/>
+      <c r="C4" s="353"/>
+      <c r="D4" s="353"/>
+      <c r="E4" s="353"/>
+      <c r="F4" s="353"/>
+      <c r="G4" s="353"/>
+      <c r="H4" s="354"/>
       <c r="I4" s="190"/>
       <c r="J4" s="119"/>
     </row>
     <row r="5" spans="1:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="404" t="s">
+      <c r="A5" s="390" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="219"/>
@@ -21996,14 +21993,14 @@
       <c r="H5" s="219"/>
       <c r="I5" s="190"/>
       <c r="J5" s="119"/>
-      <c r="L5" s="448" t="s">
+      <c r="L5" s="466" t="s">
         <v>406</v>
       </c>
-      <c r="M5" s="448"/>
-      <c r="N5" s="448"/>
+      <c r="M5" s="466"/>
+      <c r="N5" s="466"/>
     </row>
     <row r="6" spans="1:14" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A6" s="404"/>
+      <c r="A6" s="390"/>
       <c r="B6" s="220" t="s">
         <v>101</v>
       </c>
@@ -22011,10 +22008,10 @@
         <v>44</v>
       </c>
       <c r="D6" s="221" t="s">
+        <v>517</v>
+      </c>
+      <c r="E6" s="221" t="s">
         <v>518</v>
-      </c>
-      <c r="E6" s="221" t="s">
-        <v>519</v>
       </c>
       <c r="F6" s="221" t="s">
         <v>102</v>
@@ -22025,511 +22022,511 @@
       <c r="H6" s="221" t="s">
         <v>104</v>
       </c>
-      <c r="I6" s="306" t="s">
+      <c r="I6" s="305" t="s">
         <v>105</v>
       </c>
       <c r="J6" s="119"/>
-      <c r="L6" s="448"/>
-      <c r="M6" s="448"/>
-      <c r="N6" s="448"/>
+      <c r="L6" s="466"/>
+      <c r="M6" s="466"/>
+      <c r="N6" s="466"/>
     </row>
     <row r="7" spans="1:14" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A7" s="352"/>
-      <c r="B7" s="449" t="s">
+      <c r="A7" s="351"/>
+      <c r="B7" s="453" t="s">
         <v>106</v>
       </c>
-      <c r="C7" s="452" t="s">
+      <c r="C7" s="459" t="s">
         <v>46</v>
       </c>
-      <c r="D7" s="370" t="s">
+      <c r="D7" s="369" t="s">
+        <v>519</v>
+      </c>
+      <c r="E7" s="385" t="s">
         <v>520</v>
-      </c>
-      <c r="E7" s="386" t="s">
-        <v>521</v>
       </c>
       <c r="F7" s="223">
         <v>230</v>
       </c>
-      <c r="G7" s="272"/>
+      <c r="G7" s="271"/>
       <c r="H7" s="222" t="s">
         <v>72</v>
       </c>
-      <c r="I7" s="307">
+      <c r="I7" s="306">
         <f t="shared" ref="I7:I25" si="0">IF(ISBLANK(G7),F7,G7)</f>
         <v>230</v>
       </c>
       <c r="J7" s="119"/>
-      <c r="L7" s="448"/>
-      <c r="M7" s="448"/>
-      <c r="N7" s="448"/>
+      <c r="L7" s="466"/>
+      <c r="M7" s="466"/>
+      <c r="N7" s="466"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="352"/>
-      <c r="B8" s="450"/>
-      <c r="C8" s="453"/>
-      <c r="D8" s="455" t="s">
-        <v>522</v>
-      </c>
-      <c r="E8" s="387" t="s">
-        <v>584</v>
+      <c r="A8" s="351"/>
+      <c r="B8" s="454"/>
+      <c r="C8" s="460"/>
+      <c r="D8" s="457" t="s">
+        <v>521</v>
+      </c>
+      <c r="E8" s="386" t="s">
+        <v>583</v>
       </c>
       <c r="F8" s="223">
         <v>150</v>
       </c>
-      <c r="G8" s="272"/>
+      <c r="G8" s="271"/>
       <c r="H8" s="222" t="s">
         <v>72</v>
       </c>
-      <c r="I8" s="307">
+      <c r="I8" s="306">
         <f t="shared" si="0"/>
         <v>150</v>
       </c>
       <c r="J8" s="119"/>
-      <c r="L8" s="448"/>
-      <c r="M8" s="448"/>
-      <c r="N8" s="448"/>
+      <c r="L8" s="466"/>
+      <c r="M8" s="466"/>
+      <c r="N8" s="466"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="352"/>
-      <c r="B9" s="450"/>
-      <c r="C9" s="453"/>
-      <c r="D9" s="455"/>
-      <c r="E9" s="386" t="s">
-        <v>530</v>
+      <c r="A9" s="351"/>
+      <c r="B9" s="454"/>
+      <c r="C9" s="460"/>
+      <c r="D9" s="457"/>
+      <c r="E9" s="385" t="s">
+        <v>529</v>
       </c>
       <c r="F9" s="223">
         <v>160</v>
       </c>
-      <c r="G9" s="272"/>
+      <c r="G9" s="271"/>
       <c r="H9" s="222" t="s">
         <v>72</v>
       </c>
-      <c r="I9" s="307">
+      <c r="I9" s="306">
         <f t="shared" si="0"/>
         <v>160</v>
       </c>
       <c r="J9" s="119"/>
-      <c r="L9" s="448"/>
-      <c r="M9" s="448"/>
-      <c r="N9" s="448"/>
+      <c r="L9" s="466"/>
+      <c r="M9" s="466"/>
+      <c r="N9" s="466"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="352"/>
-      <c r="B10" s="450"/>
-      <c r="C10" s="453"/>
-      <c r="D10" s="455"/>
-      <c r="E10" s="387" t="s">
-        <v>531</v>
+      <c r="A10" s="351"/>
+      <c r="B10" s="454"/>
+      <c r="C10" s="460"/>
+      <c r="D10" s="457"/>
+      <c r="E10" s="386" t="s">
+        <v>530</v>
       </c>
       <c r="F10" s="223">
         <v>190</v>
       </c>
-      <c r="G10" s="272"/>
+      <c r="G10" s="271"/>
       <c r="H10" s="222" t="s">
         <v>72</v>
       </c>
-      <c r="I10" s="307">
+      <c r="I10" s="306">
         <f t="shared" si="0"/>
         <v>190</v>
       </c>
       <c r="J10" s="119"/>
-      <c r="L10" s="448"/>
-      <c r="M10" s="448"/>
-      <c r="N10" s="448"/>
+      <c r="L10" s="466"/>
+      <c r="M10" s="466"/>
+      <c r="N10" s="466"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="352"/>
-      <c r="B11" s="450"/>
-      <c r="C11" s="454"/>
-      <c r="D11" s="456"/>
-      <c r="E11" s="386" t="s">
-        <v>532</v>
+      <c r="A11" s="351"/>
+      <c r="B11" s="454"/>
+      <c r="C11" s="461"/>
+      <c r="D11" s="458"/>
+      <c r="E11" s="385" t="s">
+        <v>531</v>
       </c>
       <c r="F11" s="223">
         <v>210</v>
       </c>
-      <c r="G11" s="272"/>
+      <c r="G11" s="271"/>
       <c r="H11" s="222" t="s">
         <v>72</v>
       </c>
-      <c r="I11" s="307">
+      <c r="I11" s="306">
         <f t="shared" si="0"/>
         <v>210</v>
       </c>
       <c r="J11" s="119"/>
-      <c r="L11" s="448"/>
-      <c r="M11" s="448"/>
-      <c r="N11" s="448"/>
+      <c r="L11" s="466"/>
+      <c r="M11" s="466"/>
+      <c r="N11" s="466"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="352"/>
-      <c r="B12" s="451"/>
+      <c r="A12" s="351"/>
+      <c r="B12" s="455"/>
       <c r="C12" s="222" t="s">
         <v>107</v>
       </c>
       <c r="D12" s="223" t="s">
-        <v>512</v>
-      </c>
-      <c r="E12" s="386" t="s">
-        <v>512</v>
+        <v>511</v>
+      </c>
+      <c r="E12" s="385" t="s">
+        <v>511</v>
       </c>
       <c r="F12" s="223">
         <v>40</v>
       </c>
-      <c r="G12" s="272"/>
+      <c r="G12" s="271"/>
       <c r="H12" s="222" t="s">
         <v>72</v>
       </c>
-      <c r="I12" s="307">
+      <c r="I12" s="306">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="J12" s="119"/>
-      <c r="L12" s="448"/>
-      <c r="M12" s="448"/>
-      <c r="N12" s="448"/>
+      <c r="L12" s="466"/>
+      <c r="M12" s="466"/>
+      <c r="N12" s="466"/>
     </row>
     <row r="13" spans="1:14" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A13" s="352"/>
-      <c r="B13" s="449" t="s">
+      <c r="A13" s="351"/>
+      <c r="B13" s="453" t="s">
         <v>111</v>
       </c>
-      <c r="C13" s="452" t="s">
+      <c r="C13" s="459" t="s">
         <v>112</v>
       </c>
-      <c r="D13" s="371" t="s">
+      <c r="D13" s="370" t="s">
+        <v>519</v>
+      </c>
+      <c r="E13" s="385" t="s">
         <v>520</v>
-      </c>
-      <c r="E13" s="386" t="s">
-        <v>521</v>
       </c>
       <c r="F13" s="223">
         <v>32</v>
       </c>
-      <c r="G13" s="272"/>
+      <c r="G13" s="271"/>
       <c r="H13" s="222" t="s">
         <v>113</v>
       </c>
-      <c r="I13" s="307">
+      <c r="I13" s="306">
         <f>IF(ISBLANK(G13),F13,G13)</f>
         <v>32</v>
       </c>
       <c r="J13" s="119"/>
-      <c r="L13" s="448"/>
-      <c r="M13" s="448"/>
-      <c r="N13" s="448"/>
+      <c r="L13" s="466"/>
+      <c r="M13" s="466"/>
+      <c r="N13" s="466"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="352"/>
-      <c r="B14" s="450"/>
-      <c r="C14" s="453"/>
-      <c r="D14" s="463" t="s">
-        <v>522</v>
-      </c>
-      <c r="E14" s="386" t="s">
-        <v>584</v>
+      <c r="A14" s="351"/>
+      <c r="B14" s="454"/>
+      <c r="C14" s="460"/>
+      <c r="D14" s="456" t="s">
+        <v>521</v>
+      </c>
+      <c r="E14" s="385" t="s">
+        <v>583</v>
       </c>
       <c r="F14" s="223">
         <v>20</v>
       </c>
-      <c r="G14" s="272"/>
+      <c r="G14" s="271"/>
       <c r="H14" s="222" t="s">
         <v>113</v>
       </c>
-      <c r="I14" s="307">
+      <c r="I14" s="306">
         <f>IF(ISBLANK(G14),F14,G14)</f>
         <v>20</v>
       </c>
       <c r="J14" s="119"/>
-      <c r="L14" s="448"/>
-      <c r="M14" s="448"/>
-      <c r="N14" s="448"/>
+      <c r="L14" s="466"/>
+      <c r="M14" s="466"/>
+      <c r="N14" s="466"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="352"/>
-      <c r="B15" s="450"/>
-      <c r="C15" s="453"/>
-      <c r="D15" s="455"/>
-      <c r="E15" s="386" t="s">
-        <v>530</v>
+      <c r="A15" s="351"/>
+      <c r="B15" s="454"/>
+      <c r="C15" s="460"/>
+      <c r="D15" s="457"/>
+      <c r="E15" s="385" t="s">
+        <v>529</v>
       </c>
       <c r="F15" s="223">
         <v>28</v>
       </c>
-      <c r="G15" s="272"/>
+      <c r="G15" s="271"/>
       <c r="H15" s="222" t="s">
         <v>113</v>
       </c>
-      <c r="I15" s="307">
+      <c r="I15" s="306">
         <f t="shared" ref="I15:I16" si="1">IF(ISBLANK(G15),F15,G15)</f>
         <v>28</v>
       </c>
       <c r="J15" s="119"/>
-      <c r="L15" s="448"/>
-      <c r="M15" s="448"/>
-      <c r="N15" s="448"/>
+      <c r="L15" s="466"/>
+      <c r="M15" s="466"/>
+      <c r="N15" s="466"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="352"/>
-      <c r="B16" s="450"/>
-      <c r="C16" s="454"/>
-      <c r="D16" s="456"/>
-      <c r="E16" s="386" t="s">
-        <v>533</v>
+      <c r="A16" s="351"/>
+      <c r="B16" s="454"/>
+      <c r="C16" s="461"/>
+      <c r="D16" s="458"/>
+      <c r="E16" s="385" t="s">
+        <v>532</v>
       </c>
       <c r="F16" s="223">
         <v>32</v>
       </c>
-      <c r="G16" s="272"/>
+      <c r="G16" s="271"/>
       <c r="H16" s="222" t="s">
         <v>113</v>
       </c>
-      <c r="I16" s="307">
+      <c r="I16" s="306">
         <f t="shared" si="1"/>
         <v>32</v>
       </c>
       <c r="J16" s="119"/>
-      <c r="L16" s="448"/>
-      <c r="M16" s="448"/>
-      <c r="N16" s="448"/>
+      <c r="L16" s="466"/>
+      <c r="M16" s="466"/>
+      <c r="N16" s="466"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="437" t="s">
+      <c r="A17" s="436" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="450"/>
+      <c r="B17" s="454"/>
       <c r="C17" s="222" t="s">
         <v>46</v>
       </c>
       <c r="D17" s="223" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E17" s="223" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="F17" s="223" t="s">
-        <v>512</v>
-      </c>
-      <c r="G17" s="272"/>
+        <v>511</v>
+      </c>
+      <c r="G17" s="271"/>
       <c r="H17" s="222" t="s">
         <v>69</v>
       </c>
-      <c r="I17" s="307" t="str">
+      <c r="I17" s="306" t="str">
         <f>IF(ISBLANK(G17),"keine",G17)</f>
         <v>keine</v>
       </c>
       <c r="J17" s="119"/>
-      <c r="L17" s="448"/>
-      <c r="M17" s="448"/>
-      <c r="N17" s="448"/>
+      <c r="L17" s="466"/>
+      <c r="M17" s="466"/>
+      <c r="N17" s="466"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="437"/>
-      <c r="B18" s="450"/>
+      <c r="A18" s="436"/>
+      <c r="B18" s="454"/>
       <c r="C18" s="222" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D18" s="223" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E18" s="223" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="F18" s="223" t="s">
-        <v>512</v>
-      </c>
-      <c r="G18" s="272"/>
+        <v>511</v>
+      </c>
+      <c r="G18" s="271"/>
       <c r="H18" s="222" t="s">
         <v>69</v>
       </c>
-      <c r="I18" s="307" t="str">
+      <c r="I18" s="306" t="str">
         <f>IF(ISBLANK(G18),"keine",G18)</f>
         <v>keine</v>
       </c>
       <c r="J18" s="119"/>
-      <c r="L18" s="448"/>
-      <c r="M18" s="448"/>
-      <c r="N18" s="448"/>
+      <c r="L18" s="466"/>
+      <c r="M18" s="466"/>
+      <c r="N18" s="466"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="437"/>
-      <c r="B19" s="451"/>
+      <c r="A19" s="436"/>
+      <c r="B19" s="455"/>
       <c r="C19" s="222" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D19" s="223" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E19" s="223" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="F19" s="223" t="s">
-        <v>512</v>
-      </c>
-      <c r="G19" s="272"/>
+        <v>511</v>
+      </c>
+      <c r="G19" s="271"/>
       <c r="H19" s="222" t="s">
         <v>113</v>
       </c>
-      <c r="I19" s="307" t="str">
+      <c r="I19" s="306" t="str">
         <f>IF(ISBLANK(G19),"keine",G19)</f>
         <v>keine</v>
       </c>
       <c r="J19" s="119"/>
-      <c r="L19" s="448"/>
-      <c r="M19" s="448"/>
-      <c r="N19" s="448"/>
+      <c r="L19" s="466"/>
+      <c r="M19" s="466"/>
+      <c r="N19" s="466"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="352"/>
-      <c r="B20" s="378"/>
-      <c r="C20" s="380"/>
-      <c r="D20" s="464" t="s">
-        <v>526</v>
-      </c>
-      <c r="E20" s="465"/>
-      <c r="F20" s="381"/>
-      <c r="G20" s="382"/>
-      <c r="H20" s="379"/>
-      <c r="I20" s="307"/>
+      <c r="A20" s="351"/>
+      <c r="B20" s="377"/>
+      <c r="C20" s="379"/>
+      <c r="D20" s="462" t="s">
+        <v>525</v>
+      </c>
+      <c r="E20" s="463"/>
+      <c r="F20" s="380"/>
+      <c r="G20" s="381"/>
+      <c r="H20" s="378"/>
+      <c r="I20" s="306"/>
       <c r="J20" s="119"/>
-      <c r="L20" s="448"/>
-      <c r="M20" s="448"/>
-      <c r="N20" s="448"/>
+      <c r="L20" s="466"/>
+      <c r="M20" s="466"/>
+      <c r="N20" s="466"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="352"/>
-      <c r="B21" s="449" t="s">
+      <c r="A21" s="351"/>
+      <c r="B21" s="453" t="s">
         <v>108</v>
       </c>
-      <c r="C21" s="452" t="s">
+      <c r="C21" s="459" t="s">
         <v>109</v>
       </c>
-      <c r="D21" s="466" t="s">
-        <v>523</v>
-      </c>
-      <c r="E21" s="467"/>
-      <c r="F21" s="386">
+      <c r="D21" s="464" t="s">
+        <v>522</v>
+      </c>
+      <c r="E21" s="465"/>
+      <c r="F21" s="385">
         <v>64</v>
       </c>
-      <c r="G21" s="272"/>
+      <c r="G21" s="271"/>
       <c r="H21" s="222" t="s">
         <v>74</v>
       </c>
-      <c r="I21" s="307">
+      <c r="I21" s="306">
         <f>IF(ISBLANK(G21),F21,G21)</f>
         <v>64</v>
       </c>
       <c r="J21" s="119"/>
-      <c r="L21" s="448"/>
-      <c r="M21" s="448"/>
-      <c r="N21" s="448"/>
+      <c r="L21" s="466"/>
+      <c r="M21" s="466"/>
+      <c r="N21" s="466"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="352"/>
-      <c r="B22" s="450"/>
-      <c r="C22" s="453"/>
-      <c r="D22" s="466" t="s">
-        <v>524</v>
-      </c>
-      <c r="E22" s="467"/>
-      <c r="F22" s="386">
+      <c r="A22" s="351"/>
+      <c r="B22" s="454"/>
+      <c r="C22" s="460"/>
+      <c r="D22" s="464" t="s">
+        <v>523</v>
+      </c>
+      <c r="E22" s="465"/>
+      <c r="F22" s="385">
         <v>84</v>
       </c>
-      <c r="G22" s="272"/>
+      <c r="G22" s="271"/>
       <c r="H22" s="222" t="s">
         <v>74</v>
       </c>
-      <c r="I22" s="307">
+      <c r="I22" s="306">
         <f t="shared" ref="I22:I23" si="2">IF(ISBLANK(G22),F22,G22)</f>
         <v>84</v>
       </c>
       <c r="J22" s="119"/>
-      <c r="K22" s="383"/>
-      <c r="L22" s="448"/>
-      <c r="M22" s="448"/>
-      <c r="N22" s="448"/>
+      <c r="K22" s="382"/>
+      <c r="L22" s="466"/>
+      <c r="M22" s="466"/>
+      <c r="N22" s="466"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="352"/>
-      <c r="B23" s="451"/>
-      <c r="C23" s="454"/>
-      <c r="D23" s="466" t="s">
-        <v>525</v>
-      </c>
-      <c r="E23" s="467"/>
-      <c r="F23" s="386">
+      <c r="A23" s="351"/>
+      <c r="B23" s="455"/>
+      <c r="C23" s="461"/>
+      <c r="D23" s="464" t="s">
+        <v>524</v>
+      </c>
+      <c r="E23" s="465"/>
+      <c r="F23" s="385">
         <v>100</v>
       </c>
-      <c r="G23" s="272"/>
+      <c r="G23" s="271"/>
       <c r="H23" s="222" t="s">
         <v>74</v>
       </c>
-      <c r="I23" s="307">
+      <c r="I23" s="306">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
       <c r="J23" s="119"/>
-      <c r="L23" s="448"/>
-      <c r="M23" s="448"/>
-      <c r="N23" s="448"/>
+      <c r="L23" s="466"/>
+      <c r="M23" s="466"/>
+      <c r="N23" s="466"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="352"/>
-      <c r="B24" s="367" t="s">
+      <c r="A24" s="351"/>
+      <c r="B24" s="366" t="s">
         <v>110</v>
       </c>
-      <c r="C24" s="369" t="s">
+      <c r="C24" s="368" t="s">
         <v>109</v>
       </c>
-      <c r="D24" s="466" t="s">
-        <v>527</v>
-      </c>
-      <c r="E24" s="467"/>
-      <c r="F24" s="388">
+      <c r="D24" s="464" t="s">
+        <v>526</v>
+      </c>
+      <c r="E24" s="465"/>
+      <c r="F24" s="387">
         <v>3.6</v>
       </c>
-      <c r="G24" s="272"/>
+      <c r="G24" s="271"/>
       <c r="H24" s="222" t="s">
         <v>74</v>
       </c>
-      <c r="I24" s="307">
+      <c r="I24" s="306">
         <f>IF(ISBLANK(G24),F24,G24)</f>
         <v>3.6</v>
       </c>
       <c r="J24" s="119"/>
-      <c r="L24" s="448"/>
-      <c r="M24" s="448"/>
-      <c r="N24" s="448"/>
+      <c r="L24" s="466"/>
+      <c r="M24" s="466"/>
+      <c r="N24" s="466"/>
     </row>
     <row r="25" spans="1:14" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A25" s="353"/>
-      <c r="B25" s="356" t="s">
+      <c r="A25" s="352"/>
+      <c r="B25" s="355" t="s">
         <v>114</v>
       </c>
       <c r="C25" s="225" t="s">
         <v>107</v>
       </c>
       <c r="D25" s="223" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E25" s="223" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="F25" s="224">
         <v>60</v>
       </c>
-      <c r="G25" s="273"/>
+      <c r="G25" s="272"/>
       <c r="H25" s="225" t="s">
         <v>77</v>
       </c>
-      <c r="I25" s="307">
+      <c r="I25" s="306">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
       <c r="J25" s="191"/>
-      <c r="L25" s="448"/>
-      <c r="M25" s="448"/>
-      <c r="N25" s="448"/>
+      <c r="L25" s="466"/>
+      <c r="M25" s="466"/>
+      <c r="N25" s="466"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="119"/>
@@ -22587,15 +22584,15 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="196"/>
-      <c r="B31" s="293" t="s">
+      <c r="B31" s="292" t="s">
         <v>402</v>
       </c>
-      <c r="C31" s="339"/>
-      <c r="D31" s="339"/>
-      <c r="E31" s="339"/>
-      <c r="F31" s="340"/>
-      <c r="G31" s="340"/>
-      <c r="H31" s="341"/>
+      <c r="C31" s="338"/>
+      <c r="D31" s="338"/>
+      <c r="E31" s="338"/>
+      <c r="F31" s="339"/>
+      <c r="G31" s="339"/>
+      <c r="H31" s="340"/>
       <c r="I31" s="194"/>
       <c r="J31" s="195"/>
       <c r="K31" s="195"/>
@@ -22603,11 +22600,11 @@
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="196"/>
       <c r="B32" s="6"/>
-      <c r="C32" s="327"/>
-      <c r="D32" s="327"/>
-      <c r="E32" s="327"/>
+      <c r="C32" s="326"/>
+      <c r="D32" s="326"/>
+      <c r="E32" s="326"/>
       <c r="F32" s="6"/>
-      <c r="G32" s="327"/>
+      <c r="G32" s="326"/>
       <c r="H32" s="208"/>
       <c r="I32" s="194"/>
       <c r="J32" s="195"/>
@@ -22615,17 +22612,17 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="196"/>
-      <c r="B33" s="346" t="s">
+      <c r="B33" s="345" t="s">
         <v>48</v>
       </c>
-      <c r="C33" s="327"/>
-      <c r="D33" s="327"/>
-      <c r="E33" s="327"/>
-      <c r="F33" s="296" t="s">
+      <c r="C33" s="326"/>
+      <c r="D33" s="326"/>
+      <c r="E33" s="326"/>
+      <c r="F33" s="295" t="s">
         <v>117</v>
       </c>
-      <c r="G33" s="347"/>
-      <c r="H33" s="295" t="s">
+      <c r="G33" s="346"/>
+      <c r="H33" s="294" t="s">
         <v>104</v>
       </c>
       <c r="I33" s="194"/>
@@ -22635,15 +22632,15 @@
     <row r="34" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A34" s="196"/>
       <c r="B34" s="6"/>
-      <c r="C34" s="327"/>
-      <c r="D34" s="327"/>
-      <c r="E34" s="327"/>
+      <c r="C34" s="326"/>
+      <c r="D34" s="326"/>
+      <c r="E34" s="326"/>
       <c r="F34" s="209"/>
       <c r="G34" s="210" t="s">
         <v>103</v>
       </c>
-      <c r="H34" s="294"/>
-      <c r="I34" s="308" t="s">
+      <c r="H34" s="293"/>
+      <c r="I34" s="307" t="s">
         <v>118</v>
       </c>
       <c r="J34" s="198" t="s">
@@ -22658,8 +22655,8 @@
       <c r="B35" s="212" t="s">
         <v>121</v>
       </c>
-      <c r="C35" s="372"/>
-      <c r="D35" s="375"/>
+      <c r="C35" s="371"/>
+      <c r="D35" s="374"/>
       <c r="E35" s="213"/>
       <c r="F35" s="214">
         <v>41.4</v>
@@ -22668,12 +22665,12 @@
       <c r="H35" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="I35" s="308">
+      <c r="I35" s="307">
         <f>IF(ISNUMBER(G35),G35,F35)/100</f>
         <v>0.41399999999999998</v>
       </c>
       <c r="J35" s="199" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="K35" s="254"/>
     </row>
@@ -22682,8 +22679,8 @@
       <c r="B36" s="215" t="s">
         <v>123</v>
       </c>
-      <c r="C36" s="373"/>
-      <c r="D36" s="376"/>
+      <c r="C36" s="372"/>
+      <c r="D36" s="375"/>
       <c r="E36" s="211"/>
       <c r="F36" s="214">
         <v>59</v>
@@ -22692,12 +22689,12 @@
       <c r="H36" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="I36" s="308">
+      <c r="I36" s="307">
         <f>IF(ISNUMBER(G36),G36,F36)/100</f>
         <v>0.59</v>
       </c>
       <c r="J36" s="199" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="K36" s="254"/>
     </row>
@@ -22706,13 +22703,13 @@
       <c r="B37" s="216" t="s">
         <v>49</v>
       </c>
-      <c r="C37" s="374"/>
-      <c r="D37" s="377"/>
-      <c r="E37" s="348"/>
-      <c r="F37" s="349"/>
-      <c r="G37" s="350"/>
+      <c r="C37" s="373"/>
+      <c r="D37" s="376"/>
+      <c r="E37" s="347"/>
+      <c r="F37" s="348"/>
+      <c r="G37" s="349"/>
       <c r="H37" s="208"/>
-      <c r="I37" s="308">
+      <c r="I37" s="307">
         <f>I35*Input_Beschaffung!J32/100+I36*(1-Input_Beschaffung!J32/100)</f>
         <v>0.502</v>
       </c>
@@ -22720,50 +22717,50 @@
       <c r="K37" s="254"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="459"/>
+      <c r="A38" s="449"/>
       <c r="B38" s="212" t="s">
         <v>50</v>
       </c>
-      <c r="C38" s="372"/>
-      <c r="D38" s="375"/>
+      <c r="C38" s="371"/>
+      <c r="D38" s="374"/>
       <c r="E38" s="213"/>
-      <c r="F38" s="271">
+      <c r="F38" s="270">
         <v>1.6719999999999999</v>
       </c>
       <c r="G38" s="243"/>
       <c r="H38" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="I38" s="308">
+      <c r="I38" s="307">
         <f t="shared" ref="I38:I40" si="3">IF(ISNUMBER(G38),G38,F38)</f>
         <v>1.6719999999999999</v>
       </c>
       <c r="J38" s="199" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="K38" s="254"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="459"/>
+      <c r="A39" s="449"/>
       <c r="B39" s="212" t="s">
         <v>51</v>
       </c>
-      <c r="C39" s="372"/>
-      <c r="D39" s="375"/>
+      <c r="C39" s="371"/>
+      <c r="D39" s="374"/>
       <c r="E39" s="213"/>
-      <c r="F39" s="271">
+      <c r="F39" s="270">
         <v>1.788</v>
       </c>
       <c r="G39" s="243"/>
       <c r="H39" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="I39" s="308">
+      <c r="I39" s="307">
         <f t="shared" si="3"/>
         <v>1.788</v>
       </c>
       <c r="J39" s="199" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="K39" s="254"/>
     </row>
@@ -22772,8 +22769,8 @@
       <c r="B40" s="212" t="s">
         <v>125</v>
       </c>
-      <c r="C40" s="372"/>
-      <c r="D40" s="375"/>
+      <c r="C40" s="371"/>
+      <c r="D40" s="374"/>
       <c r="E40" s="213"/>
       <c r="F40" s="217">
         <v>1.3</v>
@@ -22782,12 +22779,12 @@
       <c r="H40" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="I40" s="308">
+      <c r="I40" s="307">
         <f t="shared" si="3"/>
         <v>1.3</v>
       </c>
       <c r="J40" s="199" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="K40" s="254"/>
     </row>
@@ -22819,31 +22816,31 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="193"/>
-      <c r="B43" s="293" t="s">
+      <c r="B43" s="292" t="s">
         <v>127</v>
       </c>
-      <c r="C43" s="339"/>
-      <c r="D43" s="339"/>
-      <c r="E43" s="339"/>
-      <c r="F43" s="340"/>
-      <c r="G43" s="340"/>
-      <c r="H43" s="341"/>
+      <c r="C43" s="338"/>
+      <c r="D43" s="338"/>
+      <c r="E43" s="338"/>
+      <c r="F43" s="339"/>
+      <c r="G43" s="339"/>
+      <c r="H43" s="340"/>
       <c r="I43" s="201"/>
       <c r="J43" s="201"/>
       <c r="K43" s="201"/>
     </row>
     <row r="44" spans="1:11" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="193"/>
-      <c r="B44" s="460" t="s">
+      <c r="B44" s="450" t="s">
         <v>128</v>
       </c>
-      <c r="C44" s="461"/>
-      <c r="D44" s="461"/>
-      <c r="E44" s="461"/>
-      <c r="F44" s="461"/>
-      <c r="G44" s="461"/>
-      <c r="H44" s="462"/>
-      <c r="I44" s="308" t="s">
+      <c r="C44" s="451"/>
+      <c r="D44" s="451"/>
+      <c r="E44" s="451"/>
+      <c r="F44" s="451"/>
+      <c r="G44" s="451"/>
+      <c r="H44" s="452"/>
+      <c r="I44" s="307" t="s">
         <v>118</v>
       </c>
       <c r="J44" s="202"/>
@@ -22852,17 +22849,17 @@
     <row r="45" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A45" s="193"/>
       <c r="B45" s="6"/>
-      <c r="C45" s="327"/>
-      <c r="D45" s="327"/>
-      <c r="E45" s="327"/>
-      <c r="F45" s="327"/>
-      <c r="G45" s="342" t="s">
+      <c r="C45" s="326"/>
+      <c r="D45" s="326"/>
+      <c r="E45" s="326"/>
+      <c r="F45" s="326"/>
+      <c r="G45" s="341" t="s">
         <v>103</v>
       </c>
-      <c r="H45" s="343" t="s">
+      <c r="H45" s="342" t="s">
         <v>104</v>
       </c>
-      <c r="I45" s="308"/>
+      <c r="I45" s="307"/>
       <c r="J45" s="195"/>
       <c r="K45" s="195"/>
     </row>
@@ -22871,9 +22868,9 @@
       <c r="B46" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="C46" s="327"/>
-      <c r="D46" s="327"/>
-      <c r="E46" s="327"/>
+      <c r="C46" s="326"/>
+      <c r="D46" s="326"/>
+      <c r="E46" s="326"/>
       <c r="F46" s="218">
         <f>IF(KostTHGVorgabe="(Niedrig) 250", 250, 860)</f>
         <v>860</v>
@@ -22882,7 +22879,7 @@
       <c r="H46" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I46" s="308">
+      <c r="I46" s="307">
         <f>IF(ISNUMBER(G46),G46,F46)</f>
         <v>860</v>
       </c>
@@ -22894,13 +22891,13 @@
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="193"/>
       <c r="B47" s="6"/>
-      <c r="C47" s="327"/>
-      <c r="D47" s="327"/>
-      <c r="E47" s="327"/>
-      <c r="F47" s="344"/>
-      <c r="G47" s="344"/>
-      <c r="H47" s="345"/>
-      <c r="I47" s="308"/>
+      <c r="C47" s="326"/>
+      <c r="D47" s="326"/>
+      <c r="E47" s="326"/>
+      <c r="F47" s="343"/>
+      <c r="G47" s="343"/>
+      <c r="H47" s="344"/>
+      <c r="I47" s="307"/>
       <c r="J47" s="195"/>
       <c r="K47" s="195"/>
     </row>
@@ -22909,9 +22906,9 @@
       <c r="B48" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="C48" s="327"/>
-      <c r="D48" s="327"/>
-      <c r="E48" s="327"/>
+      <c r="C48" s="326"/>
+      <c r="D48" s="326"/>
+      <c r="E48" s="326"/>
       <c r="F48" s="218">
         <v>0.02</v>
       </c>
@@ -22919,7 +22916,7 @@
       <c r="H48" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="I48" s="308">
+      <c r="I48" s="307">
         <f>IF(ISNUMBER(G48),G48,F48)</f>
         <v>0.02</v>
       </c>
@@ -22943,7 +22940,7 @@
       <c r="H49" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="I49" s="308">
+      <c r="I49" s="307">
         <f>IF(ISNUMBER(G49),G49,F49)</f>
         <v>0.15</v>
       </c>
@@ -22961,7 +22958,7 @@
       <c r="F50" s="194"/>
       <c r="G50" s="194"/>
       <c r="H50" s="193"/>
-      <c r="I50" s="308"/>
+      <c r="I50" s="307"/>
       <c r="J50" s="195"/>
       <c r="K50" s="195"/>
     </row>
@@ -22974,33 +22971,33 @@
       <c r="F51" s="193"/>
       <c r="G51" s="193"/>
       <c r="H51" s="193"/>
-      <c r="I51" s="308"/>
+      <c r="I51" s="307"/>
       <c r="J51" s="194"/>
       <c r="K51" s="194"/>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="193"/>
-      <c r="B52" s="293" t="s">
+      <c r="B52" s="292" t="s">
         <v>134</v>
       </c>
-      <c r="C52" s="340"/>
-      <c r="D52" s="340"/>
-      <c r="E52" s="340"/>
-      <c r="F52" s="340"/>
-      <c r="G52" s="340"/>
-      <c r="H52" s="351"/>
-      <c r="I52" s="308"/>
+      <c r="C52" s="339"/>
+      <c r="D52" s="339"/>
+      <c r="E52" s="339"/>
+      <c r="F52" s="339"/>
+      <c r="G52" s="339"/>
+      <c r="H52" s="350"/>
+      <c r="I52" s="307"/>
       <c r="J52" s="193"/>
       <c r="K52" s="193"/>
     </row>
     <row r="53" spans="1:11" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A53" s="193"/>
-      <c r="B53" s="457" t="s">
+      <c r="B53" s="447" t="s">
         <v>407</v>
       </c>
-      <c r="C53" s="458"/>
-      <c r="D53" s="368"/>
-      <c r="E53" s="368"/>
+      <c r="C53" s="448"/>
+      <c r="D53" s="367"/>
+      <c r="E53" s="367"/>
       <c r="F53" s="218">
         <v>84</v>
       </c>
@@ -23008,7 +23005,7 @@
       <c r="H53" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="I53" s="308">
+      <c r="I53" s="307">
         <f>IF(ISNUMBER(G53),G53,F53)</f>
         <v>84</v>
       </c>
@@ -23048,6 +23045,11 @@
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="19">
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="L5:N25"/>
+    <mergeCell ref="B7:B12"/>
+    <mergeCell ref="C7:C11"/>
+    <mergeCell ref="D8:D11"/>
     <mergeCell ref="B53:C53"/>
     <mergeCell ref="A38:A39"/>
     <mergeCell ref="B44:H44"/>
@@ -23062,11 +23064,6 @@
     <mergeCell ref="D22:E22"/>
     <mergeCell ref="D23:E23"/>
     <mergeCell ref="D24:E24"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="L5:N25"/>
-    <mergeCell ref="B7:B12"/>
-    <mergeCell ref="C7:C11"/>
-    <mergeCell ref="D8:D11"/>
   </mergeCells>
   <conditionalFormatting sqref="K35">
     <cfRule type="expression" dxfId="14" priority="10">
@@ -23150,7 +23147,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>20</v>
@@ -23293,7 +23290,7 @@
       <c r="B18" s="72" t="s">
         <v>143</v>
       </c>
-      <c r="C18" s="288">
+      <c r="C18" s="287">
         <f>0.0057*(ReichwPHEV1/23)^3-0.0838*(ReichwPHEV1/23)^2+0.4261*(ReichwPHEV1/23)+ 0.1633</f>
         <v>0.1633</v>
       </c>
@@ -23304,7 +23301,7 @@
       <c r="B19" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C19" s="289">
+      <c r="C19" s="288">
         <f>Verbrauch1/(1-0.9*C18)</f>
         <v>5.7442293940424145</v>
       </c>
@@ -23317,7 +23314,7 @@
       <c r="B20" s="72" t="s">
         <v>145</v>
       </c>
-      <c r="C20" s="290">
+      <c r="C20" s="289">
         <f>VerbEl_WLTP1/C18</f>
         <v>0</v>
       </c>
@@ -23330,7 +23327,7 @@
       <c r="B21" s="186" t="s">
         <v>146</v>
       </c>
-      <c r="C21" s="291">
+      <c r="C21" s="290">
         <f>0.0021*(ReichwPHEV1/23)^3-0.0358*(ReichwPHEV1/23)^2+0.2607*(ReichwPHEV1/23)- 0.0267</f>
         <v>-2.6700000000000002E-2</v>
       </c>
@@ -23338,13 +23335,13 @@
       <c r="F21" s="125"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="471" t="s">
+      <c r="A22" s="470" t="s">
         <v>11</v>
       </c>
-      <c r="B22" s="470" t="s">
+      <c r="B22" s="469" t="s">
         <v>147</v>
       </c>
-      <c r="C22" s="292">
+      <c r="C22" s="291">
         <f>C19*(1-0.9*C21)</f>
         <v>5.8822632263812533</v>
       </c>
@@ -23354,9 +23351,9 @@
       <c r="F22" s="125"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="471"/>
-      <c r="B23" s="430"/>
-      <c r="C23" s="292">
+      <c r="A23" s="470"/>
+      <c r="B23" s="429"/>
+      <c r="C23" s="291">
         <f>C20*C21</f>
         <v>0</v>
       </c>
@@ -23393,7 +23390,7 @@
       <c r="B28" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C28" s="279">
+      <c r="C28" s="278">
         <f>IF(Antriebsart1="Vollelektrisch (BEV)",0,IFERROR(VLOOKUP(Energie1,EnKostList,8,FALSE),0)*IF(Antriebsart1="Plug-In-Hybrid (PHEV)",VerbPHEV1,Verbrauch1)/100*Fahrleistung)</f>
         <v>2048.1999999999998</v>
       </c>
@@ -23406,7 +23403,7 @@
       <c r="B29" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C29" s="279">
+      <c r="C29" s="278">
         <f>IF(Antriebsart1="Verbrenner",0,VLOOKUP("Strom",EnKostList,8,FALSE)*IF(Antriebsart1="Plug-In-Hybrid (PHEV)",VerbElPHEV1,VerbEl_WLTP1)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
@@ -23418,7 +23415,7 @@
       <c r="B30" s="64" t="s">
         <v>91</v>
       </c>
-      <c r="C30" s="280">
+      <c r="C30" s="279">
         <f>SUM(C28:C29)</f>
         <v>2048.1999999999998</v>
       </c>
@@ -23445,7 +23442,7 @@
       <c r="B33" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C33" s="279">
+      <c r="C33" s="278">
         <f>IF(Antriebsart1="Plug-In-Hybrid (PHEV)",VerbPHEV1*VLOOKUP(Energie1,CO2List,2,FALSE)/100,CO2_1)*Fahrleistung/1000000</f>
         <v>3.25</v>
       </c>
@@ -23458,7 +23455,7 @@
       <c r="B34" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C34" s="279">
+      <c r="C34" s="278">
         <f>C33*Kost_THG</f>
         <v>2795</v>
       </c>
@@ -23470,7 +23467,7 @@
       <c r="B35" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C35" s="279">
+      <c r="C35" s="278">
         <f>IF(Energie1="Strom",0,NOX_1*Fahrleistung*Kost_NOX/1000)</f>
         <v>29.3</v>
       </c>
@@ -23482,7 +23479,7 @@
       <c r="B36" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C36" s="279">
+      <c r="C36" s="278">
         <f>IF(Energie1="Strom",0,Partikel1*Fahrleistung*Kost_Partikel/1000)</f>
         <v>1.575</v>
       </c>
@@ -23494,7 +23491,7 @@
       <c r="B37" s="64" t="s">
         <v>91</v>
       </c>
-      <c r="C37" s="280">
+      <c r="C37" s="279">
         <f>SUM(C34:C36)</f>
         <v>2825.875</v>
       </c>
@@ -23519,7 +23516,7 @@
       <c r="B40" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C40" s="279">
+      <c r="C40" s="278">
         <f>IFERROR(IF(Antriebsart1="Vollelektrisch (BEV)",VLOOKUP("Strom",CO2List,3,FALSE)*VerbEl_WLTP1/100*Fahrleistung/1000000,IF(Antriebsart1="Verbrenner",VLOOKUP(Energie1,CO2List,3,FALSE)*Verbrauch1/100*Fahrleistung/1000000,VLOOKUP(Energie1,CO2List,3,FALSE)*VerbPHEV1/100*Fahrleistung/1000000+VLOOKUP("Strom",CO2List,3,FALSE)*VerbElPHEV1/100*Fahrleistung/1000000)),0)</f>
         <v>1.0188889401600001</v>
       </c>
@@ -23532,7 +23529,7 @@
       <c r="B41" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C41" s="279">
+      <c r="C41" s="278">
         <f>C40*Kost_THG</f>
         <v>876.24448853760009</v>
       </c>
@@ -23564,13 +23561,13 @@
       <c r="D45" s="62"/>
     </row>
     <row r="46" spans="1:6" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="404" t="s">
+      <c r="A46" s="390" t="s">
         <v>11</v>
       </c>
-      <c r="B46" s="468" t="s">
+      <c r="B46" s="467" t="s">
         <v>152</v>
       </c>
-      <c r="C46" s="281">
+      <c r="C46" s="280">
         <f>IF(OR(Antriebsart1="Vollelektrisch (BEV)",Antriebsart1="Plug-In-Hybrid (PHEV)"),Batterie1*Batterie_THG/1000,0)</f>
         <v>0</v>
       </c>
@@ -23581,9 +23578,9 @@
       <c r="F46" s="107"/>
     </row>
     <row r="47" spans="1:6" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="404"/>
-      <c r="B47" s="469"/>
-      <c r="C47" s="281">
+      <c r="A47" s="390"/>
+      <c r="B47" s="468"/>
+      <c r="C47" s="280">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
         <v>0</v>
       </c>
@@ -23597,7 +23594,7 @@
       <c r="B48" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C48" s="279">
+      <c r="C48" s="278">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Kost_THG, C46/Haltedauer*Kost_THG)</f>
         <v>0</v>
       </c>
@@ -23628,7 +23625,7 @@
       <c r="B54" s="68" t="s">
         <v>164</v>
       </c>
-      <c r="C54" s="282">
+      <c r="C54" s="281">
         <f>IF(FinArt="Kauf",IF(KaufpreisRech="Kaufpreis",Gesamtpreis1,0),Gesamtpreis1*Haltedauer*12+IF(FinArt="Leasing",LeasSondZahl1,0))</f>
         <v>0</v>
       </c>
@@ -23638,13 +23635,13 @@
       <c r="F54" s="58"/>
     </row>
     <row r="55" spans="1:6" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A55" s="305" t="s">
+      <c r="A55" s="304" t="s">
         <v>11</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="C55" s="283">
+        <v>438</v>
+      </c>
+      <c r="C55" s="282">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis1-Gesamtpreis1*(-0.2*LN(Haltedauer)+0.667),0)</f>
         <v>26555.355418182582</v>
       </c>
@@ -23657,7 +23654,7 @@
       <c r="B56" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C56" s="283">
+      <c r="C56" s="282">
         <f>C30*Haltedauer</f>
         <v>14337.399999999998</v>
       </c>
@@ -23670,7 +23667,7 @@
       <c r="B57" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C57" s="283">
+      <c r="C57" s="282">
         <f>C37*Haltedauer</f>
         <v>19781.125</v>
       </c>
@@ -23683,7 +23680,7 @@
       <c r="B58" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C58" s="283">
+      <c r="C58" s="282">
         <f>C41*Haltedauer</f>
         <v>6133.7114197632009</v>
       </c>
@@ -23693,63 +23690,63 @@
       <c r="F58" s="58"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B59" s="329" t="s">
+      <c r="B59" s="328" t="s">
         <v>90</v>
       </c>
-      <c r="C59" s="330">
+      <c r="C59" s="329">
         <f>C48*Haltedauer</f>
         <v>0</v>
       </c>
-      <c r="D59" s="329" t="s">
+      <c r="D59" s="328" t="s">
         <v>65</v>
       </c>
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="404" t="s">
+      <c r="A60" s="390" t="s">
         <v>11</v>
       </c>
-      <c r="B60" s="327" t="str">
+      <c r="B60" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", Zusatzangabe_x)</f>
         <v>Kfz-Steuer</v>
       </c>
-      <c r="C60" s="328">
+      <c r="C60" s="327">
         <f>IF(ISBLANK(Zusatzangabe_x), "", Zusatzangabe_x1*Haltedauer)</f>
         <v>1120</v>
       </c>
-      <c r="D60" s="327" t="str">
+      <c r="D60" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", "EUR")</f>
         <v>EUR</v>
       </c>
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="404"/>
-      <c r="B61" s="327" t="str">
+      <c r="A61" s="390"/>
+      <c r="B61" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
       </c>
-      <c r="C61" s="328" t="str">
+      <c r="C61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y1*Haltedauer)</f>
         <v/>
       </c>
-      <c r="D61" s="327" t="str">
+      <c r="D61" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", "EUR")</f>
         <v/>
       </c>
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="404"/>
-      <c r="B62" s="327" t="str">
+      <c r="A62" s="390"/>
+      <c r="B62" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
       </c>
-      <c r="C62" s="328" t="str">
+      <c r="C62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z1*Haltedauer)</f>
         <v/>
       </c>
-      <c r="D62" s="327" t="str">
+      <c r="D62" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", "EUR")</f>
         <v/>
       </c>
@@ -23759,7 +23756,7 @@
       <c r="B63" s="64" t="s">
         <v>91</v>
       </c>
-      <c r="C63" s="284">
+      <c r="C63" s="283">
         <f>SUM(C54:C62)</f>
         <v>67927.591837945787</v>
       </c>
@@ -23775,7 +23772,7 @@
       <c r="B65" s="68" t="s">
         <v>166</v>
       </c>
-      <c r="C65" s="285">
+      <c r="C65" s="284">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Haltedauer, C46)</f>
         <v>0</v>
       </c>
@@ -23787,7 +23784,7 @@
       <c r="B66" s="72" t="s">
         <v>96</v>
       </c>
-      <c r="C66" s="286">
+      <c r="C66" s="285">
         <f>C33*Haltedauer+C40*Haltedauer</f>
         <v>29.882222581120001</v>
       </c>
@@ -23842,7 +23839,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>20</v>
@@ -23995,7 +23992,7 @@
       <c r="B18" s="72" t="s">
         <v>143</v>
       </c>
-      <c r="C18" s="288">
+      <c r="C18" s="287">
         <f>0.0057*(ReichwPHEV2/23)^3-0.0838*(ReichwPHEV2/23)^2+0.4261*(ReichwPHEV2/23)+ 0.1633</f>
         <v>0.1633</v>
       </c>
@@ -24007,7 +24004,7 @@
       <c r="B19" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C19" s="289">
+      <c r="C19" s="288">
         <f>Verbrauch2/(1-0.9*C18)</f>
         <v>6.6820627644983182</v>
       </c>
@@ -24021,7 +24018,7 @@
       <c r="B20" s="72" t="s">
         <v>145</v>
       </c>
-      <c r="C20" s="290">
+      <c r="C20" s="289">
         <f>VerbEl_WLTP2/C18</f>
         <v>0</v>
       </c>
@@ -24035,7 +24032,7 @@
       <c r="B21" s="186" t="s">
         <v>146</v>
       </c>
-      <c r="C21" s="291">
+      <c r="C21" s="290">
         <f>0.0021*(ReichwPHEV2/23)^3-0.0358*(ReichwPHEV2/23)^2+0.2607*(ReichwPHEV2/23)- 0.0267</f>
         <v>-2.6700000000000002E-2</v>
       </c>
@@ -24044,13 +24041,13 @@
       <c r="F21" s="125"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="471" t="s">
+      <c r="A22" s="470" t="s">
         <v>11</v>
       </c>
-      <c r="B22" s="470" t="s">
+      <c r="B22" s="469" t="s">
         <v>147</v>
       </c>
-      <c r="C22" s="292">
+      <c r="C22" s="291">
         <f>C19*(1-0.9*C21)</f>
         <v>6.8426327327292125</v>
       </c>
@@ -24061,9 +24058,9 @@
       <c r="F22" s="125"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="471"/>
-      <c r="B23" s="430"/>
-      <c r="C23" s="292">
+      <c r="A23" s="470"/>
+      <c r="B23" s="429"/>
+      <c r="C23" s="291">
         <f>C20*C21</f>
         <v>0</v>
       </c>
@@ -24104,7 +24101,7 @@
       <c r="B28" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C28" s="279">
+      <c r="C28" s="278">
         <f>IF(Antriebsart2="Vollelektrisch (BEV)",0,IFERROR(VLOOKUP(Energie2,EnKostList,8,FALSE),0)*IF(Antriebsart2="Plug-In-Hybrid (PHEV)",VerbPHEV2,Verbrauch2)/100*Fahrleistung)</f>
         <v>2382.6</v>
       </c>
@@ -24118,7 +24115,7 @@
       <c r="B29" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C29" s="279">
+      <c r="C29" s="278">
         <f>IF(Antriebsart2="Verbrenner",0,VLOOKUP("Strom",EnKostList,8,FALSE)*IF(Antriebsart2="Plug-In-Hybrid (PHEV)",VerbElPHEV2,VerbEl_WLTP2)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
@@ -24132,7 +24129,7 @@
       <c r="B30" s="64" t="s">
         <v>91</v>
       </c>
-      <c r="C30" s="280">
+      <c r="C30" s="279">
         <f>SUM(C28:C29)</f>
         <v>2382.6</v>
       </c>
@@ -24164,7 +24161,7 @@
       <c r="B33" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C33" s="279">
+      <c r="C33" s="278">
         <f>IF(Antriebsart2="Plug-In-Hybrid (PHEV)",VerbPHEV2*VLOOKUP(Energie2,CO2List,2,FALSE)/100,CO2_2)*Fahrleistung/1000000</f>
         <v>3.7250000000000001</v>
       </c>
@@ -24178,7 +24175,7 @@
       <c r="B34" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C34" s="279">
+      <c r="C34" s="278">
         <f>C33*Kost_THG</f>
         <v>3203.5</v>
       </c>
@@ -24192,7 +24189,7 @@
       <c r="B35" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="C35" s="287">
+      <c r="C35" s="286">
         <f>IF(Energie2="Strom",0,NOX_2*Fahrleistung*Kost_NOX/1000)</f>
         <v>21.2</v>
       </c>
@@ -24206,7 +24203,7 @@
       <c r="B36" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="C36" s="287">
+      <c r="C36" s="286">
         <f>IF(Energie2="Strom",0,Partikel2*Fahrleistung*Kost_Partikel/1000)</f>
         <v>1.125</v>
       </c>
@@ -24220,7 +24217,7 @@
       <c r="B37" s="64" t="s">
         <v>91</v>
       </c>
-      <c r="C37" s="280">
+      <c r="C37" s="279">
         <f>SUM(C34:C36)</f>
         <v>3225.8249999999998</v>
       </c>
@@ -24252,7 +24249,7 @@
       <c r="B40" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C40" s="279">
+      <c r="C40" s="278">
         <f>IFERROR(IF(Antriebsart2="Vollelektrisch (BEV)",VLOOKUP("Strom",CO2List,3,FALSE)*VerbEl_WLTP2/100*Fahrleistung/1000000,IF(Antriebsart2="Verbrenner",VLOOKUP(Energie2,CO2List,3,FALSE)*Verbrauch2/100*Fahrleistung/1000000,VLOOKUP(Energie2,CO2List,3,FALSE)*VerbPHEV2/100*Fahrleistung/1000000+VLOOKUP("Strom",CO2List,3,FALSE)*VerbElPHEV2/100*Fahrleistung/1000000)),0)</f>
         <v>1.1852381548800002</v>
       </c>
@@ -24266,7 +24263,7 @@
       <c r="B41" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C41" s="279">
+      <c r="C41" s="278">
         <f>C40*Kost_THG</f>
         <v>1019.3048131968002</v>
       </c>
@@ -24309,13 +24306,13 @@
       <c r="F45" s="125"/>
     </row>
     <row r="46" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A46" s="404" t="s">
+      <c r="A46" s="390" t="s">
         <v>11</v>
       </c>
-      <c r="B46" s="468" t="s">
+      <c r="B46" s="467" t="s">
         <v>152</v>
       </c>
-      <c r="C46" s="281">
+      <c r="C46" s="280">
         <f>IF(OR(Antriebsart2="Vollelektrisch (BEV)",Antriebsart2="Plug-In-Hybrid (PHEV)"),Batterie2*Batterie_THG/1000,0)</f>
         <v>0</v>
       </c>
@@ -24326,9 +24323,9 @@
       <c r="F46" s="125"/>
     </row>
     <row r="47" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="404"/>
-      <c r="B47" s="469"/>
-      <c r="C47" s="281">
+      <c r="A47" s="390"/>
+      <c r="B47" s="468"/>
+      <c r="C47" s="280">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
         <v>0</v>
       </c>
@@ -24342,7 +24339,7 @@
       <c r="B48" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C48" s="279">
+      <c r="C48" s="278">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Kost_THG, C46/Haltedauer*Kost_THG)</f>
         <v>0</v>
       </c>
@@ -24379,7 +24376,7 @@
       <c r="B54" s="68" t="s">
         <v>164</v>
       </c>
-      <c r="C54" s="282">
+      <c r="C54" s="281">
         <f>IF(FinArt="Kauf",IF(KaufpreisRech="Kaufpreis",Gesamtpreis2,0),Gesamtpreis2*Haltedauer*12+IF(FinArt="Leasing",LeasSondZahl2,0))</f>
         <v>0</v>
       </c>
@@ -24390,13 +24387,13 @@
       <c r="F54" s="58"/>
     </row>
     <row r="55" spans="1:6" s="71" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A55" s="305" t="s">
+      <c r="A55" s="304" t="s">
         <v>11</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="C55" s="283">
+        <v>438</v>
+      </c>
+      <c r="C55" s="282">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis2-Gesamtpreis2*(-0.2*LN(Haltedauer)+0.667),0)</f>
         <v>25515.413295254653</v>
       </c>
@@ -24410,7 +24407,7 @@
       <c r="B56" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C56" s="283">
+      <c r="C56" s="282">
         <f>C30*Haltedauer</f>
         <v>16678.2</v>
       </c>
@@ -24423,7 +24420,7 @@
       <c r="B57" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C57" s="283">
+      <c r="C57" s="282">
         <f>C37*Haltedauer</f>
         <v>22580.774999999998</v>
       </c>
@@ -24436,7 +24433,7 @@
       <c r="B58" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C58" s="283">
+      <c r="C58" s="282">
         <f>C41*Haltedauer</f>
         <v>7135.1336923776016</v>
       </c>
@@ -24446,63 +24443,63 @@
       <c r="F58" s="58"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B59" s="329" t="s">
+      <c r="B59" s="328" t="s">
         <v>90</v>
       </c>
-      <c r="C59" s="330">
+      <c r="C59" s="329">
         <f>C48*Haltedauer</f>
         <v>0</v>
       </c>
-      <c r="D59" s="329" t="s">
+      <c r="D59" s="328" t="s">
         <v>65</v>
       </c>
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="404" t="s">
+      <c r="A60" s="390" t="s">
         <v>11</v>
       </c>
-      <c r="B60" s="327" t="str">
+      <c r="B60" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", Zusatzangabe_x)</f>
         <v>Kfz-Steuer</v>
       </c>
-      <c r="C60" s="328">
+      <c r="C60" s="327">
         <f>IF(ISBLANK(Zusatzangabe_x), "", Zusatzangabe_x2*Haltedauer)</f>
         <v>952</v>
       </c>
-      <c r="D60" s="327" t="str">
+      <c r="D60" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", "EUR")</f>
         <v>EUR</v>
       </c>
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="404"/>
-      <c r="B61" s="327" t="str">
+      <c r="A61" s="390"/>
+      <c r="B61" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
       </c>
-      <c r="C61" s="328" t="str">
+      <c r="C61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y2*Haltedauer)</f>
         <v/>
       </c>
-      <c r="D61" s="327" t="str">
+      <c r="D61" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", "EUR")</f>
         <v/>
       </c>
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="404"/>
-      <c r="B62" s="327" t="str">
+      <c r="A62" s="390"/>
+      <c r="B62" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
       </c>
-      <c r="C62" s="328" t="str">
+      <c r="C62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z2*Haltedauer)</f>
         <v/>
       </c>
-      <c r="D62" s="327" t="str">
+      <c r="D62" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", "EUR")</f>
         <v/>
       </c>
@@ -24512,7 +24509,7 @@
       <c r="B63" s="64" t="s">
         <v>91</v>
       </c>
-      <c r="C63" s="284">
+      <c r="C63" s="283">
         <f>SUM(C54:C62)</f>
         <v>72861.521987632252</v>
       </c>
@@ -24534,7 +24531,7 @@
       <c r="B65" s="68" t="s">
         <v>166</v>
       </c>
-      <c r="C65" s="285">
+      <c r="C65" s="284">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Haltedauer, C46)</f>
         <v>0</v>
       </c>
@@ -24546,7 +24543,7 @@
       <c r="B66" s="72" t="s">
         <v>96</v>
       </c>
-      <c r="C66" s="286">
+      <c r="C66" s="285">
         <f>C33*Haltedauer+C40*Haltedauer</f>
         <v>34.371667084160002</v>
       </c>
@@ -24602,7 +24599,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>20</v>
@@ -24755,7 +24752,7 @@
       <c r="B18" s="72" t="s">
         <v>143</v>
       </c>
-      <c r="C18" s="288">
+      <c r="C18" s="287">
         <f>0.0057*(ReichwPHEV3/23)^3-0.0838*(ReichwPHEV3/23)^2+0.4261*(ReichwPHEV3/23)+ 0.1633</f>
         <v>0.1633</v>
       </c>
@@ -24767,7 +24764,7 @@
       <c r="B19" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C19" s="289">
+      <c r="C19" s="288">
         <f>Verbrauch3/(1-0.9*C18)</f>
         <v>8.9094170193310909</v>
       </c>
@@ -24781,7 +24778,7 @@
       <c r="B20" s="72" t="s">
         <v>145</v>
       </c>
-      <c r="C20" s="290">
+      <c r="C20" s="289">
         <f>VerbEl_WLTP3/C18</f>
         <v>0</v>
       </c>
@@ -24795,7 +24792,7 @@
       <c r="B21" s="186" t="s">
         <v>146</v>
       </c>
-      <c r="C21" s="291">
+      <c r="C21" s="290">
         <f>0.0021*(ReichwPHEV3/23)^3-0.0358*(ReichwPHEV3/23)^2+0.2607*(ReichwPHEV3/23)- 0.0267</f>
         <v>-2.6700000000000002E-2</v>
       </c>
@@ -24804,13 +24801,13 @@
       <c r="F21" s="125"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="471" t="s">
+      <c r="A22" s="470" t="s">
         <v>11</v>
       </c>
-      <c r="B22" s="470" t="s">
+      <c r="B22" s="469" t="s">
         <v>147</v>
       </c>
-      <c r="C22" s="292">
+      <c r="C22" s="291">
         <f>C19*(1-0.9*C21)</f>
         <v>9.1235103103056172</v>
       </c>
@@ -24821,9 +24818,9 @@
       <c r="F22" s="125"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="471"/>
-      <c r="B23" s="430"/>
-      <c r="C23" s="292">
+      <c r="A23" s="470"/>
+      <c r="B23" s="429"/>
+      <c r="C23" s="291">
         <f>C20*C21</f>
         <v>0</v>
       </c>
@@ -24864,7 +24861,7 @@
       <c r="B28" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C28" s="279">
+      <c r="C28" s="278">
         <f>IF(Antriebsart3="Vollelektrisch (BEV)",0,IFERROR(VLOOKUP(Energie3,EnKostList,8,FALSE),0)*IF(Antriebsart3="Plug-In-Hybrid (PHEV)",VerbPHEV3,Verbrauch3)/100*Fahrleistung)</f>
         <v>3176.7999999999997</v>
       </c>
@@ -24878,7 +24875,7 @@
       <c r="B29" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C29" s="279">
+      <c r="C29" s="278">
         <f>IF(Antriebsart3="Verbrenner",0,VLOOKUP("Strom",EnKostList,8,FALSE)*IF(Antriebsart3="Plug-In-Hybrid (PHEV)",VerbElPHEV3,VerbEl_WLTP3)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
@@ -24892,7 +24889,7 @@
       <c r="B30" s="64" t="s">
         <v>91</v>
       </c>
-      <c r="C30" s="280">
+      <c r="C30" s="279">
         <f>SUM(C28:C29)</f>
         <v>3176.7999999999997</v>
       </c>
@@ -24924,7 +24921,7 @@
       <c r="B33" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C33" s="279">
+      <c r="C33" s="278">
         <f>IF(Antriebsart3="Plug-In-Hybrid (PHEV)",VerbPHEV3*VLOOKUP(Energie3,CO2List,2,FALSE)/100,CO2_3)*Fahrleistung/1000000</f>
         <v>4.95</v>
       </c>
@@ -24938,7 +24935,7 @@
       <c r="B34" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C34" s="279">
+      <c r="C34" s="278">
         <f>C33*Kost_THG</f>
         <v>4257</v>
       </c>
@@ -24952,7 +24949,7 @@
       <c r="B35" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="C35" s="287">
+      <c r="C35" s="286">
         <f>IF(Energie3="Strom",0,NOX_3*Fahrleistung*Kost_NOX/1000)</f>
         <v>21.1</v>
       </c>
@@ -24966,7 +24963,7 @@
       <c r="B36" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="C36" s="287">
+      <c r="C36" s="286">
         <f>IF(Energie3="Strom",0,Partikel3*Fahrleistung*Kost_Partikel/1000)</f>
         <v>1.875</v>
       </c>
@@ -24980,7 +24977,7 @@
       <c r="B37" s="64" t="s">
         <v>91</v>
       </c>
-      <c r="C37" s="280">
+      <c r="C37" s="279">
         <f>SUM(C34:C36)</f>
         <v>4279.9750000000004</v>
       </c>
@@ -25012,7 +25009,7 @@
       <c r="B40" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C40" s="279">
+      <c r="C40" s="278">
         <f>IFERROR(IF(Antriebsart3="Vollelektrisch (BEV)",VLOOKUP("Strom",CO2List,3,FALSE)*VerbEl_WLTP3/100*Fahrleistung/1000000,IF(Antriebsart3="Verbrenner",VLOOKUP(Energie3,CO2List,3,FALSE)*Verbrauch3/100*Fahrleistung/1000000,VLOOKUP(Energie3,CO2List,3,FALSE)*VerbPHEV3/100*Fahrleistung/1000000+VLOOKUP("Strom",CO2List,3,FALSE)*VerbElPHEV3/100*Fahrleistung/1000000)),0)</f>
         <v>1.58031753984</v>
       </c>
@@ -25026,7 +25023,7 @@
       <c r="B41" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C41" s="279">
+      <c r="C41" s="278">
         <f>C40*Kost_THG</f>
         <v>1359.0730842624</v>
       </c>
@@ -25069,13 +25066,13 @@
       <c r="F45" s="125"/>
     </row>
     <row r="46" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A46" s="404" t="s">
+      <c r="A46" s="390" t="s">
         <v>11</v>
       </c>
-      <c r="B46" s="468" t="s">
+      <c r="B46" s="467" t="s">
         <v>152</v>
       </c>
-      <c r="C46" s="281">
+      <c r="C46" s="280">
         <f>IF(OR(Antriebsart3="Vollelektrisch (BEV)",Antriebsart3="Plug-In-Hybrid (PHEV)"),Batterie3*Batterie_THG/1000,0)</f>
         <v>0</v>
       </c>
@@ -25086,9 +25083,9 @@
       <c r="F46" s="133"/>
     </row>
     <row r="47" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="404"/>
-      <c r="B47" s="469"/>
-      <c r="C47" s="281">
+      <c r="A47" s="390"/>
+      <c r="B47" s="468"/>
+      <c r="C47" s="280">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
         <v>0</v>
       </c>
@@ -25102,7 +25099,7 @@
       <c r="B48" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C48" s="279">
+      <c r="C48" s="278">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Kost_THG, C46/Haltedauer*Kost_THG)</f>
         <v>0</v>
       </c>
@@ -25139,7 +25136,7 @@
       <c r="B54" s="68" t="s">
         <v>164</v>
       </c>
-      <c r="C54" s="282">
+      <c r="C54" s="281">
         <f>IF(FinArt="Kauf",IF(KaufpreisRech="Kaufpreis",Gesamtpreis3,0),Gesamtpreis3*Haltedauer*12+IF(FinArt="Leasing",LeasSondZahl3,0))</f>
         <v>0</v>
       </c>
@@ -25150,13 +25147,13 @@
       <c r="F54" s="58"/>
     </row>
     <row r="55" spans="1:6" s="71" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A55" s="305" t="s">
+      <c r="A55" s="304" t="s">
         <v>11</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="C55" s="283">
+        <v>438</v>
+      </c>
+      <c r="C55" s="282">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis3-Gesamtpreis3*(-0.2*LN(Haltedauer)+0.667),0)</f>
         <v>25739.289724496084</v>
       </c>
@@ -25170,7 +25167,7 @@
       <c r="B56" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C56" s="283">
+      <c r="C56" s="282">
         <f>C30*Haltedauer</f>
         <v>22237.599999999999</v>
       </c>
@@ -25183,7 +25180,7 @@
       <c r="B57" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C57" s="283">
+      <c r="C57" s="282">
         <f>C37*Haltedauer</f>
         <v>29959.825000000004</v>
       </c>
@@ -25196,7 +25193,7 @@
       <c r="B58" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C58" s="283">
+      <c r="C58" s="282">
         <f>C41*Haltedauer</f>
         <v>9513.5115898368003</v>
       </c>
@@ -25206,63 +25203,63 @@
       <c r="F58" s="58"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B59" s="327" t="s">
+      <c r="B59" s="326" t="s">
         <v>90</v>
       </c>
-      <c r="C59" s="328">
+      <c r="C59" s="327">
         <f>C48*Haltedauer</f>
         <v>0</v>
       </c>
-      <c r="D59" s="327" t="s">
+      <c r="D59" s="326" t="s">
         <v>65</v>
       </c>
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="404" t="s">
+      <c r="A60" s="390" t="s">
         <v>11</v>
       </c>
-      <c r="B60" s="327" t="str">
+      <c r="B60" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", Zusatzangabe_x)</f>
         <v>Kfz-Steuer</v>
       </c>
-      <c r="C60" s="328">
+      <c r="C60" s="327">
         <f>IF(ISBLANK(Zusatzangabe_x), "", Zusatzangabe_x3*Haltedauer)</f>
         <v>1204</v>
       </c>
-      <c r="D60" s="327" t="str">
+      <c r="D60" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", "EUR")</f>
         <v>EUR</v>
       </c>
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="404"/>
-      <c r="B61" s="327" t="str">
+      <c r="A61" s="390"/>
+      <c r="B61" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
       </c>
-      <c r="C61" s="328" t="str">
+      <c r="C61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y3*Haltedauer)</f>
         <v/>
       </c>
-      <c r="D61" s="327" t="str">
+      <c r="D61" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", "EUR")</f>
         <v/>
       </c>
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="404"/>
-      <c r="B62" s="327" t="str">
+      <c r="A62" s="390"/>
+      <c r="B62" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
       </c>
-      <c r="C62" s="328" t="str">
+      <c r="C62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z3*Haltedauer)</f>
         <v/>
       </c>
-      <c r="D62" s="327" t="str">
+      <c r="D62" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", "EUR")</f>
         <v/>
       </c>
@@ -25272,7 +25269,7 @@
       <c r="B63" s="64" t="s">
         <v>91</v>
       </c>
-      <c r="C63" s="284">
+      <c r="C63" s="283">
         <f>SUM(C54:C62)</f>
         <v>88654.226314332889</v>
       </c>
@@ -25294,7 +25291,7 @@
       <c r="B65" s="68" t="s">
         <v>166</v>
       </c>
-      <c r="C65" s="285">
+      <c r="C65" s="284">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Haltedauer, C46)</f>
         <v>0</v>
       </c>
@@ -25306,7 +25303,7 @@
       <c r="B66" s="72" t="s">
         <v>96</v>
       </c>
-      <c r="C66" s="286">
+      <c r="C66" s="285">
         <f>C33*Haltedauer+C40*Haltedauer</f>
         <v>45.712222778879998</v>
       </c>
@@ -25340,6 +25337,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5e4dc333-02c0-4d6f-a03d-d04a548a7be7">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101006A4EC2B1D245C948A7120CE5A36078F8" ma:contentTypeVersion="14" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="4b87026bc8dcc7f3f10cc45b8239b46f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5e4dc333-02c0-4d6f-a03d-d04a548a7be7" xmlns:ns3="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b7f15f5ac45b0ba6c0c6284d6c06137b" ns2:_="" ns3:_="">
     <xsd:import namespace="5e4dc333-02c0-4d6f-a03d-d04a548a7be7"/>
@@ -25568,41 +25585,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5e4dc333-02c0-4d6f-a03d-d04a548a7be7">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C82CFA85-B81D-4C7D-99B5-F82C00D97DE4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92A2CDCF-36F6-4C30-8F9B-D45880CB8E7E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="5e4dc333-02c0-4d6f-a03d-d04a548a7be7"/>
-    <ds:schemaRef ds:uri="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -25625,9 +25611,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92A2CDCF-36F6-4C30-8F9B-D45880CB8E7E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C82CFA85-B81D-4C7D-99B5-F82C00D97DE4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="5e4dc333-02c0-4d6f-a03d-d04a548a7be7"/>
+    <ds:schemaRef ds:uri="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>